--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD123B0-2E79-4225-8012-73A32C3812A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9276F9-E3DD-4184-853E-680482030349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
@@ -1261,9 +1261,6 @@
     <t>LTTS HOME</t>
   </si>
   <si>
-    <t>https://myts.ltts.com/Home</t>
-  </si>
-  <si>
     <t>LTTS</t>
   </si>
   <si>
@@ -1301,6 +1298,9 @@
   </si>
   <si>
     <t>https://static1.anpoimages.com/wordpress/wp-content/uploads/2023/10/how-to-create-a-gantt-chart-in-google-sheets-logo.jpg</t>
+  </si>
+  <si>
+    <t>https://myltts.ltts.com/home</t>
   </si>
 </sst>
 </file>
@@ -1433,38 +1433,30 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="16">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1497,102 +1489,6 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1653,19 +1549,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D140" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D140" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
   <autoFilter ref="A1:D140" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D140">
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="7"/>
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="6"/>
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="5"/>
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="4"/>
+    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="image" totalsRowFunction="count" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="image" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2414,7 +2310,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2428,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2442,7 +2338,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -2456,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -2696,30 +2592,30 @@
     </row>
     <row r="55" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -3790,42 +3686,42 @@
       <c r="A133" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="D133" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -3903,10 +3799,11 @@
     <hyperlink ref="B57" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
     <hyperlink ref="D69" r:id="rId2" xr:uid="{63D81A31-8F44-45D4-A777-45B5373AABF8}"/>
     <hyperlink ref="B69" r:id="rId3" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
+    <hyperlink ref="B133" r:id="rId4" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52D6D32-83AC-4A2B-B0B4-8CFB35BF5C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C503D2-9EE8-497A-A041-6706AC23D6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="301">
   <si>
     <t>title</t>
   </si>
@@ -965,6 +965,18 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t>Zrok dashboard</t>
+  </si>
+  <si>
+    <t>https://myzrok.io/dashboard</t>
+  </si>
+  <si>
+    <t>https://api-v1.zrok.io/</t>
+  </si>
+  <si>
+    <t>Zrok API</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1109,71 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1213,19 +1289,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D140" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
-  <autoFilter ref="A1:D140" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D140">
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="C2:C140" dxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D142" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20">
+  <autoFilter ref="A1:D142" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D142">
+    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="16"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1494,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.453125" style="1" customWidth="1"/>
@@ -2125,10 +2201,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>111</v>
+        <v>299</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>5</v>
@@ -2136,32 +2212,32 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>124</v>
+        <v>297</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>124</v>
+        <v>110</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>124</v>
@@ -2169,10 +2245,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>124</v>
@@ -2180,43 +2256,43 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>237</v>
+        <v>129</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>236</v>
+        <v>130</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>236</v>
@@ -2224,10 +2300,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>236</v>
@@ -2235,10 +2311,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>236</v>
@@ -2246,10 +2322,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>236</v>
@@ -2257,44 +2333,44 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>274</v>
+        <v>245</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D69" s="3"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>140</v>
+        <v>247</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D71" s="3"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>140</v>
@@ -2302,10 +2378,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>140</v>
@@ -2313,21 +2389,21 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>140</v>
@@ -2335,21 +2411,21 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>140</v>
@@ -2357,10 +2433,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>140</v>
@@ -2368,10 +2444,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>140</v>
@@ -2379,10 +2455,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>140</v>
@@ -2390,10 +2466,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>140</v>
@@ -2401,10 +2477,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>140</v>
@@ -2412,10 +2488,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>140</v>
@@ -2423,10 +2499,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>140</v>
@@ -2434,10 +2510,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>140</v>
@@ -2445,10 +2521,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>140</v>
@@ -2456,10 +2532,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>140</v>
@@ -2467,10 +2543,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>140</v>
@@ -2478,10 +2554,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>140</v>
@@ -2489,32 +2565,32 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>213</v>
+        <v>183</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>213</v>
+        <v>283</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>213</v>
@@ -2522,21 +2598,21 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>213</v>
@@ -2544,21 +2620,21 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>213</v>
@@ -2566,10 +2642,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>213</v>
@@ -2577,10 +2653,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>213</v>
@@ -2588,10 +2664,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>213</v>
@@ -2599,43 +2675,43 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>186</v>
+        <v>233</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>186</v>
@@ -2643,10 +2719,10 @@
     </row>
     <row r="104" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>186</v>
@@ -2654,10 +2730,10 @@
     </row>
     <row r="105" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>186</v>
@@ -2665,10 +2741,10 @@
     </row>
     <row r="106" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>186</v>
@@ -2676,10 +2752,10 @@
     </row>
     <row r="107" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>186</v>
@@ -2687,10 +2763,10 @@
     </row>
     <row r="108" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>186</v>
@@ -2698,10 +2774,10 @@
     </row>
     <row r="109" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>186</v>
@@ -2709,10 +2785,10 @@
     </row>
     <row r="110" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>186</v>
@@ -2720,10 +2796,10 @@
     </row>
     <row r="111" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>186</v>
@@ -2731,10 +2807,10 @@
     </row>
     <row r="112" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>186</v>
@@ -2742,65 +2818,65 @@
     </row>
     <row r="113" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>272</v>
+        <v>210</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>253</v>
@@ -2808,10 +2884,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>253</v>
@@ -2819,10 +2895,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>253</v>
@@ -2830,10 +2906,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>253</v>
@@ -2841,10 +2917,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>253</v>
@@ -2852,10 +2928,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>253</v>
@@ -2863,10 +2939,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>253</v>
@@ -2874,43 +2950,43 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>157</v>
+        <v>268</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>158</v>
+        <v>269</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>159</v>
@@ -2918,32 +2994,32 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>117</v>
@@ -2951,112 +3027,136 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>118</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>280</v>
+        <v>119</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>282</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>295</v>
+        <v>120</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>134</v>
+        <v>287</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>135</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>137</v>
+        <v>290</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>135</v>
+        <v>286</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>277</v>
+        <v>134</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>275</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>275</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>250</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B57" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
-    <hyperlink ref="B69" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
-    <hyperlink ref="B133" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B59" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
+    <hyperlink ref="B71" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
+    <hyperlink ref="B135" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B58" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
+    <hyperlink ref="B57" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C503D2-9EE8-497A-A041-6706AC23D6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15212EE-2C56-4562-845E-5CBEAB55B2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="319">
   <si>
     <t>title</t>
   </si>
@@ -403,9 +403,6 @@
     <t>insta pro apk (SamMods)</t>
   </si>
   <si>
-    <t>https://www.instamod.co/</t>
-  </si>
-  <si>
     <t>PDF2IMG</t>
   </si>
   <si>
@@ -977,6 +974,63 @@
   </si>
   <si>
     <t>Zrok API</t>
+  </si>
+  <si>
+    <t>https://liteapks.com/</t>
+  </si>
+  <si>
+    <t>liteapks</t>
+  </si>
+  <si>
+    <t>https://edit-pdf.online/</t>
+  </si>
+  <si>
+    <t>edit-pdf</t>
+  </si>
+  <si>
+    <t>https://goldrate.com/en/gold/india</t>
+  </si>
+  <si>
+    <t>GoldRate</t>
+  </si>
+  <si>
+    <t>https://goldrate.com/en/currency-converter?amount=1&amp;from=USD&amp;to=INR</t>
+  </si>
+  <si>
+    <t>USD-INR</t>
+  </si>
+  <si>
+    <t>https://www.instamod.app/</t>
+  </si>
+  <si>
+    <t>https://modded-1.com/</t>
+  </si>
+  <si>
+    <t>modded1`</t>
+  </si>
+  <si>
+    <t>https://www.jiomart.com/?tab=groceries</t>
+  </si>
+  <si>
+    <t>jiomart</t>
+  </si>
+  <si>
+    <t>https://buyhatke.com/</t>
+  </si>
+  <si>
+    <t>Online_Shopping</t>
+  </si>
+  <si>
+    <t>https://pricehistoryapp.com/</t>
+  </si>
+  <si>
+    <t>Price History</t>
+  </si>
+  <si>
+    <t>https://app.flash.co/home</t>
+  </si>
+  <si>
+    <t>Flash</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1059,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1048,6 +1102,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1075,7 +1135,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1104,12 +1164,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="75">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1137,6 +1200,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1169,12 +1240,444 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1197,38 +1700,6 @@
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1289,19 +1760,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D142" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20">
-  <autoFilter ref="A1:D142" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D142">
-    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="18"/>
-    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="C2:C142" dxfId="16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D156" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+  <autoFilter ref="A1:D156" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D156">
+    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="10"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="64" totalsRowDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1570,10 +2042,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="54.08984375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.6328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="123.54296875" style="1" customWidth="1"/>
@@ -1591,7 +2063,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1915,10 +2387,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>5</v>
@@ -1926,10 +2398,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>5</v>
@@ -1937,10 +2409,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>5</v>
@@ -1948,10 +2420,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>5</v>
@@ -1959,10 +2431,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>5</v>
@@ -1970,10 +2442,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>5</v>
@@ -1981,10 +2453,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>5</v>
@@ -1992,10 +2464,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>5</v>
@@ -2003,10 +2475,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>5</v>
@@ -2014,10 +2486,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>5</v>
@@ -2025,10 +2497,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>5</v>
@@ -2036,10 +2508,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>5</v>
@@ -2047,21 +2519,21 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>5</v>
@@ -2069,10 +2541,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>5</v>
@@ -2080,43 +2552,43 @@
     </row>
     <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>5</v>
@@ -2124,10 +2596,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>5</v>
@@ -2135,10 +2607,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>5</v>
@@ -2146,32 +2618,21 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>109</v>
+        <v>299</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>5</v>
@@ -2179,10 +2640,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>5</v>
@@ -2190,10 +2651,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>300</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>5</v>
@@ -2201,10 +2662,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>5</v>
@@ -2212,10 +2673,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>297</v>
+        <v>109</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>298</v>
+        <v>110</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>5</v>
@@ -2223,940 +2684,1049 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>110</v>
+        <v>303</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C59" s="4"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>122</v>
+        <v>206</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>124</v>
+        <v>313</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>125</v>
+        <v>316</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>124</v>
+        <v>315</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>127</v>
+        <v>318</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>124</v>
+        <v>317</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>124</v>
+        <v>63</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>131</v>
+        <v>312</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>237</v>
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>236</v>
+        <v>65</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>236</v>
+        <v>290</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>236</v>
+        <v>292</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>243</v>
+        <v>121</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>236</v>
+        <v>122</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>245</v>
+        <v>124</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>236</v>
+        <v>125</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>270</v>
+        <v>126</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>236</v>
+        <v>127</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>141</v>
+        <v>236</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>140</v>
+        <v>237</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>140</v>
+        <v>239</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>140</v>
+        <v>241</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>147</v>
+        <v>242</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>149</v>
+        <v>244</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>140</v>
+        <v>245</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>140</v>
+        <v>246</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>140</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D79" s="3"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>284</v>
+        <v>167</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>283</v>
+        <v>168</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>213</v>
+        <v>170</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>213</v>
+        <v>172</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>213</v>
+        <v>174</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>213</v>
+        <v>178</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>213</v>
+        <v>180</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>213</v>
+        <v>182</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C111" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C112" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C113" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A103" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A109" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A111" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A112" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A113" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>186</v>
+      <c r="C114" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>236</v>
+      <c r="C127" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>159</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>159</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>115</v>
+        <v>253</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>116</v>
+        <v>254</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>117</v>
+        <v>252</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>119</v>
+        <v>256</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>117</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>120</v>
+        <v>257</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>121</v>
+        <v>258</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>117</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>295</v>
+        <v>261</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>133</v>
+        <v>267</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>135</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>135</v>
+        <v>235</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>275</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>278</v>
+        <v>160</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>275</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A152" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C156" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B59" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
-    <hyperlink ref="B71" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
-    <hyperlink ref="B135" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
-    <hyperlink ref="B58" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
-    <hyperlink ref="B57" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
+    <hyperlink ref="B58" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
+    <hyperlink ref="B79" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
+    <hyperlink ref="B147" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B55" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
+    <hyperlink ref="B54" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
+    <hyperlink ref="B52" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15212EE-2C56-4562-845E-5CBEAB55B2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36483C4-948B-467F-8E46-3D422DF27195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="344">
   <si>
     <t>title</t>
   </si>
@@ -1031,6 +1031,81 @@
   </si>
   <si>
     <t>Flash</t>
+  </si>
+  <si>
+    <t>https://www.google.co.in/maps/</t>
+  </si>
+  <si>
+    <t>Google Maps</t>
+  </si>
+  <si>
+    <t>https://maps.apple.com/</t>
+  </si>
+  <si>
+    <t>Apple Maps</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/playlist?list=PL60oqUfFxq2jk5_V1gNSD1aQOri28Cp0h</t>
+  </si>
+  <si>
+    <t>PLAYLISTS</t>
+  </si>
+  <si>
+    <t>Nitin_Music_Vibes🎵</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/playlist?list=PL60oqUfFxq2h2iJEx6w6P-M9wlZl4B4ah</t>
+  </si>
+  <si>
+    <t>Telugu Folk🎵</t>
+  </si>
+  <si>
+    <t>https://music.apple.com/in/playlist/telugu-nitin/pl.u-jV890dkTDyRerzp</t>
+  </si>
+  <si>
+    <t>Telugu_NITIN</t>
+  </si>
+  <si>
+    <t>https://music.apple.com/in/playlist/eng-nitin/pl.u-GgA5kZBcoK6EJyz</t>
+  </si>
+  <si>
+    <t>Eng_Nitin</t>
+  </si>
+  <si>
+    <t>https://music.apple.com/in/playlist/hindi-nitin/pl.u-kv9l29vtJ8P3B0j</t>
+  </si>
+  <si>
+    <t>Hindi_Nitin</t>
+  </si>
+  <si>
+    <t>https://music.apple.com/in/playlist/devotional/pl.u-jV890gLCDyRerzp</t>
+  </si>
+  <si>
+    <t>Devotional</t>
+  </si>
+  <si>
+    <t>https://music.apple.com/in/playlist/binural-beats-med/pl.u-kv9l2MDuJ8P3B0j</t>
+  </si>
+  <si>
+    <t>Binural Beats Med</t>
+  </si>
+  <si>
+    <t>https://music.apple.com/in/playlist/video-obs-n/pl.u-gxblgJJsbomRNrG</t>
+  </si>
+  <si>
+    <t>video_OBS_N</t>
+  </si>
+  <si>
+    <t>https://sq2qjz9jv8qn.share.zrok.io/</t>
+  </si>
+  <si>
+    <t>Zrok FLAC access link</t>
+  </si>
+  <si>
+    <t>https://odysee.com/</t>
+  </si>
+  <si>
+    <t>Odysee Video</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1247,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="77">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1254,6 +1329,30 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8CBAD"/>
@@ -1294,412 +1393,11 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1710,13 +1408,6 @@
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1746,6 +1437,406 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1760,20 +1851,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D156" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
-  <autoFilter ref="A1:D156" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D156">
-    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="13"/>
-    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="12"/>
-    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="C2:C156" dxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D168" headerRowDxfId="26" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24">
+  <autoFilter ref="A1:D168" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D159">
+    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="18"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="70" totalsRowDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="68" totalsRowDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="66" totalsRowDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="16" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="10" totalsRowDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2042,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
@@ -2442,10 +2533,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>5</v>
@@ -2453,10 +2544,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>320</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>5</v>
@@ -2464,10 +2555,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>5</v>
@@ -2475,10 +2566,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>5</v>
@@ -2486,10 +2577,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>5</v>
@@ -2497,10 +2588,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>5</v>
@@ -2508,10 +2599,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>5</v>
@@ -2519,21 +2610,21 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>5</v>
@@ -2541,10 +2632,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>5</v>
@@ -2552,43 +2643,43 @@
     </row>
     <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="C48" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>5</v>
@@ -2596,10 +2687,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>5</v>
@@ -2607,10 +2698,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>5</v>
@@ -2618,43 +2709,43 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>308</v>
+        <v>104</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C52" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>299</v>
+        <v>108</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C55" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>5</v>
@@ -2662,10 +2753,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>5</v>
@@ -2673,10 +2764,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>109</v>
+        <v>301</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>5</v>
@@ -2684,52 +2775,54 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C59" s="4"/>
+        <v>309</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>314</v>
+        <v>109</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>314</v>
+        <v>343</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>314</v>
+        <v>303</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>63</v>
+        <v>313</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>314</v>
@@ -2737,363 +2830,363 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>318</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>65</v>
+        <v>317</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>291</v>
+        <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>290</v>
+        <v>63</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>273</v>
+        <v>242</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D79" s="3"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>139</v>
@@ -3101,10 +3194,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>139</v>
@@ -3112,10 +3205,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>139</v>
@@ -3123,65 +3216,65 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>212</v>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>212</v>
@@ -3189,10 +3282,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>212</v>
@@ -3200,21 +3293,21 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>212</v>
@@ -3222,10 +3315,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>212</v>
@@ -3233,10 +3326,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>212</v>
@@ -3244,54 +3337,54 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>185</v>
+        <v>232</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>185</v>
@@ -3299,10 +3392,10 @@
     </row>
     <row r="119" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>185</v>
@@ -3310,10 +3403,10 @@
     </row>
     <row r="120" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>185</v>
@@ -3321,10 +3414,10 @@
     </row>
     <row r="121" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>185</v>
@@ -3332,10 +3425,10 @@
     </row>
     <row r="122" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>185</v>
@@ -3343,10 +3436,10 @@
     </row>
     <row r="123" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>185</v>
@@ -3354,10 +3447,10 @@
     </row>
     <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>185</v>
@@ -3365,10 +3458,10 @@
     </row>
     <row r="125" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>185</v>
@@ -3376,10 +3469,10 @@
     </row>
     <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>185</v>
@@ -3387,76 +3480,76 @@
     </row>
     <row r="127" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>252</v>
+        <v>209</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>255</v>
+        <v>112</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>256</v>
+        <v>113</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>252</v>
@@ -3464,10 +3557,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>252</v>
@@ -3475,10 +3568,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>252</v>
@@ -3486,10 +3579,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>252</v>
@@ -3497,10 +3590,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>252</v>
@@ -3508,10 +3601,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>252</v>
@@ -3519,164 +3612,164 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>158</v>
+        <v>235</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
-        <v>280</v>
+        <v>114</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>281</v>
+        <v>116</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>294</v>
+        <v>117</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>287</v>
+        <v>119</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>286</v>
+        <v>120</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>285</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>133</v>
+        <v>284</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>135</v>
+        <v>287</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>136</v>
+        <v>286</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>134</v>
+        <v>285</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>305</v>
+        <v>132</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>304</v>
+        <v>133</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>134</v>
@@ -3684,45 +3777,177 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>275</v>
+        <v>135</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B159" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C159" s="1" t="s">
         <v>249</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A167" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B58" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
-    <hyperlink ref="B79" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
-    <hyperlink ref="B147" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
-    <hyperlink ref="B55" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
-    <hyperlink ref="B54" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
-    <hyperlink ref="B52" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>
+    <hyperlink ref="B60" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
+    <hyperlink ref="B82" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
+    <hyperlink ref="B150" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B57" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
+    <hyperlink ref="B56" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
+    <hyperlink ref="B54" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36483C4-948B-467F-8E46-3D422DF27195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A8D1EB-C205-4483-8D6B-A748C784EDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="346">
   <si>
     <t>title</t>
   </si>
@@ -1106,6 +1106,12 @@
   </si>
   <si>
     <t>Odysee Video</t>
+  </si>
+  <si>
+    <t>https://www.cardekho.com/fuel-price-in-nalgonda-city</t>
+  </si>
+  <si>
+    <t>fuel  price</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1253,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1329,6 +1335,9 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1348,9 +1357,6 @@
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1394,13 +1400,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -1408,6 +1407,13 @@
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1437,406 +1443,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1851,20 +1457,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D168" headerRowDxfId="26" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24">
-  <autoFilter ref="A1:D168" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D159">
-    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="C2:C159" dxfId="18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D170" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A1:D170" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D161">
+    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="18"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="16" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2133,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
@@ -3777,32 +3383,32 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>135</v>
+        <v>345</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>136</v>
+        <v>344</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>307</v>
+        <v>135</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>134</v>
@@ -3810,65 +3416,54 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159" s="1" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C161" s="1" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A160" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A161" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>324</v>
@@ -3876,10 +3471,10 @@
     </row>
     <row r="163" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>324</v>
@@ -3887,10 +3482,10 @@
     </row>
     <row r="164" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>324</v>
@@ -3898,10 +3493,10 @@
     </row>
     <row r="165" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>324</v>
@@ -3909,10 +3504,10 @@
     </row>
     <row r="166" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>324</v>
@@ -3920,23 +3515,45 @@
     </row>
     <row r="167" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="C170" s="1" t="s">
         <v>324</v>
       </c>
     </row>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A8D1EB-C205-4483-8D6B-A748C784EDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C7A5DE-128C-42C8-8020-7212A7396E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="350">
   <si>
     <t>title</t>
   </si>
@@ -1112,6 +1112,18 @@
   </si>
   <si>
     <t>fuel  price</t>
+  </si>
+  <si>
+    <t>https://chromewebstore.google.com/detail/twitter-auto-unmute/fakckgmacmgbgegjojkihemghibljoel</t>
+  </si>
+  <si>
+    <t>Twitter Auto Unmute</t>
+  </si>
+  <si>
+    <t>https://chromewebstore.google.com/detail/ad-skipper/dinhbmppbaekibhlomcimjbhdhacoael</t>
+  </si>
+  <si>
+    <t>Ad Skipper</t>
   </si>
 </sst>
 </file>
@@ -1457,14 +1469,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D170" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A1:D170" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D161">
-    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="C2:C161" dxfId="18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D172" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A1:D172" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D163">
+    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="18"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
@@ -1739,7 +1751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
@@ -3097,10 +3109,10 @@
     </row>
     <row r="128" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>204</v>
+        <v>347</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>205</v>
+        <v>346</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>185</v>
@@ -3108,10 +3120,10 @@
     </row>
     <row r="129" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>206</v>
+        <v>349</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>207</v>
+        <v>348</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>185</v>
@@ -3119,65 +3131,65 @@
     </row>
     <row r="130" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>271</v>
+        <v>209</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>251</v>
+        <v>111</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>253</v>
+        <v>112</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>252</v>
@@ -3185,10 +3197,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>252</v>
@@ -3196,10 +3208,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>252</v>
@@ -3207,10 +3219,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>252</v>
@@ -3218,10 +3230,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>252</v>
@@ -3229,10 +3241,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>252</v>
@@ -3240,10 +3252,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>252</v>
@@ -3251,43 +3263,43 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>156</v>
+        <v>267</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>157</v>
+        <v>268</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>158</v>
+        <v>235</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>158</v>
@@ -3295,32 +3307,32 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>116</v>
@@ -3328,87 +3340,87 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>280</v>
+        <v>117</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>279</v>
+        <v>118</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>281</v>
+        <v>116</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>294</v>
+        <v>119</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>132</v>
+        <v>287</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>133</v>
+        <v>286</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>134</v>
+        <v>285</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>345</v>
+        <v>288</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>134</v>
+        <v>285</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>134</v>
@@ -3416,76 +3428,76 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>305</v>
+        <v>135</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>304</v>
+        <v>136</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>274</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" s="1" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B163" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C163" s="1" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A162" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A163" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>324</v>
@@ -3493,10 +3505,10 @@
     </row>
     <row r="165" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>324</v>
@@ -3504,10 +3516,10 @@
     </row>
     <row r="166" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>324</v>
@@ -3515,10 +3527,10 @@
     </row>
     <row r="167" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>324</v>
@@ -3526,10 +3538,10 @@
     </row>
     <row r="168" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>324</v>
@@ -3537,23 +3549,45 @@
     </row>
     <row r="169" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A171" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="C172" s="1" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3561,7 +3595,7 @@
   <hyperlinks>
     <hyperlink ref="B60" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
     <hyperlink ref="B82" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
-    <hyperlink ref="B150" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B152" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
     <hyperlink ref="B57" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
     <hyperlink ref="B56" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
     <hyperlink ref="B54" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C7A5DE-128C-42C8-8020-7212A7396E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF404AE-FE9F-420B-8861-47F873F47D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="352">
   <si>
     <t>title</t>
   </si>
@@ -1124,6 +1124,12 @@
   </si>
   <si>
     <t>Ad Skipper</t>
+  </si>
+  <si>
+    <t>https://ebanking.indiapost.gov.in/</t>
+  </si>
+  <si>
+    <t>IND POST SB</t>
   </si>
 </sst>
 </file>
@@ -1469,14 +1475,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D172" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A1:D172" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D163">
-    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="C2:C163" dxfId="18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D175" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A1:D175" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D166">
+    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="18"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
@@ -1751,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
@@ -2646,55 +2652,47 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>273</v>
+        <v>351</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D82" s="3"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>139</v>
+        <v>234</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>139</v>
-      </c>
+      <c r="C84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>139</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D85" s="3"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>139</v>
@@ -2702,21 +2700,21 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>139</v>
@@ -2724,10 +2722,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>139</v>
@@ -2735,21 +2733,21 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>139</v>
@@ -2757,10 +2755,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>139</v>
@@ -2768,10 +2766,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>139</v>
@@ -2779,10 +2777,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>139</v>
@@ -2790,10 +2788,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>139</v>
@@ -2801,10 +2799,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>139</v>
@@ -2812,10 +2810,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>139</v>
@@ -2823,10 +2821,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>139</v>
@@ -2834,10 +2832,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>139</v>
@@ -2845,10 +2843,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>139</v>
@@ -2856,10 +2854,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>139</v>
@@ -2867,65 +2865,65 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>212</v>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>212</v>
@@ -2933,10 +2931,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>212</v>
@@ -2944,21 +2942,21 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>212</v>
@@ -2966,10 +2964,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>212</v>
@@ -2977,10 +2975,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>212</v>
@@ -2988,54 +2986,54 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>185</v>
+        <v>232</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>185</v>
@@ -3043,10 +3041,10 @@
     </row>
     <row r="122" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>185</v>
@@ -3054,10 +3052,10 @@
     </row>
     <row r="123" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>185</v>
@@ -3065,10 +3063,10 @@
     </row>
     <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>185</v>
@@ -3076,10 +3074,10 @@
     </row>
     <row r="125" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>185</v>
@@ -3087,10 +3085,10 @@
     </row>
     <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>185</v>
@@ -3098,10 +3096,10 @@
     </row>
     <row r="127" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>185</v>
@@ -3109,10 +3107,10 @@
     </row>
     <row r="128" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>347</v>
+        <v>198</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>346</v>
+        <v>199</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>185</v>
@@ -3120,10 +3118,10 @@
     </row>
     <row r="129" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>349</v>
+        <v>200</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>348</v>
+        <v>201</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>185</v>
@@ -3131,10 +3129,10 @@
     </row>
     <row r="130" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>185</v>
@@ -3142,10 +3140,10 @@
     </row>
     <row r="131" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>206</v>
+        <v>347</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>207</v>
+        <v>346</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>185</v>
@@ -3153,76 +3151,76 @@
     </row>
     <row r="132" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>208</v>
+        <v>349</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>252</v>
+        <v>209</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>255</v>
+        <v>112</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>256</v>
+        <v>113</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>252</v>
@@ -3230,10 +3228,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>252</v>
@@ -3241,10 +3239,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>252</v>
@@ -3252,10 +3250,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>252</v>
@@ -3263,10 +3261,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>252</v>
@@ -3274,10 +3272,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>252</v>
@@ -3285,164 +3283,153 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>280</v>
+        <v>114</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>281</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>294</v>
+        <v>117</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>287</v>
+        <v>119</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>286</v>
+        <v>120</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>285</v>
+        <v>116</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>133</v>
+        <v>284</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>345</v>
+        <v>287</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>344</v>
+        <v>286</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>134</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>135</v>
+        <v>288</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>307</v>
+        <v>132</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>306</v>
+        <v>133</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>134</v>
@@ -3450,10 +3437,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>134</v>
@@ -3461,76 +3448,76 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>275</v>
+        <v>135</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>274</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A164" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A165" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A166" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>324</v>
@@ -3538,10 +3525,10 @@
     </row>
     <row r="168" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>324</v>
@@ -3549,10 +3536,10 @@
     </row>
     <row r="169" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>324</v>
@@ -3560,10 +3547,10 @@
     </row>
     <row r="170" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>324</v>
@@ -3571,31 +3558,64 @@
     </row>
     <row r="171" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A173" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A174" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="B175" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="C175" s="1" t="s">
         <v>324</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B60" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
-    <hyperlink ref="B82" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
-    <hyperlink ref="B152" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B85" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
+    <hyperlink ref="B155" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
     <hyperlink ref="B57" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
     <hyperlink ref="B56" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
     <hyperlink ref="B54" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF404AE-FE9F-420B-8861-47F873F47D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FE5538-5099-4D1D-87B6-31BD0D6AAC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="359">
   <si>
     <t>title</t>
   </si>
@@ -1130,6 +1130,27 @@
   </si>
   <si>
     <t>IND POST SB</t>
+  </si>
+  <si>
+    <t>https://cdma.cgg.gov.in/CDMA_ARBS/CDMA_PG/GetWTDetails</t>
+  </si>
+  <si>
+    <t>Bill</t>
+  </si>
+  <si>
+    <t>Water Bill</t>
+  </si>
+  <si>
+    <t>https://sourceforge.net/projects/gnuwin32/files/</t>
+  </si>
+  <si>
+    <t>WinGNU32</t>
+  </si>
+  <si>
+    <t>https://www.district.in/</t>
+  </si>
+  <si>
+    <t>Dsitrict</t>
   </si>
 </sst>
 </file>
@@ -1271,47 +1292,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1475,20 +1456,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D175" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A1:D175" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D166">
-    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="C2:C166" dxfId="18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D176" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
+  <autoFilter ref="A1:D176" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D167">
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="17"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="16"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="15"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="13"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1757,17 +1738,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D175"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D176"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="54.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="123.54296875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="77.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="54.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="123.5546875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1762,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1792,7 +1773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1803,7 +1784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1814,7 +1795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1825,7 +1806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1836,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,7 +1828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1858,7 +1839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1869,7 +1850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1880,7 +1861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1891,7 +1872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1902,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,7 +1894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -1924,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1935,7 +1916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,7 +1927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1957,7 +1938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
@@ -1968,7 +1949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
@@ -1979,7 +1960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1990,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -2001,7 +1982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
@@ -2012,7 +1993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
@@ -2023,7 +2004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
@@ -2034,7 +2015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>50</v>
       </c>
@@ -2045,7 +2026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
@@ -2056,7 +2037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -2067,7 +2048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>56</v>
       </c>
@@ -2078,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
@@ -2089,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
@@ -2100,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>66</v>
       </c>
@@ -2111,7 +2092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>68</v>
       </c>
@@ -2122,7 +2103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
@@ -2133,7 +2114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>72</v>
       </c>
@@ -2144,7 +2125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
@@ -2155,7 +2136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>322</v>
       </c>
@@ -2166,7 +2147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>320</v>
       </c>
@@ -2177,7 +2158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
@@ -2188,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>78</v>
       </c>
@@ -2199,7 +2180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>80</v>
       </c>
@@ -2210,7 +2191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -2221,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>84</v>
       </c>
@@ -2232,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>86</v>
       </c>
@@ -2243,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>88</v>
       </c>
@@ -2254,7 +2235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>90</v>
       </c>
@@ -2265,7 +2246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>92</v>
       </c>
@@ -2276,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>94</v>
       </c>
@@ -2287,7 +2268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>96</v>
       </c>
@@ -2298,7 +2279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>98</v>
       </c>
@@ -2309,7 +2290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>100</v>
       </c>
@@ -2320,7 +2301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -2331,7 +2312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>104</v>
       </c>
@@ -2342,7 +2323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>106</v>
       </c>
@@ -2353,7 +2334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>108</v>
       </c>
@@ -2364,1260 +2345,1293 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+      <c r="C57" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
+      <c r="C58" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B59" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
+      <c r="C59" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+      <c r="C61" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B62" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+      <c r="C62" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+      <c r="C63" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>62</v>
+        <v>318</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>312</v>
+        <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>311</v>
+        <v>63</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>64</v>
+        <v>312</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>65</v>
+        <v>311</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>269</v>
+        <v>244</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>350</v>
+        <v>246</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>233</v>
+        <v>351</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C84" s="8"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B86" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C86" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
+      <c r="D86" s="3"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>282</v>
+        <v>182</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A122" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>347</v>
+        <v>202</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>204</v>
+        <v>349</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>205</v>
+        <v>348</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" s="1" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B155" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C155" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" s="1" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B156" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A156" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B159" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>135</v>
+        <v>345</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>136</v>
+        <v>344</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>307</v>
+        <v>135</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B164" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C164" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A165" s="1" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" s="1" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C167" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A167" s="1" t="s">
+    <row r="168" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A168" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>324</v>
       </c>
     </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B60" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
-    <hyperlink ref="B85" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
-    <hyperlink ref="B155" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
-    <hyperlink ref="B57" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
-    <hyperlink ref="B56" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
+    <hyperlink ref="B61" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
+    <hyperlink ref="B86" r:id="rId2" xr:uid="{60680A10-1FFE-4959-B2F7-366C1B00A63D}"/>
+    <hyperlink ref="B156" r:id="rId3" xr:uid="{C95626FA-14A8-4604-BFD5-EED429938D23}"/>
+    <hyperlink ref="B58" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
+    <hyperlink ref="B57" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
     <hyperlink ref="B54" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FE5538-5099-4D1D-87B6-31BD0D6AAC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44135735-1DFB-4EC6-8BD6-47086F8140CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="364">
   <si>
     <t>title</t>
   </si>
@@ -1151,6 +1151,21 @@
   </si>
   <si>
     <t>Dsitrict</t>
+  </si>
+  <si>
+    <t>FLAC</t>
+  </si>
+  <si>
+    <t>https://github.com/anandprtp/Antra/releases/</t>
+  </si>
+  <si>
+    <t>Antra_FLAC</t>
+  </si>
+  <si>
+    <t>https://github.com/spotiflacapp/SpotiFLAC-Mobile/</t>
+  </si>
+  <si>
+    <t>Spoti_FLAC</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1307,47 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="27">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1456,20 +1511,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D176" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
-  <autoFilter ref="A1:D176" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D178" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A1:D178" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D167">
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="16"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="22"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="21"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="20"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="19"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="18"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1738,17 +1793,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D176"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D178"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="54.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="123.5546875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="54.08984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="123.54296875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1762,7 +1817,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1773,7 +1828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1784,7 +1839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1795,7 +1850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1806,7 +1861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1817,7 +1872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1828,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1839,7 +1894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1850,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1861,7 +1916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1872,7 +1927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1883,7 +1938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1894,7 +1949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -1905,7 +1960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1916,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1927,7 +1982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1938,7 +1993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
@@ -1949,7 +2004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
@@ -1960,7 +2015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1971,7 +2026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -1982,7 +2037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
@@ -1993,7 +2048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
@@ -2004,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
@@ -2015,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>50</v>
       </c>
@@ -2026,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>52</v>
       </c>
@@ -2037,7 +2092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -2048,7 +2103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>56</v>
       </c>
@@ -2059,7 +2114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
@@ -2070,7 +2125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
@@ -2081,7 +2136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>66</v>
       </c>
@@ -2092,7 +2147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>68</v>
       </c>
@@ -2103,7 +2158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
@@ -2114,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>72</v>
       </c>
@@ -2125,7 +2180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
@@ -2136,7 +2191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>322</v>
       </c>
@@ -2147,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>320</v>
       </c>
@@ -2158,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
@@ -2169,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>78</v>
       </c>
@@ -2180,7 +2235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>80</v>
       </c>
@@ -2191,7 +2246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -2202,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>84</v>
       </c>
@@ -2213,7 +2268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>86</v>
       </c>
@@ -2224,7 +2279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>88</v>
       </c>
@@ -2235,7 +2290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>90</v>
       </c>
@@ -2246,7 +2301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>92</v>
       </c>
@@ -2257,7 +2312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>94</v>
       </c>
@@ -2268,7 +2323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>96</v>
       </c>
@@ -2279,7 +2334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>98</v>
       </c>
@@ -2290,7 +2345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>100</v>
       </c>
@@ -2301,7 +2356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -2312,7 +2367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>104</v>
       </c>
@@ -2323,7 +2378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>106</v>
       </c>
@@ -2334,7 +2389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>108</v>
       </c>
@@ -2345,7 +2400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>356</v>
       </c>
@@ -2356,7 +2411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>358</v>
       </c>
@@ -2367,7 +2422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>299</v>
       </c>
@@ -2378,7 +2433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>296</v>
       </c>
@@ -2389,7 +2444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>301</v>
       </c>
@@ -2400,7 +2455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>310</v>
       </c>
@@ -2411,7 +2466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>109</v>
       </c>
@@ -2422,7 +2477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>343</v>
       </c>
@@ -2433,7 +2488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>303</v>
       </c>
@@ -2444,7 +2499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>206</v>
       </c>
@@ -2455,7 +2510,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>316</v>
       </c>
@@ -2466,7 +2521,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>318</v>
       </c>
@@ -2477,7 +2532,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>62</v>
       </c>
@@ -2488,7 +2543,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>312</v>
       </c>
@@ -2499,7 +2554,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>64</v>
       </c>
@@ -2510,7 +2565,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>291</v>
       </c>
@@ -2521,7 +2576,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>293</v>
       </c>
@@ -2532,7 +2587,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>121</v>
       </c>
@@ -2543,7 +2598,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>124</v>
       </c>
@@ -2554,7 +2609,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>126</v>
       </c>
@@ -2565,7 +2620,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>128</v>
       </c>
@@ -2576,7 +2631,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>130</v>
       </c>
@@ -2587,7 +2642,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>236</v>
       </c>
@@ -2598,7 +2653,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>238</v>
       </c>
@@ -2609,7 +2664,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>240</v>
       </c>
@@ -2620,7 +2675,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>242</v>
       </c>
@@ -2631,7 +2686,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>244</v>
       </c>
@@ -2642,7 +2697,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>269</v>
       </c>
@@ -2653,7 +2708,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>351</v>
       </c>
@@ -2664,7 +2719,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>233</v>
       </c>
@@ -2675,10 +2730,10 @@
         <v>235</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C85" s="8"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>270</v>
       </c>
@@ -2690,7 +2745,7 @@
       </c>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>137</v>
       </c>
@@ -2701,7 +2756,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>140</v>
       </c>
@@ -2712,7 +2767,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>142</v>
       </c>
@@ -2723,7 +2778,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>144</v>
       </c>
@@ -2734,7 +2789,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>146</v>
       </c>
@@ -2745,7 +2800,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>148</v>
       </c>
@@ -2756,7 +2811,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>150</v>
       </c>
@@ -2767,7 +2822,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>152</v>
       </c>
@@ -2778,7 +2833,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>154</v>
       </c>
@@ -2789,7 +2844,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>163</v>
       </c>
@@ -2800,7 +2855,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>165</v>
       </c>
@@ -2811,7 +2866,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>167</v>
       </c>
@@ -2822,7 +2877,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>169</v>
       </c>
@@ -2833,7 +2888,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>171</v>
       </c>
@@ -2844,7 +2899,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>173</v>
       </c>
@@ -2855,7 +2910,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>175</v>
       </c>
@@ -2866,7 +2921,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>177</v>
       </c>
@@ -2877,7 +2932,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>179</v>
       </c>
@@ -2888,7 +2943,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>181</v>
       </c>
@@ -2899,7 +2954,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>283</v>
       </c>
@@ -2910,7 +2965,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>354</v>
       </c>
@@ -2921,7 +2976,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>210</v>
       </c>
@@ -2932,7 +2987,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>213</v>
       </c>
@@ -2943,7 +2998,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>215</v>
       </c>
@@ -2954,7 +3009,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>217</v>
       </c>
@@ -2965,7 +3020,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>219</v>
       </c>
@@ -2976,7 +3031,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>221</v>
       </c>
@@ -2987,7 +3042,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>223</v>
       </c>
@@ -2998,7 +3053,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>225</v>
       </c>
@@ -3009,7 +3064,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>227</v>
       </c>
@@ -3020,7 +3075,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>229</v>
       </c>
@@ -3031,7 +3086,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>231</v>
       </c>
@@ -3042,7 +3097,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>183</v>
       </c>
@@ -3053,7 +3108,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>186</v>
       </c>
@@ -3064,7 +3119,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>188</v>
       </c>
@@ -3075,7 +3130,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>190</v>
       </c>
@@ -3086,7 +3141,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>192</v>
       </c>
@@ -3097,7 +3152,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>194</v>
       </c>
@@ -3108,7 +3163,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>196</v>
       </c>
@@ -3119,7 +3174,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>198</v>
       </c>
@@ -3130,7 +3185,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>200</v>
       </c>
@@ -3141,7 +3196,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>202</v>
       </c>
@@ -3152,7 +3207,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>347</v>
       </c>
@@ -3163,7 +3218,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>349</v>
       </c>
@@ -3174,7 +3229,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>204</v>
       </c>
@@ -3185,7 +3240,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>206</v>
       </c>
@@ -3196,7 +3251,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>208</v>
       </c>
@@ -3207,7 +3262,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>272</v>
       </c>
@@ -3218,7 +3273,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>112</v>
       </c>
@@ -3229,7 +3284,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>250</v>
       </c>
@@ -3240,7 +3295,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>253</v>
       </c>
@@ -3251,7 +3306,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>255</v>
       </c>
@@ -3262,7 +3317,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>257</v>
       </c>
@@ -3273,7 +3328,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>259</v>
       </c>
@@ -3284,7 +3339,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>261</v>
       </c>
@@ -3295,7 +3350,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>263</v>
       </c>
@@ -3306,7 +3361,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>265</v>
       </c>
@@ -3317,7 +3372,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>267</v>
       </c>
@@ -3328,7 +3383,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>156</v>
       </c>
@@ -3339,7 +3394,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>159</v>
       </c>
@@ -3350,7 +3405,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>161</v>
       </c>
@@ -3361,7 +3416,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>114</v>
       </c>
@@ -3372,7 +3427,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>117</v>
       </c>
@@ -3383,7 +3438,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>119</v>
       </c>
@@ -3394,7 +3449,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>280</v>
       </c>
@@ -3405,7 +3460,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>284</v>
       </c>
@@ -3416,7 +3471,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>287</v>
       </c>
@@ -3427,7 +3482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>288</v>
       </c>
@@ -3438,7 +3493,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>132</v>
       </c>
@@ -3449,7 +3504,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>345</v>
       </c>
@@ -3460,7 +3515,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>135</v>
       </c>
@@ -3471,7 +3526,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>307</v>
       </c>
@@ -3482,7 +3537,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>305</v>
       </c>
@@ -3493,7 +3548,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>275</v>
       </c>
@@ -3504,7 +3559,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>278</v>
       </c>
@@ -3515,7 +3570,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>247</v>
       </c>
@@ -3526,7 +3581,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>325</v>
       </c>
@@ -3537,7 +3592,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>327</v>
       </c>
@@ -3548,7 +3603,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>329</v>
       </c>
@@ -3559,7 +3614,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>331</v>
       </c>
@@ -3570,7 +3625,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>333</v>
       </c>
@@ -3581,7 +3636,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>335</v>
       </c>
@@ -3592,7 +3647,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>337</v>
       </c>
@@ -3603,7 +3658,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>339</v>
       </c>
@@ -3614,7 +3669,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>341</v>
       </c>
@@ -3623,6 +3678,28 @@
       </c>
       <c r="C176" s="1" t="s">
         <v>324</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44135735-1DFB-4EC6-8BD6-47086F8140CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93672E47-F58D-4AF8-9DE4-F7ECFC0771A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="600">
   <si>
     <t>title</t>
   </si>
@@ -1166,6 +1166,714 @@
   </si>
   <si>
     <t>Spoti_FLAC</t>
+  </si>
+  <si>
+    <t>https://panzoid.com/creations</t>
+  </si>
+  <si>
+    <t>YT</t>
+  </si>
+  <si>
+    <t>panzoid</t>
+  </si>
+  <si>
+    <t>https://www.keybr.com/</t>
+  </si>
+  <si>
+    <t>TYPING</t>
+  </si>
+  <si>
+    <t>https://www.typing.com/student/lessons</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>https://unblockit.pages.dev/</t>
+  </si>
+  <si>
+    <t>https://yts.mx/</t>
+  </si>
+  <si>
+    <t>https://unblock_it.gitlab.io/site/</t>
+  </si>
+  <si>
+    <t>https://presearch.com/</t>
+  </si>
+  <si>
+    <t>https://www.entireweb.com/</t>
+  </si>
+  <si>
+    <t>https://www.shodan.io/</t>
+  </si>
+  <si>
+    <t>https://tineye.com/</t>
+  </si>
+  <si>
+    <t>https://elgoog.im/</t>
+  </si>
+  <si>
+    <t>https://duckduckgo.com/bang</t>
+  </si>
+  <si>
+    <t>https://www.searchenginemap.com/</t>
+  </si>
+  <si>
+    <t>https://blog.mojeek.com/2013/10/crawler-based-search-engine.html</t>
+  </si>
+  <si>
+    <t>https://devfolio.io/</t>
+  </si>
+  <si>
+    <t>RESUME</t>
+  </si>
+  <si>
+    <t>https://nothingprivate.gkr.pw/</t>
+  </si>
+  <si>
+    <t>PRIVACY</t>
+  </si>
+  <si>
+    <t>https://privacytests.org/</t>
+  </si>
+  <si>
+    <t>https://browserleaks.com/</t>
+  </si>
+  <si>
+    <t>https://www.whois.com/</t>
+  </si>
+  <si>
+    <t>https://tosdr.org/</t>
+  </si>
+  <si>
+    <t>https://www.webmasterworld.com/</t>
+  </si>
+  <si>
+    <t>https://reports.exodus-privacy.eu.org/en/</t>
+  </si>
+  <si>
+    <t>ANDROID APP PRIVACY BCHECK</t>
+  </si>
+  <si>
+    <t>https://spreadprivacy.com/</t>
+  </si>
+  <si>
+    <t>https://clickclickclick.click/</t>
+  </si>
+  <si>
+    <t>https://youradchoices.com/</t>
+  </si>
+  <si>
+    <t>https://optout.aboutads.info/?c=2&amp;lang=EN</t>
+  </si>
+  <si>
+    <t>https://dnsdumpster.com/</t>
+  </si>
+  <si>
+    <t>Lookup Website Hosted</t>
+  </si>
+  <si>
+    <t>https://www.freeopenvpn.org/</t>
+  </si>
+  <si>
+    <t>VPN</t>
+  </si>
+  <si>
+    <t>https://www.vpngate.net/EN/</t>
+  </si>
+  <si>
+    <t>https://ipspeed.info/freevpn_openvpn.php?language=en</t>
+  </si>
+  <si>
+    <t>https://www.vpnbook.com/</t>
+  </si>
+  <si>
+    <t>https://signature-generator.com/email-signature-generator/</t>
+  </si>
+  <si>
+    <t>https://www.cdn77.com/tls-test/</t>
+  </si>
+  <si>
+    <t>https://geekflare.com/tools</t>
+  </si>
+  <si>
+    <t>https://www.getresponse.com/pricing</t>
+  </si>
+  <si>
+    <t>MAIL_PRIVACY</t>
+  </si>
+  <si>
+    <t>https://monitor.firefox.com/</t>
+  </si>
+  <si>
+    <t>https://justdeleteme.xyz/index.html</t>
+  </si>
+  <si>
+    <t>https://haveibeenpwned.com/</t>
+  </si>
+  <si>
+    <t>https://madstream.live/</t>
+  </si>
+  <si>
+    <t>https://mhdtvworld.me/</t>
+  </si>
+  <si>
+    <t>https://jiotv.chadasaniya.ml/</t>
+  </si>
+  <si>
+    <t>LIVE_TV</t>
+  </si>
+  <si>
+    <t>GITHUB_APPS</t>
+  </si>
+  <si>
+    <t>https://github.com/agalwood/Motrix/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/th-ch/youtube-music/releases</t>
+  </si>
+  <si>
+    <t>https://transmissionbt.com/</t>
+  </si>
+  <si>
+    <t>https://anydesk.com/en/downloads/windows</t>
+  </si>
+  <si>
+    <t>https://github.com/subhra74/xdm/releases</t>
+  </si>
+  <si>
+    <t>https://chrome.google.com/webstore/detail/xtreme-download-manager/dkckaoghoiffdbomfbbodbbgmhjblecj</t>
+  </si>
+  <si>
+    <t>https://github.com/arsenetar/dupeguru/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/nextdns/windows/releases/tag/v3.0.0</t>
+  </si>
+  <si>
+    <t>https://github.com/brave/brave-browser/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/public-apis/public-apis</t>
+  </si>
+  <si>
+    <t>https://github.com/pbatard/rufus/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/raindropio/desktop/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/obsidianmd/obsidian-releases/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/0x192/universal-android-debloater/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/DNSCrypt/dnscrypt-proxy/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/FreeTubeApp/FreeTube/releases</t>
+  </si>
+  <si>
+    <t>https://www.libreoffice.org/</t>
+  </si>
+  <si>
+    <t>https://www.mp3tag.de/en/download.html</t>
+  </si>
+  <si>
+    <t>https://code.visualstudio.com/</t>
+  </si>
+  <si>
+    <t>https://atom.io/</t>
+  </si>
+  <si>
+    <t>https://www.oracle.com/java/technologies/downloads/</t>
+  </si>
+  <si>
+    <t>https://www.python.org/downloads/</t>
+  </si>
+  <si>
+    <t>https://www.jetbrains.com/pycharm/</t>
+  </si>
+  <si>
+    <t>https://www.eclipse.org/downloads/</t>
+  </si>
+  <si>
+    <t>https://gitforwindows.org/</t>
+  </si>
+  <si>
+    <t>https://www.virtualdj.com/download/index.html</t>
+  </si>
+  <si>
+    <t>https://github.com/sumatrapdfreader/sumatrapdf/releases</t>
+  </si>
+  <si>
+    <t>https://www.irfanview.com/64bit.htm</t>
+  </si>
+  <si>
+    <t>https://github.com/HandBrake/HandBrake/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/fluxcd/flux/releases</t>
+  </si>
+  <si>
+    <t>https://osdn.net/projects/crystaldiskinfo/downloads/77136/CrystalDiskInfo8_16_4.zip/</t>
+  </si>
+  <si>
+    <t>https://www.cpuid.com/softwares/cpu-z.html</t>
+  </si>
+  <si>
+    <t>https://www.techpowerup.com/gpuz/</t>
+  </si>
+  <si>
+    <t>https://fxhome.com/product/hitfilm-express</t>
+  </si>
+  <si>
+    <t>https://www.virtualbox.org/</t>
+  </si>
+  <si>
+    <t>https://www.bluestacks.com/</t>
+  </si>
+  <si>
+    <t>https://www.gameloop.com/</t>
+  </si>
+  <si>
+    <t>https://okular.kde.org/</t>
+  </si>
+  <si>
+    <t>https://github.com/syncthing/syncthing/releases</t>
+  </si>
+  <si>
+    <t>https://github.com/VSCodium/vscodium/releases</t>
+  </si>
+  <si>
+    <t>https://pdf.shizuka.my.id/</t>
+  </si>
+  <si>
+    <t>https://pdfmerge.me/</t>
+  </si>
+  <si>
+    <t>https://www.erase.bg/upload</t>
+  </si>
+  <si>
+    <t>https://github.com/QL-Win/QuickLook/releases</t>
+  </si>
+  <si>
+    <t>https://www.thregr.org/~wavexx/software/screenkey/</t>
+  </si>
+  <si>
+    <t>https://github.com/Code52/carnac</t>
+  </si>
+  <si>
+    <t>https://github.com/ventoy/Ventoy/releases/</t>
+  </si>
+  <si>
+    <t>Android_APPS</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.lastpass.lpandroid</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.tollguru.tollcalculator</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=scientific.calculator.es991.es115.es300</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.ext.ui</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.royalapps.cpuhardwareinfo</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=flar2.devcheck</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.fragileheart.gpsspeedometer</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.gamebasic.decibel</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.nihilentanalytics.TurfviewMobile</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.csdroid.pkg</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.gombosdev.ampere</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.digibites.accubattery</t>
+  </si>
+  <si>
+    <t>https://play.google.com/store/apps/details?id=com.sportandtravel.biketracker</t>
+  </si>
+  <si>
+    <t>https://github.com/vfsfitvnm/ViMusic/releases</t>
+  </si>
+  <si>
+    <t>https://download.pixelexperience.org/</t>
+  </si>
+  <si>
+    <t>https://www.avast.com/en-in/index#pc</t>
+  </si>
+  <si>
+    <t>Antivirus PC</t>
+  </si>
+  <si>
+    <t>https://www.malwarebytes.com/mwb-download</t>
+  </si>
+  <si>
+    <t>https://www.avira.com/</t>
+  </si>
+  <si>
+    <t>https://snapdrop.net/</t>
+  </si>
+  <si>
+    <t>https://toffeeshare.com/</t>
+  </si>
+  <si>
+    <t>https://wetransfer.com/</t>
+  </si>
+  <si>
+    <t>https://www.sharedrop.io/</t>
+  </si>
+  <si>
+    <t>File_Transfer</t>
+  </si>
+  <si>
+    <t>https://www.irctc.co.in/nget/train-search</t>
+  </si>
+  <si>
+    <t>https://www.zomato.com/nalgonda</t>
+  </si>
+  <si>
+    <t>https://www.swiggy.com/</t>
+  </si>
+  <si>
+    <t>https://aws.amazon.com/console/</t>
+  </si>
+  <si>
+    <t>https://www.pexels.com/</t>
+  </si>
+  <si>
+    <t>https://discord.com/</t>
+  </si>
+  <si>
+    <t>https://radio.garden/</t>
+  </si>
+  <si>
+    <t>https://weather.com/en-IN/weather/tenday/l/58b2a5d4ab361402de684f8f055bcb4d7eb9704083bd0f27dd0115f6754b972b</t>
+  </si>
+  <si>
+    <t>https://miniwebtool.com/bitwise-calculator/</t>
+  </si>
+  <si>
+    <t>https://www.copy.ai/</t>
+  </si>
+  <si>
+    <t>https://wallpaperswide.com/</t>
+  </si>
+  <si>
+    <t>https://en.tutiempo.net/astronomy/sun-earth-moon-3d.html#UTC20260503T0750</t>
+  </si>
+  <si>
+    <t>E-BOOKS</t>
+  </si>
+  <si>
+    <t>https://libgen.li/</t>
+  </si>
+  <si>
+    <t>https://www.overdrive.com/</t>
+  </si>
+  <si>
+    <t>https://vdoc.pub/</t>
+  </si>
+  <si>
+    <t>https://github.com/EbookFoundation/free-programming-books/blob/main/books/free-programming-books-langs.md</t>
+  </si>
+  <si>
+    <t>https://github.com/EbookFoundation/free-programming-books/blob/main/books/free-programming-books-subjects.md</t>
+  </si>
+  <si>
+    <t>https://book-drive.com/</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/books</t>
+  </si>
+  <si>
+    <t>https://digilibraries.com/</t>
+  </si>
+  <si>
+    <t>https://manybooks.net/</t>
+  </si>
+  <si>
+    <t>https://www.free-ebooks.net/</t>
+  </si>
+  <si>
+    <t>https://openlibrary.org/</t>
+  </si>
+  <si>
+    <t>https://www.gutenberg.org/</t>
+  </si>
+  <si>
+    <t>https://www.pdfdrive.com/</t>
+  </si>
+  <si>
+    <t>https://librivox.org/</t>
+  </si>
+  <si>
+    <t>https://libgen.is/</t>
+  </si>
+  <si>
+    <t>https://www.bookbub.com/ebook-deals?sort=recency</t>
+  </si>
+  <si>
+    <t>https://1lib.in/</t>
+  </si>
+  <si>
+    <t>https://www.worldcat.org/</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/books/spring-make-make-community-books?partner=universalsci</t>
+  </si>
+  <si>
+    <t>http://www.techbooksyard.com/</t>
+  </si>
+  <si>
+    <t>https://www.erexams.com/</t>
+  </si>
+  <si>
+    <t>https://competitive-exam.in/</t>
+  </si>
+  <si>
+    <t>https://z-lib.org/</t>
+  </si>
+  <si>
+    <t>https://easyengineering.net/ece/</t>
+  </si>
+  <si>
+    <t>https://www.bookbenefits.com/</t>
+  </si>
+  <si>
+    <t>https://www.free-ebooks.net/engineering-textbooks</t>
+  </si>
+  <si>
+    <t>https://www.pdfdrive.com/engineering-books.html</t>
+  </si>
+  <si>
+    <t>https://bookboon.com/en/electrical-electronic-engineering-ebooks</t>
+  </si>
+  <si>
+    <t>https://archive.org/</t>
+  </si>
+  <si>
+    <t>https://www.lifewire.com/free-and-public-dns-servers-2626062</t>
+  </si>
+  <si>
+    <t>https://www.quad9.net/service/service-addresses-and-features</t>
+  </si>
+  <si>
+    <t>https://1.1.1.1/dns/</t>
+  </si>
+  <si>
+    <t>https://pastebin.com/ENEq0v9B</t>
+  </si>
+  <si>
+    <t>https://adguard-dns.io/</t>
+  </si>
+  <si>
+    <t>DNS</t>
+  </si>
+  <si>
+    <t>High-Level-Lang</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/mobile/folders/16ymOzi6yw3WJLPOyo42sDib0zEwqdl0a?usp=sharing</t>
+  </si>
+  <si>
+    <t>Shashank running notes CJ</t>
+  </si>
+  <si>
+    <t>https://www.quora.com/Is-it-possible-to-execute-a-Java-class-without-main-method</t>
+  </si>
+  <si>
+    <t>LBP running notes</t>
+  </si>
+  <si>
+    <t>python bootcamp</t>
+  </si>
+  <si>
+    <t>stack overflow</t>
+  </si>
+  <si>
+    <t>HackerRank</t>
+  </si>
+  <si>
+    <t>Codeforces</t>
+  </si>
+  <si>
+    <t>HackerEarth</t>
+  </si>
+  <si>
+    <t>CodeArena</t>
+  </si>
+  <si>
+    <t>Codechef</t>
+  </si>
+  <si>
+    <t>Internshala</t>
+  </si>
+  <si>
+    <t>InterviewBit</t>
+  </si>
+  <si>
+    <t>Hackathon IO</t>
+  </si>
+  <si>
+    <t>LeetCode</t>
+  </si>
+  <si>
+    <t>Practice | GeeksforGeeks | A computer science portal for geeks</t>
+  </si>
+  <si>
+    <t>Educative: Interactive Courses for Software Developers</t>
+  </si>
+  <si>
+    <t>GeeksforGeeks | A computer science portal for geeks</t>
+  </si>
+  <si>
+    <t>Take Input - Pepcoding</t>
+  </si>
+  <si>
+    <t>https://www.pepcoding.com/resources/online-java-foundation</t>
+  </si>
+  <si>
+    <t>PepCoding | PepCoding | Online resources of data structure and advanced algorithms</t>
+  </si>
+  <si>
+    <t>Virtusa Interview Questions | HackerRank</t>
+  </si>
+  <si>
+    <t>Online Courses - Anytime, Anywhere | Udemy</t>
+  </si>
+  <si>
+    <t>Udacity</t>
+  </si>
+  <si>
+    <t>Introduction - Learn | Microsoft Docs</t>
+  </si>
+  <si>
+    <t>NextStep- Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t>GDB online Debugger | Compiler - Code, Compile, Run, Debug online C, C++</t>
+  </si>
+  <si>
+    <t>Superset :: University Recruiting Platform</t>
+  </si>
+  <si>
+    <t>Your Dashboard | Forage</t>
+  </si>
+  <si>
+    <t>Edusat Registrations</t>
+  </si>
+  <si>
+    <t>Embark</t>
+  </si>
+  <si>
+    <t>30 Days of Google Cloud - Home</t>
+  </si>
+  <si>
+    <t>Machine Learning Crash Course  |  Google Developers</t>
+  </si>
+  <si>
+    <t>450 DSA Cracker</t>
+  </si>
+  <si>
+    <t>java compiler</t>
+  </si>
+  <si>
+    <t>Lesson: Classes and Objects (The Java™ Tutorials &gt; Learning the Java Language)</t>
+  </si>
+  <si>
+    <t>HashSet (Java SE 16 &amp; JDK 16)</t>
+  </si>
+  <si>
+    <t>HTML emojis</t>
+  </si>
+  <si>
+    <t>Atom Shortcuts</t>
+  </si>
+  <si>
+    <t>Coding Music</t>
+  </si>
+  <si>
+    <t>Superset</t>
+  </si>
+  <si>
+    <t>Manipal Adapt Capgremini</t>
+  </si>
+  <si>
+    <t>Atos Jumpstart</t>
+  </si>
+  <si>
+    <t>Hackerrank LBP</t>
+  </si>
+  <si>
+    <t>TapAcademy</t>
+  </si>
+  <si>
+    <t>https://filen.io/</t>
+  </si>
+  <si>
+    <t>https://mega.nz/fm/</t>
+  </si>
+  <si>
+    <t>https://web3.storage/account/</t>
+  </si>
+  <si>
+    <t>https://onionshare.org/</t>
+  </si>
+  <si>
+    <t>CLOUD_STORAGE</t>
+  </si>
+  <si>
+    <t>https://cdma.cgg.gov.in/cdma_arbs/CDMA_PG/WTMenu</t>
+  </si>
+  <si>
+    <t>TS-WATER-BILL</t>
+  </si>
+  <si>
+    <t>https://www.moneycontrol.com/</t>
+  </si>
+  <si>
+    <t>https://coinmarketcap.com/</t>
+  </si>
+  <si>
+    <t>https://www.tickertape.in/</t>
+  </si>
+  <si>
+    <t>https://simplywall.st/</t>
+  </si>
+  <si>
+    <t>https://simplywall.st/stocks/in/semiconductors/market-cap-large</t>
+  </si>
+  <si>
+    <t>https://web.stockedge.com/trending-stocks?filter-type=Major%20Stocks</t>
+  </si>
+  <si>
+    <t>https://intradayscreener.com/price-action-scanner-intraday</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/</t>
+  </si>
+  <si>
+    <t>https://ez.analog.com/</t>
+  </si>
+  <si>
+    <t>EDU</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1952,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1265,12 +1973,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1302,91 +2021,27 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="17">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1408,9 +2063,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1454,6 +2106,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -1461,13 +2120,6 @@
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1511,20 +2163,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D178" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
-  <autoFilter ref="A1:D178" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}" name="Table3" displayName="Table3" ref="A1:D184" headerRowDxfId="16" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14">
+  <autoFilter ref="A1:D184" xr:uid="{03E3FB43-9AEF-40D1-8FBE-6434E6283EA1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D167">
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="22"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="21"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="20"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="19"/>
-    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="18"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="C2:C167" dxfId="8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{FF371AF1-99C5-4AAC-BB80-035E3D76979B}" name="title" totalsRowLabel="Total" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3693D4F3-FFA3-4FC1-92A0-DB464B710988}" name="url" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{D68EC384-C9FA-42C9-A1F7-3B3C2801C07F}" name="category" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{6169A379-D1C5-4FFB-86EC-6185B276DF18}" name="Column1" totalsRowFunction="count" dataDxfId="0" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1793,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DF5B64-E9A5-40DF-A3C5-BFEB4275BBF3}">
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D426"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="77.36328125" style="1" customWidth="1"/>
@@ -3702,6 +4354,1594 @@
         <v>359</v>
       </c>
     </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B180" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B181" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B182" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B183" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B184" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B186" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B187" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B188" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B189" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B190" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B191" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B192" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B193" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B195" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B197" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B198" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B199" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B200" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B201" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B202" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B204" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B205" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B206" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B207" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B209" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B210" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B211" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B212" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B213" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B214" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B215" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B216" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B217" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B218" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B219" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B221" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B222" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B223" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B224" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B225" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B226" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B227" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B228" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B229" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B230" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B231" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B232" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B233" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B234" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B235" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B236" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B237" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B238" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B239" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B240" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B241" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B242" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B243" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B244" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B245" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B246" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B247" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B248" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B249" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B250" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B251" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B252" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B253" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B254" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B255" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B256" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B257" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B258" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B259" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B260" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B261" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B262" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B263" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B264" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B265" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B266" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B267" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B268" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B269" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B270" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B271" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B272" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B273" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B274" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B275" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B276" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B277" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B278" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B279" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B280" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B281" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B282" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B283" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B284" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B285" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B286" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B287" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B288" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B289" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B290" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B291" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B292" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B293" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B294" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B295" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B296" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B297" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B298" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B299" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B300" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B301" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B302" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B303" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B304" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B305" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B306" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B307" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B308" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B309" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B310" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B311" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="312" spans="2:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B312" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B313" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B314" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B315" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B316" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B317" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B318" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B319" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B320" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B321" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B322" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B323" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B324" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B325" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B326" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B327" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B328" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B329" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B330" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="331" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B331" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B332" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B333" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="334" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B334" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="335" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B335" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="336" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B336" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B337" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="338" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B338" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="339" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B339" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="340" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B340" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="341" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B341" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="343" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B343" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="344" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B344" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="345" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B345" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="346" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B346" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="347" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B347" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="348" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B348" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="349" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B349" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="351" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B351" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="352" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B352" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="353" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B353" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="354" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B354" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="355" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B355" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="356" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B356" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="357" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B357" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="358" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B358" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="359" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B359" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="360" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B360" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="361" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B361" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="362" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B362" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="363" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B363" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="364" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B364" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="365" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B365" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="366" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B366" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="367" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B367" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="368" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B368" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="369" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B369" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="370" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B370" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="371" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B371" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="372" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B372" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="373" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B373" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="374" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B374" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="375" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B375" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="376" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B376" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="377" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B377" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="378" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B378" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="379" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B379" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="380" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B380" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="381" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B381" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="382" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B382" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="383" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B383" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="384" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B384" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="385" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B385" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="386" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B386" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="387" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B387" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="388" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B388" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="389" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B389" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="390" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B390" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="391" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B391" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="392" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B392" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="393" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B393" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="394" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B394" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="395" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B395" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="396" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B396" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="397" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B397" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="398" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B398" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="399" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B399" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="400" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B400" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B401" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B402" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B403" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B404" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B405" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B406" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B407" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D407" s="14"/>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B408" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B409" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A410" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C410" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B415" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C415" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B416" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C416" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="417" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B417" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C417" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="418" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B418" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C418" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="419" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B419" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C419" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="420" spans="2:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B420" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C420" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="421" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B421" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C421" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="423" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B423" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="424" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B424" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="425" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B425" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="426" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B426" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B61" r:id="rId1" xr:uid="{AA559BEB-464C-4ED1-95E5-59EDFA000179}"/>
@@ -3710,10 +5950,84 @@
     <hyperlink ref="B58" r:id="rId4" xr:uid="{650F5B98-5A2F-4504-8500-FEF88678D4CD}"/>
     <hyperlink ref="B57" r:id="rId5" xr:uid="{4951DDE6-BEC9-42D4-A61D-08BBC1013A44}"/>
     <hyperlink ref="B54" r:id="rId6" xr:uid="{85F0D396-0D47-450E-9F27-710F146F101C}"/>
+    <hyperlink ref="B192" r:id="rId7" xr:uid="{65FF1DF7-FC0D-4353-A1FB-1FF4B7570ED5}"/>
+    <hyperlink ref="B272" r:id="rId8" xr:uid="{124FBE81-B24A-4A9A-BA25-79F0A921281A}"/>
+    <hyperlink ref="B287" r:id="rId9" xr:uid="{170C7A3A-DCD3-4134-A9B5-B3A68E5BFCEB}"/>
+    <hyperlink ref="B322" r:id="rId10" xr:uid="{CD604EDA-984B-4F7C-BC18-23F96CF1C934}"/>
+    <hyperlink ref="B323" r:id="rId11" xr:uid="{FD592AF1-4432-4776-9012-61BFF9205E46}"/>
+    <hyperlink ref="B327" r:id="rId12" xr:uid="{6DD88E5B-0E1D-4870-BDB8-C1B5BEB0DEAD}"/>
+    <hyperlink ref="B329" r:id="rId13" xr:uid="{A58FD682-17E5-4B05-9125-56D0A1F78899}"/>
+    <hyperlink ref="B331" r:id="rId14" xr:uid="{0B68135E-2F29-4DD7-BD2D-80A32FE7E89A}"/>
+    <hyperlink ref="B332" r:id="rId15" xr:uid="{FF1E1B13-C856-44BB-85B5-F0AFAEC3ED35}"/>
+    <hyperlink ref="B333" r:id="rId16" xr:uid="{41A04192-064B-47B6-8F92-33B94EB73BEF}"/>
+    <hyperlink ref="B335" r:id="rId17" xr:uid="{46FE58D5-7106-47FC-9C3E-4C2E3B41B158}"/>
+    <hyperlink ref="B340" r:id="rId18" xr:uid="{9401DFD8-02A1-48DA-8E19-0B688F5ED1C9}"/>
+    <hyperlink ref="B341" r:id="rId19" xr:uid="{C8082707-5F1E-4AC9-8B7D-AF6C308D8642}"/>
+    <hyperlink ref="B343" r:id="rId20" xr:uid="{CB314F3A-FE99-459F-AF23-DD381EEC6FD1}"/>
+    <hyperlink ref="B344" r:id="rId21" xr:uid="{0096BFD3-64EE-457D-9302-D8A563B40A06}"/>
+    <hyperlink ref="B345" r:id="rId22" xr:uid="{3111ECD3-CF9D-4E60-ABF9-3BE02A3A32C2}"/>
+    <hyperlink ref="B346" r:id="rId23" xr:uid="{12A5079E-77C0-4D39-B65A-4633D14116F1}"/>
+    <hyperlink ref="B347" r:id="rId24" xr:uid="{2FC9784E-05F4-4022-83E4-89629DA5E1CD}"/>
+    <hyperlink ref="B348" r:id="rId25" xr:uid="{5591E96F-764C-47CF-8AA9-BBA516006308}"/>
+    <hyperlink ref="B349" r:id="rId26" xr:uid="{23063BB9-90C6-455C-B4E9-95372264078A}"/>
+    <hyperlink ref="B352" r:id="rId27" display="https://docs.google.com/document/d/1M2hEx1RDrhEmfX60yWlWIBdylB3OnVphXTS96F-768c/edit" xr:uid="{E01A2879-0EDF-4365-9824-3990A20E5E13}"/>
+    <hyperlink ref="B353" r:id="rId28" xr:uid="{E6D7173C-47B1-49DE-82B1-40AA331D8818}"/>
+    <hyperlink ref="B354" r:id="rId29" display="https://drive.google.com/drive/u/0/folders/12tlYLXNJ23693OnyjLWCuHIWp5vheWkM" xr:uid="{CE13B1D3-0C64-4C62-AA27-722FADB238FD}"/>
+    <hyperlink ref="B356" r:id="rId30" display="https://github.com/chrisjkeenan/PythonBootcamp" xr:uid="{AB2598BB-5A32-4B2A-9011-2140B7E217EB}"/>
+    <hyperlink ref="B357" r:id="rId31" display="https://stackoverflow.com/" xr:uid="{12F90E37-C2A1-43DA-936D-5AD2CE7A9539}"/>
+    <hyperlink ref="B355" r:id="rId32" display="https://www.hackerrank.com/dashboard" xr:uid="{BDAF91CA-DCB7-432B-A524-F486FD68E112}"/>
+    <hyperlink ref="B358" r:id="rId33" display="https://codeforces.com/" xr:uid="{B921531B-995E-4D07-9C1F-D35ECB893B82}"/>
+    <hyperlink ref="B359" r:id="rId34" display="https://www.hackerearth.com/practice/" xr:uid="{76456175-EC30-455E-8145-4C7230980D9F}"/>
+    <hyperlink ref="B360" r:id="rId35" display="https://www.hackerearth.com/practice/" xr:uid="{85423E6E-1619-4B78-9E3B-F4F1AD64ACF3}"/>
+    <hyperlink ref="B361" r:id="rId36" display="https://www.hackerearth.com/codearena/" xr:uid="{5D77FFD7-911E-48EA-A2E3-D532E051C509}"/>
+    <hyperlink ref="B362" r:id="rId37" display="https://www.codechef.com/" xr:uid="{C587DFD9-5B2F-4869-9CE1-5955C85BFB15}"/>
+    <hyperlink ref="B363" r:id="rId38" display="https://internshala.com/fresher-jobs/matching-preferences" xr:uid="{F5A9F486-D26E-447C-9469-AEB9DBA418EA}"/>
+    <hyperlink ref="B364" r:id="rId39" display="https://www.interviewbit.com/practice/" xr:uid="{108EB656-E2AE-4D0C-AC5C-6D001B520731}"/>
+    <hyperlink ref="B365" r:id="rId40" display="https://www.hackathon.io/events" xr:uid="{F62A4F5D-C054-4F14-892C-EF67445336DA}"/>
+    <hyperlink ref="B366" r:id="rId41" display="https://leetcode.com/explore/" xr:uid="{80C1518E-5017-4F4B-B2BB-DF1F0E7107C9}"/>
+    <hyperlink ref="B367" r:id="rId42" display="https://practice.geeksforgeeks.org/home/" xr:uid="{DF951D2C-8B5B-444C-A9E9-D40C19E6E742}"/>
+    <hyperlink ref="B368" r:id="rId43" display="https://www.educative.io/" xr:uid="{F3AE2F24-C0CA-4AAB-A938-9563F4F9D30D}"/>
+    <hyperlink ref="B369" r:id="rId44" display="https://www.geeksforgeeks.org/" xr:uid="{6875AFD5-5440-43FF-A3C2-492A2ECF77F4}"/>
+    <hyperlink ref="B370" r:id="rId45" display="https://www.pepcoding.com/resources/online-java-foundation/getting-started/take-input-official/video" xr:uid="{6D28365F-95F5-41E7-9817-B646251DE75D}"/>
+    <hyperlink ref="B371" r:id="rId46" xr:uid="{984F5A20-1686-42A1-8D55-B94312744EBD}"/>
+    <hyperlink ref="B372" r:id="rId47" display="https://www.pepcoding.com/resources/" xr:uid="{7D1A417C-BCBE-4F4F-AC94-A9628CD7E282}"/>
+    <hyperlink ref="B373" r:id="rId48" display="https://www.hackerrank.com/interview/virtusa/challenges" xr:uid="{B1B0E3BD-941F-49D4-89F0-F0E7F555F927}"/>
+    <hyperlink ref="B374" r:id="rId49" display="https://www.udemy.com/" xr:uid="{32D8FCF2-4EAE-4BAD-8225-8B1170C15ABE}"/>
+    <hyperlink ref="B375" r:id="rId50" display="https://www.udacity.com/" xr:uid="{1585929B-2C76-4EDC-A9DB-FD58116AB337}"/>
+    <hyperlink ref="B376" r:id="rId51" display="https://docs.microsoft.com/en-us/learn/modules/intro-to-azure-fundamentals/introduction" xr:uid="{6DFE47FD-4A48-40C7-8154-E1590D41B527}"/>
+    <hyperlink ref="B377" r:id="rId52" location="/" display="https://nextstep.tcs.com/campus/ - /" xr:uid="{73B0B997-F043-4ADE-B61D-5149E6AD0DC9}"/>
+    <hyperlink ref="B378" r:id="rId53" display="https://www.onlinegdb.com/" xr:uid="{A8676E27-BC47-410A-A7E4-CF6DCA33C954}"/>
+    <hyperlink ref="B379" r:id="rId54" location="/s/feed" display="https://app.joinsuperset.com/ - /s/feed" xr:uid="{601A5598-E142-472F-AD73-35430E703418}"/>
+    <hyperlink ref="B380" r:id="rId55" display="https://www.theforage.com/dashboard?ref=s8uq9k2DwmytK2qhg" xr:uid="{AD9D90D7-4C0B-468F-93AC-52FF8B04AA93}"/>
+    <hyperlink ref="B381" r:id="rId56" display="https://elearning.iirs.gov.in/edusatregistration/studentstatus" xr:uid="{6760E8FA-1A8B-4FB2-9A70-0B06CA95B04D}"/>
+    <hyperlink ref="B382" r:id="rId57" display="https://app.upraised.co/embark/home" xr:uid="{F13BE8F6-884C-4A36-9D1B-C843F337A24F}"/>
+    <hyperlink ref="B383" r:id="rId58" location="content" display="https://events.withgoogle.com/30daysofgooglecloud/ - content" xr:uid="{63985442-378C-44CB-93E3-75AF4A7E481C}"/>
+    <hyperlink ref="B384" r:id="rId59" display="https://developers.google.com/machine-learning/crash-course" xr:uid="{EFE7EC2C-5206-4D56-AFDD-5F0A06D1DE15}"/>
+    <hyperlink ref="B385" r:id="rId60" display="https://450dsa.com/" xr:uid="{38AF8199-9FED-4C50-83B7-F7806C98EE68}"/>
+    <hyperlink ref="B386" r:id="rId61" display="https://www.tutorialspoint.com/compile_java_online.php" xr:uid="{06A01880-19E4-4931-8F16-20527F863C50}"/>
+    <hyperlink ref="B387" r:id="rId62" display="https://docs.oracle.com/javase/tutorial/java/javaOO/index.html" xr:uid="{AC13663E-F2CD-4CB0-8B72-B4356A48237E}"/>
+    <hyperlink ref="B388" r:id="rId63" display="https://docs.oracle.com/en/java/javase/16/docs/api/java.base/java/util/HashSet.html" xr:uid="{8DA660C7-9B6B-403B-95E1-C6313E320452}"/>
+    <hyperlink ref="B389" r:id="rId64" display="https://www.alt-codes.net/smiley_alt_codes.php" xr:uid="{F49C52D0-98FA-46F0-A0D3-D96E21057BDA}"/>
+    <hyperlink ref="B390" r:id="rId65" display="https://usersnap.com/blog/atom-tips-shortcuts/" xr:uid="{B59C17D3-F286-48A4-B699-D25EEBF3F7A4}"/>
+    <hyperlink ref="B391" r:id="rId66" display="https://musicforprogramming.net/latest/" xr:uid="{A22C48E7-9DF0-4529-A06E-C1522762466F}"/>
+    <hyperlink ref="B392" r:id="rId67" location="/s/feed" display="https://app.joinsuperset.com/ - /s/feed" xr:uid="{35BBC8E7-D263-4C12-A4E0-CCAF15E97709}"/>
+    <hyperlink ref="B393" r:id="rId68" display="https://manipal-adapt.in.capgemini.com/" xr:uid="{E7271674-3E7C-46B0-A7DA-D8240F5BB222}"/>
+    <hyperlink ref="B394" r:id="rId69" display="https://jumpstartatos.percipio.com/" xr:uid="{20BC0999-BFEC-4075-9D16-2FBC6571EA6A}"/>
+    <hyperlink ref="B395" r:id="rId70" display="https://www.hackerrank.com/kpb303125" xr:uid="{729DBBA3-CC1A-4CF2-9E28-324868E0ED92}"/>
+    <hyperlink ref="B396" r:id="rId71" display="https://tapacademy.thinkific.com/enrollments" xr:uid="{79E7D139-EEBA-43FC-A8B2-8F8F0033DA2B}"/>
+    <hyperlink ref="B397" r:id="rId72" xr:uid="{DAB8695B-EDE1-49B6-9C9F-00C803C389B8}"/>
+    <hyperlink ref="B398" r:id="rId73" xr:uid="{25C09976-386E-478D-8462-9D1C035C1298}"/>
+    <hyperlink ref="B399" r:id="rId74" xr:uid="{9EA5BF9B-6A6A-447C-9683-9B6000CBC802}"/>
+    <hyperlink ref="B400" r:id="rId75" xr:uid="{6DCD6524-C6A8-4344-9E02-27010BB3A30C}"/>
+    <hyperlink ref="B402" r:id="rId76" xr:uid="{E952A444-C115-49C6-882B-076F76410E58}"/>
+    <hyperlink ref="B403" r:id="rId77" xr:uid="{BDAC1DC2-E806-45E9-9AEB-A4581BC54888}"/>
+    <hyperlink ref="B404" r:id="rId78" xr:uid="{6C5A9996-A7D7-48CC-A0B8-39D4081A2F7E}"/>
+    <hyperlink ref="B405" r:id="rId79" xr:uid="{03A5B867-C65C-4FE4-B1C6-8FF7C5911B0A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId80"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId81"/>
   </tableParts>
 </worksheet>
 </file>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD0C4F2-A73E-45C1-97C1-104D913D3DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C84EFC-F368-4CB4-B72F-6E53741D7FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="807">
   <si>
     <t>title</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Apple Maps</t>
   </si>
   <si>
-    <t>https://maps.apple.com/</t>
-  </si>
-  <si>
     <t>Google Maps</t>
   </si>
   <si>
@@ -2423,6 +2420,27 @@
   </si>
   <si>
     <t>SEARCH_ENGINE</t>
+  </si>
+  <si>
+    <t>Maps</t>
+  </si>
+  <si>
+    <t>https://maps.apple.com/frame?center=17.055245%2C79.273554&amp;span=0.082152%2C0.102119</t>
+  </si>
+  <si>
+    <t>https://www.mappls.com/@lnajveql,orlovevv,nsaqlsesfjqatelts,l,f,f,f,f,f,f,zdata</t>
+  </si>
+  <si>
+    <t>Mapples</t>
+  </si>
+  <si>
+    <t>https://streamtest.in/logs</t>
+  </si>
+  <si>
+    <t>IPTV</t>
+  </si>
+  <si>
+    <t>StreamTest IPTV</t>
   </si>
 </sst>
 </file>
@@ -2451,7 +2469,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2500,8 +2518,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2533,12 +2557,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2577,10 +2614,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2588,47 +2631,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC65911"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA9D08E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </dxf>
@@ -2749,20 +2752,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:D185" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:D185" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A1:D185" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D168">
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="17"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="16"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="15"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="14"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="10"/>
+    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="9"/>
+    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="8"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" totalsRowLabel="Total" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="url" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="category" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column1" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" totalsRowLabel="Total" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="url" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="category" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column1" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3031,7 +3034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D423"/>
+  <dimension ref="A1:D427"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.33203125" style="1" customWidth="1"/>
@@ -3430,34 +3433,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>6</v>
@@ -3465,10 +3446,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>6</v>
@@ -3476,10 +3457,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>6</v>
@@ -3487,10 +3468,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>6</v>
@@ -3498,10 +3479,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>6</v>
@@ -3509,10 +3490,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>6</v>
@@ -3520,10 +3501,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>6</v>
@@ -3531,10 +3512,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>6</v>
@@ -3542,10 +3523,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>6</v>
@@ -3553,10 +3534,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>6</v>
@@ -3564,10 +3545,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>6</v>
@@ -3575,10 +3556,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>6</v>
@@ -3586,10 +3567,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>6</v>
@@ -3597,10 +3578,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>6</v>
@@ -3608,10 +3589,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>6</v>
@@ -3619,10 +3600,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>6</v>
@@ -3630,10 +3611,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>6</v>
@@ -3641,10 +3622,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
@@ -3652,10 +3633,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>6</v>
@@ -3663,10 +3644,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>6</v>
@@ -3674,10 +3655,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>6</v>
@@ -3685,10 +3666,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>6</v>
@@ -3696,10 +3677,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>6</v>
@@ -3707,10 +3688,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>6</v>
@@ -3718,10 +3699,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>6</v>
@@ -3729,10 +3710,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>6</v>
@@ -3740,233 +3721,233 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C65" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C66" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C67" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C68" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C69" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C70" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="C71" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="C73" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="C74" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="C75" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="C76" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C78" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C79" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C80" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C81" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C82" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C83" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C84" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -3974,1166 +3955,1166 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="C86" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D86" s="3"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C88" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C89" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C90" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C91" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C92" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C93" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C94" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C95" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C96" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C97" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C98" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C99" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C100" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C101" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C102" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C103" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C104" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C105" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C106" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C112" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C113" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C114" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C115" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C116" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C117" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C118" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="C119" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="C120" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C121" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C123" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C124" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C125" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C126" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C127" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C128" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C129" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C130" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C131" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C132" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C133" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C134" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C136" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C138" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C140" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C141" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C142" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C143" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C144" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C145" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C146" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C147" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="C149" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C150" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C151" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C153" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C155" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="C157" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C158" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C159" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C161" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C162" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C163" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C164" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C167" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C170" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C171" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C172" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C173" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C174" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C175" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C176" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C177" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C179" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>366</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>369</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="C182" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>371</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>374</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C184" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C185" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
+      </c>
+      <c r="C185" s="13" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>377</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C187" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
+        <v>379</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="C188" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
+        <v>381</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C189" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>383</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C190" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>385</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C191" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>387</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C192" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>389</v>
+      </c>
+      <c r="B193" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>391</v>
-      </c>
       <c r="C193" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>391</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C194" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>393</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
+        <v>396</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
+        <v>399</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>6</v>
@@ -5141,10 +5122,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>401</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="C200" s="14" t="s">
         <v>6</v>
@@ -5152,10 +5133,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
+        <v>403</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>6</v>
@@ -5163,10 +5144,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
+        <v>405</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>6</v>
@@ -5174,10 +5155,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>407</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>6</v>
@@ -5185,10 +5166,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>6</v>
@@ -5196,10 +5177,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
+        <v>411</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>6</v>
@@ -5207,10 +5188,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
+        <v>413</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="C206" s="14" t="s">
         <v>6</v>
@@ -5218,10 +5199,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>415</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>6</v>
@@ -5229,10 +5210,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
+        <v>417</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="C208" s="14" t="s">
         <v>6</v>
@@ -5240,10 +5221,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>6</v>
@@ -5251,21 +5232,21 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
+        <v>421</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
+        <v>424</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>6</v>
@@ -5273,10 +5254,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
+        <v>426</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>6</v>
@@ -5284,10 +5265,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
+        <v>428</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="C213" s="14" t="s">
         <v>6</v>
@@ -5295,552 +5276,552 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
+        <v>430</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="C214" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
+        <v>433</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="C215" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
+        <v>435</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="C216" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
+        <v>437</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C217" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
+        <v>439</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C218" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>441</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C219" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
+        <v>443</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C220" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>445</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
+        <v>448</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C223" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
+        <v>450</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C224" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
+        <v>452</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="C225" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
+        <v>455</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C226" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
+        <v>457</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C227" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
+        <v>459</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="C228" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
+        <v>461</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C229" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
+        <v>463</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="C230" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
+        <v>465</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="C231" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
+        <v>467</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C232" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
+        <v>469</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C233" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
+        <v>471</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C234" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
+        <v>473</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C235" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
+        <v>475</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C236" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
+        <v>477</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C237" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
+        <v>479</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C238" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
+        <v>481</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C239" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>483</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C240" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
+        <v>485</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C241" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
+        <v>487</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="C242" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
+        <v>489</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C243" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
+        <v>491</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="C244" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
+        <v>493</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C245" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
+        <v>495</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="C246" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
+        <v>497</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C247" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
+        <v>499</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="C248" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
+        <v>501</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C249" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
+        <v>503</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C250" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>505</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C251" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
+        <v>507</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C252" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
+        <v>509</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C253" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
+        <v>511</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C254" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
+        <v>513</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C255" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
+        <v>515</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="C256" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>517</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C257" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
+        <v>519</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C258" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
+        <v>521</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C259" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
+        <v>523</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="C260" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
+        <v>525</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="C261" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>527</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="C262" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
+        <v>529</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="C263" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
+        <v>531</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>533</v>
-      </c>
       <c r="C264" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
@@ -5848,10 +5829,10 @@
         <v>59</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
@@ -5859,337 +5840,337 @@
         <v>59</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
+        <v>533</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="C267" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
+        <v>535</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="C268" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
+        <v>537</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="C269" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
+        <v>539</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="C270" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
+        <v>541</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="C271" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
+        <v>543</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="C272" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
+        <v>545</v>
+      </c>
+      <c r="B273" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="B273" s="3" t="s">
-        <v>547</v>
-      </c>
       <c r="C273" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B274" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C274" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
+        <v>561</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C287" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
+        <v>563</v>
+      </c>
+      <c r="B288" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B288" s="3" t="s">
-        <v>565</v>
-      </c>
       <c r="C288" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
+        <v>565</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="C289" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>568</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="C290" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
+        <v>570</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>572</v>
-      </c>
       <c r="C291" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
+        <v>572</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
+        <v>575</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>577</v>
-      </c>
       <c r="C293" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
+        <v>577</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>579</v>
-      </c>
       <c r="C294" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
+        <v>579</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>581</v>
-      </c>
       <c r="C295" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
+        <v>581</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="C296" s="14" t="s">
         <v>6</v>
@@ -6197,10 +6178,10 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>583</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="C297" s="14" t="s">
         <v>6</v>
@@ -6208,10 +6189,10 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>585</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>587</v>
       </c>
       <c r="C298" s="14" t="s">
         <v>6</v>
@@ -6219,10 +6200,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
+        <v>587</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="C299" s="14" t="s">
         <v>6</v>
@@ -6230,10 +6211,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
+        <v>589</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="C300" s="14" t="s">
         <v>6</v>
@@ -6241,10 +6222,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
+        <v>591</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>593</v>
       </c>
       <c r="C301" s="14" t="s">
         <v>6</v>
@@ -6252,10 +6233,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
+        <v>593</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="C302" s="14" t="s">
         <v>6</v>
@@ -6263,10 +6244,10 @@
     </row>
     <row r="303" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
+        <v>595</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="C303" s="14" t="s">
         <v>6</v>
@@ -6274,10 +6255,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>597</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="C304" s="14" t="s">
         <v>6</v>
@@ -6285,10 +6266,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
+        <v>599</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="C305" s="14" t="s">
         <v>6</v>
@@ -6296,10 +6277,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
+        <v>599</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="C306" s="14" t="s">
         <v>6</v>
@@ -6307,10 +6288,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
+        <v>601</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="C307" s="14" t="s">
         <v>6</v>
@@ -6318,10 +6299,10 @@
     </row>
     <row r="308" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
+        <v>603</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>605</v>
       </c>
       <c r="C308" s="14" t="s">
         <v>6</v>
@@ -6329,1235 +6310,1279 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
+        <v>605</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B309" s="1" t="s">
+      <c r="C309" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
+        <v>608</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="C310" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
+        <v>610</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C311" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
+        <v>612</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C312" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
+        <v>615</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>617</v>
-      </c>
       <c r="C314" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
+        <v>617</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>619</v>
-      </c>
       <c r="C315" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
+        <v>619</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>621</v>
-      </c>
       <c r="C316" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
+        <v>621</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>623</v>
-      </c>
       <c r="C317" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
+        <v>623</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="C318" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
+        <v>623</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="C319" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
+        <v>625</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="C320" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
+        <v>627</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="C321" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
+        <v>629</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C322" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
+        <v>631</v>
+      </c>
+      <c r="B323" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B323" s="3" t="s">
-        <v>633</v>
-      </c>
       <c r="C323" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
+        <v>627</v>
+      </c>
+      <c r="B324" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B324" s="3" t="s">
-        <v>629</v>
-      </c>
       <c r="C324" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
+        <v>629</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C325" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
+        <v>631</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="C326" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
+        <v>608</v>
+      </c>
+      <c r="B328" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B328" s="3" t="s">
-        <v>610</v>
-      </c>
       <c r="C328" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
+        <v>634</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="C329" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
+        <v>636</v>
+      </c>
+      <c r="B330" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B330" s="3" t="s">
-        <v>638</v>
-      </c>
       <c r="C330" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
+        <v>638</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="C331" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
+        <v>640</v>
+      </c>
+      <c r="B332" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B332" s="3" t="s">
-        <v>642</v>
-      </c>
       <c r="C332" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
+        <v>642</v>
+      </c>
+      <c r="B333" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B333" s="3" t="s">
-        <v>644</v>
-      </c>
       <c r="C333" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
+        <v>644</v>
+      </c>
+      <c r="B334" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="B334" s="3" t="s">
-        <v>646</v>
-      </c>
       <c r="C334" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
+        <v>646</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="C335" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
+        <v>648</v>
+      </c>
+      <c r="B336" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B336" s="3" t="s">
-        <v>650</v>
-      </c>
       <c r="C336" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
+        <v>650</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>652</v>
-      </c>
       <c r="C337" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
+        <v>652</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B338" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="C338" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
+        <v>656</v>
+      </c>
+      <c r="B341" s="11" t="s">
         <v>657</v>
       </c>
-      <c r="B341" s="11" t="s">
-        <v>658</v>
-      </c>
       <c r="C341" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
+        <v>659</v>
+      </c>
+      <c r="B344" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C344" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="B344" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
+        <v>661</v>
+      </c>
+      <c r="B345" s="11" t="s">
         <v>662</v>
       </c>
-      <c r="B345" s="11" t="s">
-        <v>663</v>
-      </c>
       <c r="C345" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
+        <v>663</v>
+      </c>
+      <c r="B346" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="B346" s="11" t="s">
-        <v>665</v>
-      </c>
       <c r="C346" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B347" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
+        <v>666</v>
+      </c>
+      <c r="B348" s="11" t="s">
         <v>667</v>
       </c>
-      <c r="B348" s="11" t="s">
-        <v>668</v>
-      </c>
       <c r="C348" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
+        <v>668</v>
+      </c>
+      <c r="B349" s="11" t="s">
         <v>669</v>
       </c>
-      <c r="B349" s="11" t="s">
-        <v>670</v>
-      </c>
       <c r="C349" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
+        <v>670</v>
+      </c>
+      <c r="B350" s="11" t="s">
         <v>671</v>
       </c>
-      <c r="B350" s="11" t="s">
-        <v>672</v>
-      </c>
       <c r="C350" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B352" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="C352" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
+        <v>674</v>
+      </c>
+      <c r="B353" s="11" t="s">
         <v>675</v>
       </c>
-      <c r="B353" s="11" t="s">
-        <v>676</v>
-      </c>
       <c r="C353" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
+        <v>676</v>
+      </c>
+      <c r="B354" s="11" t="s">
         <v>677</v>
       </c>
-      <c r="B354" s="11" t="s">
-        <v>678</v>
-      </c>
       <c r="C354" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
+        <v>678</v>
+      </c>
+      <c r="B355" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="B355" s="11" t="s">
-        <v>680</v>
-      </c>
       <c r="C355" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
+        <v>680</v>
+      </c>
+      <c r="B356" s="11" t="s">
         <v>681</v>
       </c>
-      <c r="B356" s="11" t="s">
-        <v>682</v>
-      </c>
       <c r="C356" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
+        <v>682</v>
+      </c>
+      <c r="B357" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="B357" s="11" t="s">
-        <v>684</v>
-      </c>
       <c r="C357" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
+        <v>684</v>
+      </c>
+      <c r="B358" s="11" t="s">
         <v>685</v>
       </c>
-      <c r="B358" s="11" t="s">
-        <v>686</v>
-      </c>
       <c r="C358" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
+        <v>686</v>
+      </c>
+      <c r="B359" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="B359" s="11" t="s">
-        <v>688</v>
-      </c>
       <c r="C359" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
+        <v>688</v>
+      </c>
+      <c r="B360" s="11" t="s">
         <v>689</v>
       </c>
-      <c r="B360" s="11" t="s">
-        <v>690</v>
-      </c>
       <c r="C360" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
+        <v>688</v>
+      </c>
+      <c r="B361" s="11" t="s">
         <v>689</v>
       </c>
-      <c r="B361" s="11" t="s">
-        <v>690</v>
-      </c>
       <c r="C361" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
+        <v>690</v>
+      </c>
+      <c r="B362" s="11" t="s">
         <v>691</v>
       </c>
-      <c r="B362" s="11" t="s">
-        <v>692</v>
-      </c>
       <c r="C362" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
+        <v>692</v>
+      </c>
+      <c r="B363" s="11" t="s">
         <v>693</v>
       </c>
-      <c r="B363" s="11" t="s">
-        <v>694</v>
-      </c>
       <c r="C363" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
+        <v>694</v>
+      </c>
+      <c r="B364" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="B364" s="11" t="s">
-        <v>696</v>
-      </c>
       <c r="C364" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
+        <v>696</v>
+      </c>
+      <c r="B365" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="B365" s="11" t="s">
-        <v>698</v>
-      </c>
       <c r="C365" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
+        <v>698</v>
+      </c>
+      <c r="B366" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="B366" s="11" t="s">
-        <v>700</v>
-      </c>
       <c r="C366" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
+        <v>700</v>
+      </c>
+      <c r="B367" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="B367" s="11" t="s">
-        <v>702</v>
-      </c>
       <c r="C367" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
+        <v>702</v>
+      </c>
+      <c r="B368" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="B368" s="11" t="s">
-        <v>704</v>
-      </c>
       <c r="C368" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
+        <v>704</v>
+      </c>
+      <c r="B369" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="B369" s="11" t="s">
-        <v>706</v>
-      </c>
       <c r="C369" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
+        <v>707</v>
+      </c>
+      <c r="B371" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="B371" s="11" t="s">
-        <v>709</v>
-      </c>
       <c r="C371" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
+        <v>709</v>
+      </c>
+      <c r="B372" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="B372" s="11" t="s">
-        <v>711</v>
-      </c>
       <c r="C372" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
+        <v>713</v>
+      </c>
+      <c r="B375" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="B375" s="11" t="s">
-        <v>715</v>
-      </c>
       <c r="C375" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
+        <v>715</v>
+      </c>
+      <c r="B376" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="B376" s="11" t="s">
-        <v>717</v>
-      </c>
       <c r="C376" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
+        <v>717</v>
+      </c>
+      <c r="B377" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="B377" s="11" t="s">
-        <v>719</v>
-      </c>
       <c r="C377" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
+        <v>719</v>
+      </c>
+      <c r="B378" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="B378" s="11" t="s">
-        <v>721</v>
-      </c>
       <c r="C378" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
+        <v>721</v>
+      </c>
+      <c r="B379" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="B379" s="11" t="s">
-        <v>723</v>
-      </c>
       <c r="C379" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
+        <v>723</v>
+      </c>
+      <c r="B380" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="B380" s="11" t="s">
-        <v>725</v>
-      </c>
       <c r="C380" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
+        <v>725</v>
+      </c>
+      <c r="B381" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="B381" s="11" t="s">
-        <v>727</v>
-      </c>
       <c r="C381" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
+        <v>727</v>
+      </c>
+      <c r="B382" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="B382" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="C382" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
+        <v>729</v>
+      </c>
+      <c r="B383" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="B383" s="11" t="s">
-        <v>731</v>
-      </c>
       <c r="C383" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
+        <v>731</v>
+      </c>
+      <c r="B384" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="B384" s="11" t="s">
-        <v>733</v>
-      </c>
       <c r="C384" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B385" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
+        <v>734</v>
+      </c>
+      <c r="B386" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="B386" s="11" t="s">
-        <v>736</v>
-      </c>
       <c r="C386" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
+        <v>736</v>
+      </c>
+      <c r="B387" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="B387" s="11" t="s">
-        <v>738</v>
-      </c>
       <c r="C387" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
+        <v>738</v>
+      </c>
+      <c r="B388" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="B388" s="11" t="s">
-        <v>740</v>
-      </c>
       <c r="C388" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
+        <v>740</v>
+      </c>
+      <c r="B389" s="11" t="s">
         <v>741</v>
       </c>
-      <c r="B389" s="11" t="s">
-        <v>742</v>
-      </c>
       <c r="C389" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
+        <v>742</v>
+      </c>
+      <c r="B390" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="B390" s="11" t="s">
-        <v>744</v>
-      </c>
       <c r="C390" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
+        <v>744</v>
+      </c>
+      <c r="B391" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="B391" s="11" t="s">
-        <v>746</v>
-      </c>
       <c r="C391" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
+        <v>746</v>
+      </c>
+      <c r="B392" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="B392" s="11" t="s">
-        <v>748</v>
-      </c>
       <c r="C392" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B393" s="11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
+        <v>749</v>
+      </c>
+      <c r="B394" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="B394" s="11" t="s">
-        <v>751</v>
-      </c>
       <c r="C394" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
+        <v>751</v>
+      </c>
+      <c r="B395" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="B395" s="11" t="s">
-        <v>753</v>
-      </c>
       <c r="C395" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B396" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
+        <v>754</v>
+      </c>
+      <c r="B397" s="11" t="s">
         <v>755</v>
       </c>
-      <c r="B397" s="11" t="s">
-        <v>756</v>
-      </c>
       <c r="C397" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B398" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C398" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B399" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B400" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B401" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B402" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B404" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B406" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
+        <v>765</v>
+      </c>
+      <c r="B407" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B407" s="1" t="s">
+      <c r="C407" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
+        <v>768</v>
+      </c>
+      <c r="B408" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B408" s="1" t="s">
-        <v>770</v>
-      </c>
       <c r="C408" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D408" s="13"/>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
+        <v>770</v>
+      </c>
+      <c r="B409" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="B409" s="1" t="s">
-        <v>772</v>
-      </c>
       <c r="C409" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
+        <v>772</v>
+      </c>
+      <c r="B410" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B410" s="1" t="s">
-        <v>774</v>
-      </c>
       <c r="C410" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B411" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="B411" s="1" t="s">
-        <v>776</v>
-      </c>
       <c r="C411" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
+        <v>776</v>
+      </c>
+      <c r="B412" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="B412" s="1" t="s">
-        <v>778</v>
-      </c>
       <c r="C412" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
+        <v>778</v>
+      </c>
+      <c r="B413" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="B413" s="1" t="s">
-        <v>780</v>
-      </c>
       <c r="C413" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
+        <v>780</v>
+      </c>
+      <c r="B414" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B414" s="1" t="s">
-        <v>782</v>
-      </c>
       <c r="C414" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
+        <v>782</v>
+      </c>
+      <c r="B415" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="B415" s="1" t="s">
-        <v>784</v>
-      </c>
       <c r="C415" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C416" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
+        <v>785</v>
+      </c>
+      <c r="B417" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="B417" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="C417" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
+        <v>787</v>
+      </c>
+      <c r="B418" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="B418" s="1" t="s">
-        <v>789</v>
-      </c>
       <c r="C418" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
+        <v>789</v>
+      </c>
+      <c r="B420" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>791</v>
-      </c>
       <c r="C420" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
+        <v>791</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C421" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="B421" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C421" s="1" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
+        <v>793</v>
+      </c>
+      <c r="B422" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="B422" s="1" t="s">
-        <v>795</v>
-      </c>
       <c r="C422" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A424" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B424" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="C424" s="13" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B425" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C425" s="13" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>805</v>
       </c>
     </row>
   </sheetData>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitvolume\html_bookmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C84EFC-F368-4CB4-B72F-6E53741D7FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843C20CE-0C88-4C84-8D62-0D7B0ADBABE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="819">
   <si>
     <t>title</t>
   </si>
@@ -2441,6 +2441,42 @@
   </si>
   <si>
     <t>StreamTest IPTV</t>
+  </si>
+  <si>
+    <t>fuel prices #</t>
+  </si>
+  <si>
+    <t>https://www.goodreturns.in/diesel-price-in-nalgonda.html</t>
+  </si>
+  <si>
+    <t>https://randomstreetview.world/</t>
+  </si>
+  <si>
+    <t>Random street view</t>
+  </si>
+  <si>
+    <t>https://randomstreetview.com/br</t>
+  </si>
+  <si>
+    <t>Random Streeview</t>
+  </si>
+  <si>
+    <t>https://www.powercut.live/pincode/508001</t>
+  </si>
+  <si>
+    <t>Powercut live</t>
+  </si>
+  <si>
+    <t>https://channelincome.com/tool/youtube-revenue-calculator#youtube-tool</t>
+  </si>
+  <si>
+    <t>YT INCOME ESTIMATOR</t>
+  </si>
+  <si>
+    <t>https://socialblade.com/</t>
+  </si>
+  <si>
+    <t>socialblade- yt estimation</t>
   </si>
 </sst>
 </file>
@@ -2631,30 +2667,46 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="27">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -2695,6 +2747,70 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC65911"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF548235"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA9D08E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -2752,20 +2868,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:D185" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
-  <autoFilter ref="A1:D185" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D168">
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="12"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="11"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="10"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="9"/>
-    <sortCondition sortBy="cellColor" ref="C2:C168" dxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:D188" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A1:D188" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D171">
+    <sortCondition sortBy="cellColor" ref="C2:C171" dxfId="14"/>
+    <sortCondition sortBy="cellColor" ref="C2:C171" dxfId="13"/>
+    <sortCondition sortBy="cellColor" ref="C2:C171" dxfId="12"/>
+    <sortCondition sortBy="cellColor" ref="C2:C171" dxfId="11"/>
+    <sortCondition sortBy="cellColor" ref="C2:C171" dxfId="10"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" totalsRowLabel="Total" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="url" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="category" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column1" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="title" totalsRowLabel="Total" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="url" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="category" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column1" totalsRowFunction="count" dataDxfId="16" totalsRowDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3034,7 +3150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D427"/>
+  <dimension ref="A1:D433"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.33203125" style="1" customWidth="1"/>
@@ -3323,12 +3439,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>816</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>815</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>6</v>
@@ -3336,10 +3452,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>818</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>817</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>6</v>
@@ -3347,10 +3463,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>6</v>
@@ -3358,10 +3474,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>6</v>
@@ -3369,10 +3485,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>6</v>
@@ -3380,10 +3496,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>6</v>
@@ -3391,10 +3507,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>6</v>
@@ -3402,10 +3518,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>6</v>
@@ -3413,10 +3529,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>6</v>
@@ -3424,43 +3540,43 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>6</v>
@@ -3468,10 +3584,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>6</v>
@@ -3479,10 +3595,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>6</v>
@@ -3490,10 +3606,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>6</v>
@@ -3501,10 +3617,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>6</v>
@@ -3512,10 +3628,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>6</v>
@@ -3523,10 +3639,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>6</v>
@@ -3534,10 +3650,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>6</v>
@@ -3545,10 +3661,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>6</v>
@@ -3556,10 +3672,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>6</v>
@@ -3567,10 +3683,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>6</v>
@@ -3578,10 +3694,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>6</v>
@@ -3589,10 +3705,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>6</v>
@@ -3600,10 +3716,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>6</v>
@@ -3611,10 +3727,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>6</v>
@@ -3622,10 +3738,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
@@ -3633,10 +3749,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>6</v>
@@ -3644,10 +3760,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>6</v>
@@ -3655,10 +3771,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>6</v>
@@ -3666,10 +3782,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>6</v>
@@ -3677,10 +3793,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>6</v>
@@ -3688,10 +3804,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>6</v>
@@ -3699,10 +3815,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>6</v>
@@ -3710,10 +3826,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>6</v>
@@ -3721,32 +3837,32 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>130</v>
+        <v>124</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>130</v>
@@ -3754,10 +3870,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>130</v>
@@ -3765,10 +3881,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>130</v>
@@ -3776,10 +3892,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>130</v>
@@ -3787,10 +3903,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>130</v>
@@ -3798,10 +3914,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>130</v>
@@ -3809,32 +3925,32 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>147</v>
@@ -3842,10 +3958,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>147</v>
@@ -3853,43 +3969,43 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>158</v>
+        <v>153</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>158</v>
@@ -3897,10 +4013,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>158</v>
@@ -3908,10 +4024,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>158</v>
@@ -3919,10 +4035,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>158</v>
@@ -3930,10 +4046,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>158</v>
@@ -3941,58 +4057,58 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C85" s="8"/>
+      <c r="A85" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D86" s="3"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>177</v>
-      </c>
+      <c r="C87" s="8"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D88" s="3"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>177</v>
@@ -4000,10 +4116,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>177</v>
@@ -4011,21 +4127,21 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>177</v>
@@ -4033,21 +4149,21 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>177</v>
@@ -4055,10 +4171,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>177</v>
@@ -4066,10 +4182,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>177</v>
@@ -4077,10 +4193,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>177</v>
@@ -4088,10 +4204,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>177</v>
@@ -4099,10 +4215,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>177</v>
@@ -4110,10 +4226,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>177</v>
@@ -4121,10 +4237,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>177</v>
@@ -4132,10 +4248,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>177</v>
@@ -4143,10 +4259,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>177</v>
@@ -4154,10 +4270,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>177</v>
@@ -4165,10 +4281,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>177</v>
@@ -4176,10 +4292,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>177</v>
@@ -4187,43 +4303,43 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>218</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>221</v>
@@ -4231,21 +4347,21 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>221</v>
@@ -4253,21 +4369,21 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>221</v>
@@ -4275,10 +4391,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>221</v>
@@ -4286,10 +4402,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>221</v>
@@ -4297,10 +4413,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>221</v>
@@ -4308,43 +4424,43 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>244</v>
@@ -4352,10 +4468,10 @@
     </row>
     <row r="125" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>244</v>
@@ -4363,10 +4479,10 @@
     </row>
     <row r="126" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>244</v>
@@ -4374,10 +4490,10 @@
     </row>
     <row r="127" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>244</v>
@@ -4385,10 +4501,10 @@
     </row>
     <row r="128" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>244</v>
@@ -4396,10 +4512,10 @@
     </row>
     <row r="129" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>244</v>
@@ -4407,10 +4523,10 @@
     </row>
     <row r="130" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>244</v>
@@ -4418,10 +4534,10 @@
     </row>
     <row r="131" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>244</v>
@@ -4429,10 +4545,10 @@
     </row>
     <row r="132" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>244</v>
@@ -4440,10 +4556,10 @@
     </row>
     <row r="133" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>244</v>
@@ -4451,10 +4567,10 @@
     </row>
     <row r="134" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>244</v>
@@ -4462,10 +4578,10 @@
     </row>
     <row r="135" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>244</v>
@@ -4473,65 +4589,65 @@
     </row>
     <row r="136" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>272</v>
+        <v>128</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>279</v>
@@ -4539,10 +4655,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>279</v>
@@ -4550,10 +4666,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>279</v>
@@ -4561,10 +4677,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>279</v>
@@ -4572,10 +4688,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>279</v>
@@ -4583,10 +4699,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>279</v>
@@ -4594,43 +4710,43 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>279</v>
       </c>
     </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>298</v>
@@ -4638,32 +4754,32 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>797</v>
+        <v>303</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>796</v>
+        <v>304</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>305</v>
@@ -4671,10 +4787,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>305</v>
@@ -4682,87 +4798,87 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>310</v>
+        <v>797</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>311</v>
+        <v>796</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>327</v>
+        <v>807</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>328</v>
+        <v>808</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>322</v>
@@ -4770,10 +4886,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>322</v>
@@ -4781,76 +4897,76 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>333</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>341</v>
@@ -4858,10 +4974,10 @@
     </row>
     <row r="173" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>341</v>
@@ -4869,10 +4985,10 @@
     </row>
     <row r="174" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>341</v>
@@ -4880,10 +4996,10 @@
     </row>
     <row r="175" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>341</v>
@@ -4891,153 +5007,153 @@
     </row>
     <row r="176" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="C183" s="1" t="s">
         <v>365</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>366</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>369</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>371</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>798</v>
+        <v>369</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C185" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>371</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>799</v>
+        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>379</v>
+        <v>798</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>381</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>799</v>
+        <v>376</v>
+      </c>
+      <c r="C188" s="13" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>799</v>
@@ -5045,10 +5161,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>799</v>
@@ -5056,10 +5172,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>799</v>
@@ -5067,87 +5183,87 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>389</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>799</v>
       </c>
     </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>387</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>393</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>390</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>396</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>398</v>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>391</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C199" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>401</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C200" s="14" t="s">
-        <v>6</v>
+        <v>394</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C201" s="14" t="s">
-        <v>6</v>
+        <v>397</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>6</v>
@@ -5155,21 +5271,21 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" s="1" t="s">
-        <v>409</v>
+      <c r="A204" t="s">
+        <v>403</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>6</v>
@@ -5177,10 +5293,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>6</v>
@@ -5188,21 +5304,21 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C206" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>415</v>
+      <c r="A207" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>6</v>
@@ -5210,21 +5326,21 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C208" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" s="1" t="s">
-        <v>419</v>
+      <c r="A209" t="s">
+        <v>413</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>6</v>
@@ -5232,32 +5348,32 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
+      </c>
+      <c r="C210" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>426</v>
+      <c r="A212" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>6</v>
@@ -5265,54 +5381,54 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C213" s="14" t="s">
-        <v>6</v>
+        <v>422</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
+      </c>
+      <c r="C214" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
+      </c>
+      <c r="C215" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
+      </c>
+      <c r="C216" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>432</v>
@@ -5320,10 +5436,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>432</v>
@@ -5331,10 +5447,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>432</v>
@@ -5342,87 +5458,87 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>432</v>
       </c>
     </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>439</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>450</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>454</v>
@@ -5430,21 +5546,21 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>454</v>
@@ -5452,10 +5568,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>454</v>
@@ -5463,21 +5579,21 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>454</v>
@@ -5485,10 +5601,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>454</v>
@@ -5496,10 +5612,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>454</v>
@@ -5507,10 +5623,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>454</v>
@@ -5518,10 +5634,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>454</v>
@@ -5529,10 +5645,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>454</v>
@@ -5540,10 +5656,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>454</v>
@@ -5551,10 +5667,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>454</v>
@@ -5562,10 +5678,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>454</v>
@@ -5573,10 +5689,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>454</v>
@@ -5584,10 +5700,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>454</v>
@@ -5595,10 +5711,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>454</v>
@@ -5606,10 +5722,10 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>454</v>
@@ -5617,10 +5733,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>454</v>
@@ -5628,10 +5744,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>454</v>
@@ -5639,10 +5755,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>454</v>
@@ -5650,10 +5766,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>454</v>
@@ -5661,10 +5777,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>454</v>
@@ -5672,10 +5788,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>454</v>
@@ -5683,10 +5799,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>454</v>
@@ -5694,10 +5810,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>454</v>
@@ -5705,21 +5821,21 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>454</v>
@@ -5727,10 +5843,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>454</v>
@@ -5738,21 +5854,21 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>454</v>
@@ -5760,10 +5876,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>454</v>
@@ -5771,10 +5887,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>454</v>
@@ -5782,10 +5898,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>454</v>
@@ -5793,10 +5909,10 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>454</v>
@@ -5804,10 +5920,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>454</v>
@@ -5815,10 +5931,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>454</v>
@@ -5826,10 +5942,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>59</v>
+        <v>527</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>87</v>
+        <v>528</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>454</v>
@@ -5837,10 +5953,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>59</v>
+        <v>529</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>123</v>
+        <v>530</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>454</v>
@@ -5848,10 +5964,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>454</v>
@@ -5859,10 +5975,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>535</v>
+        <v>59</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>536</v>
+        <v>87</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>454</v>
@@ -5870,10 +5986,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>537</v>
+        <v>59</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>538</v>
+        <v>123</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>454</v>
@@ -5881,10 +5997,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>454</v>
@@ -5892,10 +6008,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>454</v>
@@ -5903,10 +6019,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>454</v>
@@ -5914,54 +6030,54 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>545</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>546</v>
+        <v>539</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>540</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>463</v>
+        <v>541</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>463</v>
+        <v>543</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>463</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>546</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>463</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>548</v>
@@ -5972,29 +6088,29 @@
         <v>463</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>463</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>463</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>548</v>
@@ -6005,29 +6121,29 @@
         <v>463</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>463</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>463</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>548</v>
@@ -6038,7 +6154,7 @@
         <v>463</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>548</v>
@@ -6049,117 +6165,117 @@
         <v>463</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>463</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>561</v>
+        <v>463</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>563</v>
-      </c>
-      <c r="B288" s="3" t="s">
-        <v>564</v>
+        <v>463</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>559</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>565</v>
+        <v>463</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>570</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>571</v>
+        <v>563</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>564</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>574</v>
@@ -6167,43 +6283,43 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="C296" s="14" t="s">
-        <v>6</v>
+        <v>576</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="C297" s="14" t="s">
-        <v>6</v>
+        <v>578</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="C298" s="14" t="s">
-        <v>6</v>
+        <v>580</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C299" s="14" t="s">
         <v>6</v>
@@ -6211,10 +6327,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C300" s="14" t="s">
         <v>6</v>
@@ -6222,10 +6338,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C301" s="14" t="s">
         <v>6</v>
@@ -6233,21 +6349,21 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C302" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C303" s="14" t="s">
         <v>6</v>
@@ -6255,10 +6371,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C304" s="14" t="s">
         <v>6</v>
@@ -6266,21 +6382,21 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C305" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C306" s="14" t="s">
         <v>6</v>
@@ -6288,21 +6404,21 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C307" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C308" s="14" t="s">
         <v>6</v>
@@ -6310,54 +6426,54 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>607</v>
+        <v>600</v>
+      </c>
+      <c r="C309" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+      <c r="C310" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+      <c r="C311" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>607</v>
@@ -6365,32 +6481,32 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>607</v>
@@ -6398,10 +6514,10 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>607</v>
@@ -6409,10 +6525,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>607</v>
@@ -6420,10 +6536,10 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>607</v>
@@ -6431,10 +6547,10 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>607</v>
@@ -6442,10 +6558,10 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>607</v>
@@ -6453,10 +6569,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>607</v>
@@ -6464,10 +6580,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>631</v>
-      </c>
-      <c r="B323" s="3" t="s">
-        <v>632</v>
+        <v>625</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>626</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>607</v>
@@ -6477,7 +6593,7 @@
       <c r="A324" t="s">
         <v>627</v>
       </c>
-      <c r="B324" s="3" t="s">
+      <c r="B324" s="1" t="s">
         <v>628</v>
       </c>
       <c r="C324" s="1" t="s">
@@ -6499,7 +6615,7 @@
       <c r="A326" t="s">
         <v>631</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="B326" s="3" t="s">
         <v>632</v>
       </c>
       <c r="C326" s="1" t="s">
@@ -6508,10 +6624,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>605</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>633</v>
+        <v>627</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>628</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>607</v>
@@ -6519,10 +6635,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>608</v>
-      </c>
-      <c r="B328" s="3" t="s">
-        <v>609</v>
+        <v>629</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>630</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>607</v>
@@ -6530,10 +6646,10 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>607</v>
@@ -6541,10 +6657,10 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>636</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>637</v>
+        <v>605</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>633</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>607</v>
@@ -6552,21 +6668,21 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>638</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>639</v>
+        <v>608</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>640</v>
-      </c>
-      <c r="B332" s="3" t="s">
-        <v>641</v>
+        <v>634</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>635</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>607</v>
@@ -6574,10 +6690,10 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>607</v>
@@ -6585,21 +6701,21 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>644</v>
-      </c>
-      <c r="B334" s="3" t="s">
-        <v>645</v>
+        <v>638</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>639</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>646</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>647</v>
+        <v>640</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>641</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>607</v>
@@ -6607,10 +6723,10 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>607</v>
@@ -6618,10 +6734,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>650</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>651</v>
+        <v>644</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>607</v>
@@ -6629,10 +6745,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>607</v>
@@ -6640,10 +6756,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>623</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>649</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>607</v>
@@ -6651,10 +6767,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>607</v>
@@ -6662,10 +6778,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>656</v>
-      </c>
-      <c r="B341" s="11" t="s">
-        <v>657</v>
+        <v>652</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>607</v>
@@ -6673,54 +6789,54 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>617</v>
-      </c>
-      <c r="B342" s="11" t="s">
-        <v>658</v>
+        <v>623</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>607</v>
       </c>
     </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>629</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>420</v>
+        <v>657</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>660</v>
+        <v>607</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>661</v>
+        <v>617</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
-        <v>663</v>
-      </c>
-      <c r="B346" s="11" t="s">
-        <v>664</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>660</v>
+        <v>607</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>54</v>
+        <v>420</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>660</v>
@@ -6728,10 +6844,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>660</v>
@@ -6739,10 +6855,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>660</v>
@@ -6750,54 +6866,54 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>671</v>
+        <v>54</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>660</v>
       </c>
     </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>666</v>
+      </c>
+      <c r="B351" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>463</v>
+        <v>668</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A354" t="s">
-        <v>676</v>
-      </c>
-      <c r="B354" s="11" t="s">
-        <v>677</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>678</v>
+        <v>463</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>673</v>
@@ -6805,10 +6921,10 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>673</v>
@@ -6816,10 +6932,10 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>673</v>
@@ -6827,10 +6943,10 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>673</v>
@@ -6838,10 +6954,10 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>673</v>
@@ -6849,10 +6965,10 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>673</v>
@@ -6860,10 +6976,10 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B361" s="11" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>673</v>
@@ -6871,10 +6987,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>673</v>
@@ -6882,10 +6998,10 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>673</v>
@@ -6893,10 +7009,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>673</v>
@@ -6904,10 +7020,10 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>673</v>
@@ -6915,10 +7031,10 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>673</v>
@@ -6926,10 +7042,10 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>673</v>
@@ -6937,10 +7053,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>673</v>
@@ -6948,10 +7064,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>673</v>
@@ -6959,10 +7075,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>673</v>
@@ -6970,10 +7086,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>673</v>
@@ -6981,10 +7097,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>673</v>
@@ -6992,10 +7108,10 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>673</v>
@@ -7003,10 +7119,10 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>681</v>
+        <v>708</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>673</v>
@@ -7014,10 +7130,10 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>673</v>
@@ -7025,10 +7141,10 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>673</v>
@@ -7036,10 +7152,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>718</v>
+        <v>681</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>673</v>
@@ -7047,10 +7163,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B378" s="11" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>673</v>
@@ -7058,10 +7174,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B379" s="11" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>673</v>
@@ -7069,10 +7185,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="B380" s="11" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>673</v>
@@ -7080,10 +7196,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B381" s="11" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>673</v>
@@ -7091,10 +7207,10 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B382" s="11" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>673</v>
@@ -7102,10 +7218,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B383" s="11" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>673</v>
@@ -7113,10 +7229,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B384" s="11" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>673</v>
@@ -7124,10 +7240,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B385" s="11" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>673</v>
@@ -7135,10 +7251,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B386" s="11" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>673</v>
@@ -7146,10 +7262,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>673</v>
@@ -7157,10 +7273,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>673</v>
@@ -7168,10 +7284,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="B389" s="11" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>673</v>
@@ -7179,10 +7295,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>673</v>
@@ -7190,10 +7306,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="B391" s="11" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>673</v>
@@ -7201,10 +7317,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B392" s="11" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>673</v>
@@ -7212,10 +7328,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B393" s="11" t="s">
-        <v>724</v>
+        <v>743</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>673</v>
@@ -7223,10 +7339,10 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B394" s="11" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>673</v>
@@ -7234,10 +7350,10 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B395" s="11" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>673</v>
@@ -7245,10 +7361,10 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B396" s="11" t="s">
-        <v>681</v>
+        <v>724</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>673</v>
@@ -7256,10 +7372,10 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B397" s="11" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>673</v>
@@ -7267,43 +7383,43 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B398" s="11" t="s">
-        <v>278</v>
+        <v>752</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>279</v>
+        <v>673</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B399" s="11" t="s">
-        <v>281</v>
+        <v>681</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>279</v>
+        <v>673</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B400" s="11" t="s">
-        <v>283</v>
+        <v>755</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>279</v>
+        <v>673</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B401" s="11" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>279</v>
@@ -7311,10 +7427,10 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B402" s="11" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>279</v>
@@ -7322,10 +7438,10 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>279</v>
@@ -7333,10 +7449,10 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B404" s="11" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>279</v>
@@ -7344,10 +7460,10 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>279</v>
@@ -7355,10 +7471,10 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B406" s="11" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>279</v>
@@ -7366,121 +7482,121 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>765</v>
-      </c>
-      <c r="B407" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
+      </c>
+      <c r="B407" s="11" t="s">
+        <v>291</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>767</v>
+        <v>279</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>768</v>
-      </c>
-      <c r="B408" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
+      </c>
+      <c r="B408" s="11" t="s">
+        <v>293</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="D408" s="13"/>
+        <v>279</v>
+      </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>770</v>
-      </c>
-      <c r="B409" s="1" t="s">
-        <v>771</v>
+        <v>764</v>
+      </c>
+      <c r="B409" s="11" t="s">
+        <v>295</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>767</v>
+        <v>279</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A411" s="1" t="s">
-        <v>774</v>
+      <c r="A411" t="s">
+        <v>768</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="C411" s="12" t="s">
-        <v>158</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="D411" s="13"/>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="C412" s="13" t="s">
-        <v>322</v>
+        <v>771</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="C413" s="13" t="s">
-        <v>322</v>
+        <v>773</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A414" t="s">
-        <v>780</v>
+      <c r="A414" s="1" t="s">
+        <v>774</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C414" s="13" t="s">
-        <v>322</v>
+        <v>775</v>
+      </c>
+      <c r="C414" s="12" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C415" s="13" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="C416" s="13" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="C417" s="13" t="s">
         <v>322</v>
@@ -7488,184 +7604,244 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="C418" s="13" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>782</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C419" s="13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
+        <v>785</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C420" s="13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>787</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C421" s="13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
         <v>789</v>
       </c>
-      <c r="B420" s="1" t="s">
+      <c r="B423" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="C420" s="1" t="s">
+      <c r="C423" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" t="s">
+    <row r="424" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
         <v>791</v>
       </c>
-      <c r="B421" s="1" t="s">
+      <c r="B424" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C421" s="1" t="s">
+      <c r="C424" s="1" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A422" t="s">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
         <v>793</v>
       </c>
-      <c r="B422" s="1" t="s">
+      <c r="B425" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="C422" s="1" t="s">
+      <c r="C425" s="1" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A423" t="s">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
         <v>795</v>
       </c>
-      <c r="B423" s="1" t="s">
+      <c r="B426" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C423" s="1" t="s">
+      <c r="C426" s="1" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A424" s="15" t="s">
+    <row r="427" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A427" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B424" s="16" t="s">
+      <c r="B427" s="16" t="s">
         <v>801</v>
       </c>
-      <c r="C424" s="13" t="s">
+      <c r="C427" s="13" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A425" s="17" t="s">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B425" s="13" t="s">
+      <c r="B428" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C425" s="13" t="s">
+      <c r="C428" s="13" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A426" s="1" t="s">
+    <row r="429" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B426" s="1" t="s">
+      <c r="B429" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="C426" s="1" t="s">
+      <c r="C429" s="1" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A427" s="1" t="s">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="B427" s="1" t="s">
+      <c r="B432" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="C427" s="1" t="s">
+      <c r="C432" s="1" t="s">
         <v>805</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="C433" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B54" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B57" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B58" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B61" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B86" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B157" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B193" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B273" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B288" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B323" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B324" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B328" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B330" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B332" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B333" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B334" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B336" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B341" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B342" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B344" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B345" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B346" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B347" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B348" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B349" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B350" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B353" r:id="rId27" display="https://docs.google.com/document/d/1M2hEx1RDrhEmfX60yWlWIBdylB3OnVphXTS96F-768c/edit" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="B354" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B355" r:id="rId29" display="https://drive.google.com/drive/u/0/folders/12tlYLXNJ23693OnyjLWCuHIWp5vheWkM" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B356" r:id="rId30" display="https://www.hackerrank.com/dashboard" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B357" r:id="rId31" display="https://github.com/chrisjkeenan/PythonBootcamp" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B358" r:id="rId32" display="https://stackoverflow.com/" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B359" r:id="rId33" display="https://codeforces.com/" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B360" r:id="rId34" display="https://www.hackerearth.com/practice/" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B361" r:id="rId35" display="https://www.hackerearth.com/practice/" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="B362" r:id="rId36" display="https://www.hackerearth.com/codearena/" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B363" r:id="rId37" display="https://www.codechef.com/" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B364" r:id="rId38" display="https://internshala.com/fresher-jobs/matching-preferences" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B365" r:id="rId39" display="https://www.interviewbit.com/practice/" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B366" r:id="rId40" display="https://www.hackathon.io/events" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B367" r:id="rId41" display="https://leetcode.com/explore/" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B368" r:id="rId42" display="https://practice.geeksforgeeks.org/home/" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B369" r:id="rId43" display="https://www.educative.io/" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B370" r:id="rId44" display="https://www.geeksforgeeks.org/" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B371" r:id="rId45" display="https://www.pepcoding.com/resources/online-java-foundation/getting-started/take-input-official/video" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B372" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="B373" r:id="rId47" display="https://www.pepcoding.com/resources/" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B374" r:id="rId48" display="https://www.hackerrank.com/interview/virtusa/challenges" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B375" r:id="rId49" display="https://www.udemy.com/" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B376" r:id="rId50" display="https://www.udacity.com/" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B377" r:id="rId51" display="https://docs.microsoft.com/en-us/learn/modules/intro-to-azure-fundamentals/introduction" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B378" r:id="rId52" location="/" display="https://nextstep.tcs.com/campus/ - /" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B379" r:id="rId53" display="https://www.onlinegdb.com/" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B380" r:id="rId54" location="/s/feed" display="https://app.joinsuperset.com/ - /s/feed" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="B381" r:id="rId55" display="https://www.theforage.com/dashboard?ref=s8uq9k2DwmytK2qhg" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B382" r:id="rId56" display="https://elearning.iirs.gov.in/edusatregistration/studentstatus" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="B383" r:id="rId57" display="https://app.upraised.co/embark/home" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B384" r:id="rId58" location="content" display="https://events.withgoogle.com/30daysofgooglecloud/ - content" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B385" r:id="rId59" display="https://developers.google.com/machine-learning/crash-course" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="B386" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B387" r:id="rId61" display="https://www.tutorialspoint.com/compile_java_online.php" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B388" r:id="rId62" display="https://docs.oracle.com/javase/tutorial/java/javaOO/index.html" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B389" r:id="rId63" display="https://docs.oracle.com/en/java/javase/16/docs/api/java.base/java/util/HashSet.html" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="B390" r:id="rId64" display="https://www.alt-codes.net/smiley_alt_codes.php" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B391" r:id="rId65" display="https://usersnap.com/blog/atom-tips-shortcuts/" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B392" r:id="rId66" display="https://musicforprogramming.net/latest/" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B393" r:id="rId67" location="/s/feed" display="https://app.joinsuperset.com/ - /s/feed" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B394" r:id="rId68" display="https://manipal-adapt.in.capgemini.com/" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B395" r:id="rId69" display="https://jumpstartatos.percipio.com/" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B396" r:id="rId70" display="https://www.hackerrank.com/kpb303125" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B397" r:id="rId71" display="https://tapacademy.thinkific.com/enrollments" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B398" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="B399" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B400" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B401" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B403" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B404" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B405" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="B406" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B56" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B59" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B60" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B63" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B88" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B159" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B196" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B276" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B291" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B326" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B327" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B331" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B333" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="B335" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B336" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B337" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B339" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B344" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B345" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B347" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B348" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B349" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B350" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B351" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B352" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B353" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B356" r:id="rId27" display="https://docs.google.com/document/d/1M2hEx1RDrhEmfX60yWlWIBdylB3OnVphXTS96F-768c/edit" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="B357" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B358" r:id="rId29" display="https://drive.google.com/drive/u/0/folders/12tlYLXNJ23693OnyjLWCuHIWp5vheWkM" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B359" r:id="rId30" display="https://www.hackerrank.com/dashboard" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="B360" r:id="rId31" display="https://github.com/chrisjkeenan/PythonBootcamp" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B361" r:id="rId32" display="https://stackoverflow.com/" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B362" r:id="rId33" display="https://codeforces.com/" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B363" r:id="rId34" display="https://www.hackerearth.com/practice/" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B364" r:id="rId35" display="https://www.hackerearth.com/practice/" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="B365" r:id="rId36" display="https://www.hackerearth.com/codearena/" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B366" r:id="rId37" display="https://www.codechef.com/" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B367" r:id="rId38" display="https://internshala.com/fresher-jobs/matching-preferences" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B368" r:id="rId39" display="https://www.interviewbit.com/practice/" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B369" r:id="rId40" display="https://www.hackathon.io/events" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B370" r:id="rId41" display="https://leetcode.com/explore/" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B371" r:id="rId42" display="https://practice.geeksforgeeks.org/home/" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B372" r:id="rId43" display="https://www.educative.io/" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B373" r:id="rId44" display="https://www.geeksforgeeks.org/" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B374" r:id="rId45" display="https://www.pepcoding.com/resources/online-java-foundation/getting-started/take-input-official/video" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B375" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="B376" r:id="rId47" display="https://www.pepcoding.com/resources/" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B377" r:id="rId48" display="https://www.hackerrank.com/interview/virtusa/challenges" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B378" r:id="rId49" display="https://www.udemy.com/" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B379" r:id="rId50" display="https://www.udacity.com/" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B380" r:id="rId51" display="https://docs.microsoft.com/en-us/learn/modules/intro-to-azure-fundamentals/introduction" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B381" r:id="rId52" location="/" display="https://nextstep.tcs.com/campus/ - /" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B382" r:id="rId53" display="https://www.onlinegdb.com/" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B383" r:id="rId54" location="/s/feed" display="https://app.joinsuperset.com/ - /s/feed" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="B384" r:id="rId55" display="https://www.theforage.com/dashboard?ref=s8uq9k2DwmytK2qhg" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="B385" r:id="rId56" display="https://elearning.iirs.gov.in/edusatregistration/studentstatus" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="B386" r:id="rId57" display="https://app.upraised.co/embark/home" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="B387" r:id="rId58" location="content" display="https://events.withgoogle.com/30daysofgooglecloud/ - content" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B388" r:id="rId59" display="https://developers.google.com/machine-learning/crash-course" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="B389" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B390" r:id="rId61" display="https://www.tutorialspoint.com/compile_java_online.php" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B391" r:id="rId62" display="https://docs.oracle.com/javase/tutorial/java/javaOO/index.html" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="B392" r:id="rId63" display="https://docs.oracle.com/en/java/javase/16/docs/api/java.base/java/util/HashSet.html" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="B393" r:id="rId64" display="https://www.alt-codes.net/smiley_alt_codes.php" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B394" r:id="rId65" display="https://usersnap.com/blog/atom-tips-shortcuts/" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="B395" r:id="rId66" display="https://musicforprogramming.net/latest/" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B396" r:id="rId67" location="/s/feed" display="https://app.joinsuperset.com/ - /s/feed" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="B397" r:id="rId68" display="https://manipal-adapt.in.capgemini.com/" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="B398" r:id="rId69" display="https://jumpstartatos.percipio.com/" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B399" r:id="rId70" display="https://www.hackerrank.com/kpb303125" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="B400" r:id="rId71" display="https://tapacademy.thinkific.com/enrollments" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="B401" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="B402" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="B403" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="B404" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B406" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="B407" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="B408" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="B409" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/bookmarks.xlsx
+++ b/bookmarks.xlsx
@@ -6,22 +6,22 @@
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_69C3906C_70E3_4709_B001_22E5206BF726_.wvu.FilterData">Sheet1!$A$1:$D$189</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_840AC4D9_05FC_4DF1_A02E_909E79011D7E_.wvu.FilterData">Sheet1!$A$1:$D$190</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{69C3906C-70E3-4709-B001-22E5206BF726}" name="Table3 filter view"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{840AC4D9-05FC-4DF1-A02E-909E79011D7E}" name="Table3 filter view"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TXOAGtL63lBzHQjVvGO4KfUHBwVKvZ+6UkkfTRh2Mw0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="WaK5mABwvImRjwfTxMcTtItxoSqI67xcSlrue2MmZvk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="837">
   <si>
     <t>title</t>
   </si>
@@ -536,7 +536,7 @@
     <t>IND POST SB</t>
   </si>
   <si>
-    <t>https://ebanking.indiapost.gov.in/</t>
+    <t>https://www.indiapost.gov.in/banking-services/netbanking</t>
   </si>
   <si>
     <t>SC BANK</t>
@@ -1035,6 +1035,12 @@
   </si>
   <si>
     <t>https://goldrate.com/en/gold/india</t>
+  </si>
+  <si>
+    <t>INVESTOR GAIN IPO GMP</t>
+  </si>
+  <si>
+    <t>https://www.investorgain.com/</t>
   </si>
   <si>
     <t>EasyGo Bus</t>
@@ -2532,7 +2538,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -2558,7 +2564,19 @@
     <font>
       <u/>
       <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -2582,6 +2600,12 @@
       <u/>
       <sz val="11.0"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -2717,7 +2741,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2733,10 +2757,13 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2748,10 +2775,13 @@
     <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2763,39 +2793,42 @@
     <xf borderId="2" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2882,7 +2915,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D189" displayName="Table3" name="Table3" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D190" displayName="Table3" name="Table3" id="1">
   <tableColumns count="4">
     <tableColumn name="title" id="1"/>
     <tableColumn name="url" id="2"/>
@@ -3141,10 +3174,10 @@
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="4"/>
@@ -3178,7 +3211,7 @@
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4"/>
@@ -3212,7 +3245,7 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="4"/>
@@ -3246,7 +3279,7 @@
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="4"/>
@@ -3280,7 +3313,7 @@
       <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="4"/>
@@ -3314,7 +3347,7 @@
       <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="4"/>
@@ -3348,7 +3381,7 @@
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="4"/>
@@ -3382,7 +3415,7 @@
       <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="4"/>
@@ -3416,7 +3449,7 @@
       <c r="B10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="4"/>
@@ -3450,7 +3483,7 @@
       <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="4"/>
@@ -3484,7 +3517,7 @@
       <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="4"/>
@@ -3518,7 +3551,7 @@
       <c r="B13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="4"/>
@@ -3552,7 +3585,7 @@
       <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="4"/>
@@ -3586,7 +3619,7 @@
       <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="4"/>
@@ -3620,7 +3653,7 @@
       <c r="B16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="4"/>
@@ -3654,7 +3687,7 @@
       <c r="B17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="4"/>
@@ -3688,7 +3721,7 @@
       <c r="B18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="4"/>
@@ -3722,7 +3755,7 @@
       <c r="B19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="4"/>
@@ -3756,7 +3789,7 @@
       <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="4"/>
@@ -3790,7 +3823,7 @@
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="4"/>
@@ -3824,7 +3857,7 @@
       <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="4"/>
@@ -3858,7 +3891,7 @@
       <c r="B23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="4"/>
@@ -3892,7 +3925,7 @@
       <c r="B24" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="4"/>
@@ -3926,7 +3959,7 @@
       <c r="B25" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="4"/>
@@ -3960,7 +3993,7 @@
       <c r="B26" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="4"/>
@@ -3994,7 +4027,7 @@
       <c r="B27" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="4"/>
@@ -4028,7 +4061,7 @@
       <c r="B28" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="4"/>
@@ -4062,7 +4095,7 @@
       <c r="B29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="4"/>
@@ -4096,7 +4129,7 @@
       <c r="B30" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="4"/>
@@ -4130,7 +4163,7 @@
       <c r="B31" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="4"/>
@@ -4164,7 +4197,7 @@
       <c r="B32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="4"/>
@@ -4198,7 +4231,7 @@
       <c r="B33" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="4"/>
@@ -4232,7 +4265,7 @@
       <c r="B34" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="4"/>
@@ -4266,7 +4299,7 @@
       <c r="B35" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="4"/>
@@ -4300,7 +4333,7 @@
       <c r="B36" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="4"/>
@@ -4334,7 +4367,7 @@
       <c r="B37" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="4"/>
@@ -4424,7 +4457,7 @@
       <c r="B40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="4"/>
@@ -4458,7 +4491,7 @@
       <c r="B41" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="4"/>
@@ -4492,7 +4525,7 @@
       <c r="B42" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="4"/>
@@ -4526,7 +4559,7 @@
       <c r="B43" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="4"/>
@@ -4560,7 +4593,7 @@
       <c r="B44" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="4"/>
@@ -4594,7 +4627,7 @@
       <c r="B45" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="4"/>
@@ -4628,7 +4661,7 @@
       <c r="B46" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="4"/>
@@ -4662,7 +4695,7 @@
       <c r="B47" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D47" s="4"/>
@@ -4696,7 +4729,7 @@
       <c r="B48" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="4"/>
@@ -4730,7 +4763,7 @@
       <c r="B49" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="4"/>
@@ -4764,7 +4797,7 @@
       <c r="B50" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="4"/>
@@ -4798,7 +4831,7 @@
       <c r="B51" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D51" s="4"/>
@@ -4832,7 +4865,7 @@
       <c r="B52" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="4"/>
@@ -4866,7 +4899,7 @@
       <c r="B53" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D53" s="4"/>
@@ -4900,7 +4933,7 @@
       <c r="B54" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D54" s="4"/>
@@ -4934,7 +4967,7 @@
       <c r="B55" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="4"/>
@@ -4965,10 +4998,10 @@
       <c r="A56" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="4"/>
@@ -5002,7 +5035,7 @@
       <c r="B57" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="4"/>
@@ -5036,7 +5069,7 @@
       <c r="B58" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="4"/>
@@ -5067,10 +5100,10 @@
       <c r="A59" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="4"/>
@@ -5101,10 +5134,10 @@
       <c r="A60" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="4"/>
@@ -5135,10 +5168,10 @@
       <c r="A61" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="4"/>
@@ -5169,10 +5202,10 @@
       <c r="A62" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="4"/>
@@ -5203,10 +5236,10 @@
       <c r="A63" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D63" s="4"/>
@@ -5237,10 +5270,10 @@
       <c r="A64" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="4"/>
@@ -5271,10 +5304,10 @@
       <c r="A65" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D65" s="4"/>
@@ -5308,7 +5341,7 @@
       <c r="B66" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D66" s="4"/>
@@ -5342,7 +5375,7 @@
       <c r="B67" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D67" s="4"/>
@@ -5376,7 +5409,7 @@
       <c r="B68" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D68" s="4"/>
@@ -5410,7 +5443,7 @@
       <c r="B69" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D69" s="4"/>
@@ -5444,7 +5477,7 @@
       <c r="B70" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D70" s="4"/>
@@ -5478,7 +5511,7 @@
       <c r="B71" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D71" s="4"/>
@@ -5512,7 +5545,7 @@
       <c r="B72" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D72" s="4"/>
@@ -5546,7 +5579,7 @@
       <c r="B73" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D73" s="4"/>
@@ -5580,7 +5613,7 @@
       <c r="B74" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="9" t="s">
         <v>148</v>
       </c>
       <c r="D74" s="4"/>
@@ -5614,7 +5647,7 @@
       <c r="B75" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="9" t="s">
         <v>148</v>
       </c>
       <c r="D75" s="4"/>
@@ -5648,7 +5681,7 @@
       <c r="B76" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="9" t="s">
         <v>148</v>
       </c>
       <c r="D76" s="4"/>
@@ -5682,7 +5715,7 @@
       <c r="B77" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="9" t="s">
         <v>148</v>
       </c>
       <c r="D77" s="4"/>
@@ -5716,7 +5749,7 @@
       <c r="B78" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="9" t="s">
         <v>148</v>
       </c>
       <c r="D78" s="4"/>
@@ -5750,7 +5783,7 @@
       <c r="B79" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D79" s="4"/>
@@ -5784,7 +5817,7 @@
       <c r="B80" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D80" s="4"/>
@@ -5818,7 +5851,7 @@
       <c r="B81" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D81" s="4"/>
@@ -5852,7 +5885,7 @@
       <c r="B82" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D82" s="4"/>
@@ -5886,7 +5919,7 @@
       <c r="B83" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="C83" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D83" s="4"/>
@@ -5920,7 +5953,7 @@
       <c r="B84" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D84" s="4"/>
@@ -5951,10 +5984,10 @@
       <c r="A85" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D85" s="4"/>
@@ -5988,7 +6021,7 @@
       <c r="B86" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" s="10" t="s">
         <v>159</v>
       </c>
       <c r="D86" s="4"/>
@@ -6018,7 +6051,7 @@
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
-      <c r="C87" s="9"/>
+      <c r="C87" s="10"/>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -6047,13 +6080,13 @@
       <c r="A88" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D88" s="6"/>
+      <c r="D88" s="7"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -6078,16 +6111,16 @@
       <c r="Z88" s="3"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D89" s="6"/>
+      <c r="D89" s="7"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -6118,7 +6151,7 @@
       <c r="B90" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D90" s="4"/>
@@ -6152,7 +6185,7 @@
       <c r="B91" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D91" s="4"/>
@@ -6186,7 +6219,7 @@
       <c r="B92" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D92" s="4"/>
@@ -6220,7 +6253,7 @@
       <c r="B93" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D93" s="4"/>
@@ -6254,7 +6287,7 @@
       <c r="B94" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D94" s="4"/>
@@ -6288,7 +6321,7 @@
       <c r="B95" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D95" s="4"/>
@@ -6322,7 +6355,7 @@
       <c r="B96" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D96" s="4"/>
@@ -6356,7 +6389,7 @@
       <c r="B97" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D97" s="4"/>
@@ -6390,7 +6423,7 @@
       <c r="B98" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D98" s="4"/>
@@ -6424,7 +6457,7 @@
       <c r="B99" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D99" s="4"/>
@@ -6458,7 +6491,7 @@
       <c r="B100" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D100" s="4"/>
@@ -6492,7 +6525,7 @@
       <c r="B101" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D101" s="4"/>
@@ -6526,7 +6559,7 @@
       <c r="B102" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D102" s="4"/>
@@ -6560,7 +6593,7 @@
       <c r="B103" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D103" s="4"/>
@@ -6594,7 +6627,7 @@
       <c r="B104" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D104" s="4"/>
@@ -6628,7 +6661,7 @@
       <c r="B105" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C105" s="12" t="s">
+      <c r="C105" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D105" s="4"/>
@@ -6662,7 +6695,7 @@
       <c r="B106" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D106" s="4"/>
@@ -6696,7 +6729,7 @@
       <c r="B107" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D107" s="4"/>
@@ -6730,7 +6763,7 @@
       <c r="B108" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D108" s="4"/>
@@ -6764,7 +6797,7 @@
       <c r="B109" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D109" s="4"/>
@@ -6916,7 +6949,7 @@
       <c r="B114" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D114" s="4"/>
@@ -6950,7 +6983,7 @@
       <c r="B115" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D115" s="4"/>
@@ -6984,7 +7017,7 @@
       <c r="B116" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D116" s="4"/>
@@ -7018,7 +7051,7 @@
       <c r="B117" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D117" s="4"/>
@@ -7052,7 +7085,7 @@
       <c r="B118" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C118" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D118" s="4"/>
@@ -7086,7 +7119,7 @@
       <c r="B119" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D119" s="4"/>
@@ -7120,7 +7153,7 @@
       <c r="B120" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C120" s="13" t="s">
+      <c r="C120" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D120" s="4"/>
@@ -7154,7 +7187,7 @@
       <c r="B121" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D121" s="4"/>
@@ -7188,7 +7221,7 @@
       <c r="B122" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D122" s="4"/>
@@ -7222,7 +7255,7 @@
       <c r="B123" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D123" s="4"/>
@@ -7256,7 +7289,7 @@
       <c r="B124" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D124" s="4"/>
@@ -7290,7 +7323,7 @@
       <c r="B125" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D125" s="4"/>
@@ -7324,7 +7357,7 @@
       <c r="B126" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D126" s="4"/>
@@ -7358,7 +7391,7 @@
       <c r="B127" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C127" s="14" t="s">
+      <c r="C127" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D127" s="4"/>
@@ -7392,7 +7425,7 @@
       <c r="B128" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D128" s="4"/>
@@ -7426,7 +7459,7 @@
       <c r="B129" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C129" s="14" t="s">
+      <c r="C129" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D129" s="4"/>
@@ -7460,7 +7493,7 @@
       <c r="B130" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C130" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D130" s="4"/>
@@ -7494,7 +7527,7 @@
       <c r="B131" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C131" s="14" t="s">
+      <c r="C131" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D131" s="4"/>
@@ -7528,7 +7561,7 @@
       <c r="B132" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C132" s="14" t="s">
+      <c r="C132" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D132" s="4"/>
@@ -7562,7 +7595,7 @@
       <c r="B133" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C133" s="14" t="s">
+      <c r="C133" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D133" s="4"/>
@@ -7596,7 +7629,7 @@
       <c r="B134" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C134" s="14" t="s">
+      <c r="C134" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D134" s="4"/>
@@ -7630,7 +7663,7 @@
       <c r="B135" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C135" s="14" t="s">
+      <c r="C135" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D135" s="4"/>
@@ -7664,7 +7697,7 @@
       <c r="B136" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C136" s="14" t="s">
+      <c r="C136" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D136" s="4"/>
@@ -7698,7 +7731,7 @@
       <c r="B137" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C137" s="14" t="s">
+      <c r="C137" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D137" s="4"/>
@@ -7732,7 +7765,7 @@
       <c r="B138" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C138" s="14" t="s">
+      <c r="C138" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D138" s="4"/>
@@ -7766,7 +7799,7 @@
       <c r="B139" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C139" s="14" t="s">
+      <c r="C139" s="16" t="s">
         <v>247</v>
       </c>
       <c r="D139" s="4"/>
@@ -8471,7 +8504,7 @@
       <c r="A160" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B160" s="7" t="s">
         <v>319</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -8774,14 +8807,14 @@
       <c r="Z168" s="3"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="11" t="s">
         <v>339</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="3"/>
@@ -8808,9 +8841,15 @@
       <c r="Z169" s="3"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
+      <c r="A170" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>342</v>
+      </c>
       <c r="D170" s="4"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
@@ -8836,15 +8875,9 @@
       <c r="Z170" s="3"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>340</v>
-      </c>
+      <c r="A171" s="4"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
@@ -8877,7 +8910,7 @@
         <v>344</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="3"/>
@@ -8903,15 +8936,15 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" ht="28.5" customHeight="1">
+    <row r="173" ht="14.25" customHeight="1">
       <c r="A173" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B173" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="C173" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="3"/>
@@ -8939,13 +8972,13 @@
     </row>
     <row r="174" ht="28.5" customHeight="1">
       <c r="A174" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B174" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="C174" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="3"/>
@@ -8979,7 +9012,7 @@
         <v>352</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="3"/>
@@ -9013,7 +9046,7 @@
         <v>354</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="3"/>
@@ -9047,7 +9080,7 @@
         <v>356</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="3"/>
@@ -9081,7 +9114,7 @@
         <v>358</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="3"/>
@@ -9115,7 +9148,7 @@
         <v>360</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="3"/>
@@ -9149,7 +9182,7 @@
         <v>362</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="3"/>
@@ -9175,7 +9208,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" ht="28.5" customHeight="1">
       <c r="A181" s="4" t="s">
         <v>363</v>
       </c>
@@ -9183,7 +9216,7 @@
         <v>364</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="3"/>
@@ -9217,7 +9250,7 @@
         <v>366</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="3"/>
@@ -9245,13 +9278,13 @@
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B183" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="C183" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="3"/>
@@ -9285,7 +9318,7 @@
         <v>371</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="3"/>
@@ -9312,14 +9345,14 @@
       <c r="Z184" s="3"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
-      <c r="A185" s="15" t="s">
+      <c r="A185" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="C185" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="3"/>
@@ -9346,14 +9379,14 @@
       <c r="Z185" s="3"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="15" t="s">
+      <c r="A186" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B186" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="C186" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="3"/>
@@ -9380,14 +9413,14 @@
       <c r="Z186" s="3"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="15" t="s">
+      <c r="A187" s="17" t="s">
         <v>378</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>379</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="3"/>
@@ -9414,14 +9447,14 @@
       <c r="Z187" s="3"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="A188" s="15" t="s">
+      <c r="A188" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B188" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="C188" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="3"/>
@@ -9448,14 +9481,14 @@
       <c r="Z188" s="3"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="15" t="s">
+      <c r="A189" s="17" t="s">
         <v>383</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C189" s="16" t="s">
-        <v>380</v>
+      <c r="C189" s="4" t="s">
+        <v>382</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="3"/>
@@ -9482,10 +9515,16 @@
       <c r="Z189" s="3"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
+      <c r="A190" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C190" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="D190" s="4"/>
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
@@ -9510,15 +9549,9 @@
       <c r="Z190" s="3"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c r="A191" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>387</v>
-      </c>
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
@@ -9544,14 +9577,14 @@
       <c r="Z191" s="3"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c r="A192" s="17" t="s">
+      <c r="A192" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B192" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="C192" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="C192" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -9578,14 +9611,14 @@
       <c r="Z192" s="3"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="17" t="s">
+      <c r="A193" s="19" t="s">
         <v>390</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>391</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -9612,14 +9645,14 @@
       <c r="Z193" s="3"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="17" t="s">
+      <c r="A194" s="19" t="s">
         <v>392</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>393</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -9646,14 +9679,14 @@
       <c r="Z194" s="3"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
-      <c r="A195" s="17" t="s">
+      <c r="A195" s="19" t="s">
         <v>394</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>395</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -9680,14 +9713,14 @@
       <c r="Z195" s="3"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c r="A196" s="17" t="s">
+      <c r="A196" s="19" t="s">
         <v>396</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>397</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -9714,14 +9747,14 @@
       <c r="Z196" s="3"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="17" t="s">
+      <c r="A197" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="B197" s="18" t="s">
+      <c r="B197" s="3" t="s">
         <v>399</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -9747,15 +9780,15 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" ht="28.5" customHeight="1">
-      <c r="A198" s="17" t="s">
+    <row r="198" ht="14.25" customHeight="1">
+      <c r="A198" s="19" t="s">
         <v>400</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="20" t="s">
         <v>401</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -9781,10 +9814,16 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
-      <c r="C199" s="3"/>
+    <row r="199" ht="28.5" customHeight="1">
+      <c r="A199" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
@@ -9810,15 +9849,9 @@
       <c r="Z199" s="3"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C200" s="3" t="s">
-        <v>404</v>
-      </c>
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
@@ -9844,9 +9877,15 @@
       <c r="Z200" s="3"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
-      <c r="C201" s="3"/>
+      <c r="A201" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>406</v>
+      </c>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
@@ -9872,15 +9911,9 @@
       <c r="Z201" s="3"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>407</v>
-      </c>
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
@@ -9906,14 +9939,14 @@
       <c r="Z202" s="3"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
-      <c r="A203" s="17" t="s">
+      <c r="A203" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="B203" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="C203" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C203" s="19" t="s">
-        <v>6</v>
       </c>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -9940,13 +9973,13 @@
       <c r="Z203" s="3"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="17" t="s">
+      <c r="A204" s="19" t="s">
         <v>410</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C204" s="19" t="s">
+      <c r="C204" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D204" s="3"/>
@@ -9974,13 +10007,13 @@
       <c r="Z204" s="3"/>
     </row>
     <row r="205" ht="14.25" customHeight="1">
-      <c r="A205" s="17" t="s">
+      <c r="A205" s="19" t="s">
         <v>412</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C205" s="19" t="s">
+      <c r="C205" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D205" s="3"/>
@@ -10008,13 +10041,13 @@
       <c r="Z205" s="3"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
-      <c r="A206" s="17" t="s">
+      <c r="A206" s="19" t="s">
         <v>414</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C206" s="19" t="s">
+      <c r="C206" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D206" s="3"/>
@@ -10042,13 +10075,13 @@
       <c r="Z206" s="3"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
-      <c r="A207" s="17" t="s">
+      <c r="A207" s="19" t="s">
         <v>416</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C207" s="19" t="s">
+      <c r="C207" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D207" s="3"/>
@@ -10076,13 +10109,13 @@
       <c r="Z207" s="3"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c r="A208" s="3" t="s">
+      <c r="A208" s="19" t="s">
         <v>418</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C208" s="19" t="s">
+      <c r="C208" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D208" s="3"/>
@@ -10110,13 +10143,13 @@
       <c r="Z208" s="3"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="17" t="s">
+      <c r="A209" s="3" t="s">
         <v>420</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C209" s="19" t="s">
+      <c r="C209" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D209" s="3"/>
@@ -10144,13 +10177,13 @@
       <c r="Z209" s="3"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="17" t="s">
+      <c r="A210" s="19" t="s">
         <v>422</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C210" s="19" t="s">
+      <c r="C210" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D210" s="3"/>
@@ -10178,13 +10211,13 @@
       <c r="Z210" s="3"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="17" t="s">
+      <c r="A211" s="19" t="s">
         <v>424</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C211" s="19" t="s">
+      <c r="C211" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D211" s="3"/>
@@ -10212,13 +10245,13 @@
       <c r="Z211" s="3"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="17" t="s">
+      <c r="A212" s="19" t="s">
         <v>426</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="C212" s="19" t="s">
+      <c r="C212" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D212" s="3"/>
@@ -10246,13 +10279,13 @@
       <c r="Z212" s="3"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="3" t="s">
+      <c r="A213" s="19" t="s">
         <v>428</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="C213" s="19" t="s">
+      <c r="C213" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D213" s="3"/>
@@ -10280,14 +10313,14 @@
       <c r="Z213" s="3"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="17" t="s">
+      <c r="A214" s="3" t="s">
         <v>430</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>432</v>
+      <c r="C214" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -10314,14 +10347,14 @@
       <c r="Z214" s="3"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
-      <c r="A215" s="17" t="s">
+      <c r="A215" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="B215" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="C215" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="C215" s="19" t="s">
-        <v>6</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -10348,13 +10381,13 @@
       <c r="Z215" s="3"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
-      <c r="A216" s="17" t="s">
+      <c r="A216" s="19" t="s">
         <v>435</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C216" s="19" t="s">
+      <c r="C216" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D216" s="3"/>
@@ -10382,13 +10415,13 @@
       <c r="Z216" s="3"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c r="A217" s="17" t="s">
+      <c r="A217" s="19" t="s">
         <v>437</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C217" s="19" t="s">
+      <c r="C217" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D217" s="3"/>
@@ -10416,14 +10449,14 @@
       <c r="Z217" s="3"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c r="A218" s="17" t="s">
+      <c r="A218" s="19" t="s">
         <v>439</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>441</v>
+      <c r="C218" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -10450,14 +10483,14 @@
       <c r="Z218" s="3"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c r="A219" s="17" t="s">
+      <c r="A219" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="B219" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="C219" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -10484,14 +10517,14 @@
       <c r="Z219" s="3"/>
     </row>
     <row r="220" ht="14.25" customHeight="1">
-      <c r="A220" s="17" t="s">
+      <c r="A220" s="19" t="s">
         <v>444</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>445</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -10518,14 +10551,14 @@
       <c r="Z220" s="3"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
-      <c r="A221" s="17" t="s">
+      <c r="A221" s="19" t="s">
         <v>446</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>447</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -10552,14 +10585,14 @@
       <c r="Z221" s="3"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="17" t="s">
+      <c r="A222" s="19" t="s">
         <v>448</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>449</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -10586,14 +10619,14 @@
       <c r="Z222" s="3"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="17" t="s">
+      <c r="A223" s="19" t="s">
         <v>450</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>451</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -10620,14 +10653,14 @@
       <c r="Z223" s="3"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
-      <c r="A224" s="17" t="s">
+      <c r="A224" s="19" t="s">
         <v>452</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>453</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -10654,9 +10687,15 @@
       <c r="Z224" s="3"/>
     </row>
     <row r="225" ht="14.25" customHeight="1">
-      <c r="A225" s="3"/>
-      <c r="B225" s="3"/>
-      <c r="C225" s="3"/>
+      <c r="A225" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>443</v>
+      </c>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
@@ -10682,15 +10721,9 @@
       <c r="Z225" s="3"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>456</v>
-      </c>
+      <c r="A226" s="3"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
@@ -10716,14 +10749,14 @@
       <c r="Z226" s="3"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
-      <c r="A227" s="17" t="s">
+      <c r="A227" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="B227" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="C227" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -10750,14 +10783,14 @@
       <c r="Z227" s="3"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c r="A228" s="17" t="s">
+      <c r="A228" s="19" t="s">
         <v>459</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>460</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -10784,14 +10817,14 @@
       <c r="Z228" s="3"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="17" t="s">
+      <c r="A229" s="19" t="s">
         <v>461</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>462</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -10818,14 +10851,14 @@
       <c r="Z229" s="3"/>
     </row>
     <row r="230" ht="14.25" customHeight="1">
-      <c r="A230" s="17" t="s">
+      <c r="A230" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="B230" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="C230" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -10852,14 +10885,14 @@
       <c r="Z230" s="3"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
-      <c r="A231" s="17" t="s">
+      <c r="A231" s="19" t="s">
         <v>466</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>467</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -10886,14 +10919,14 @@
       <c r="Z231" s="3"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c r="A232" s="17" t="s">
+      <c r="A232" s="19" t="s">
         <v>468</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>469</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -10920,14 +10953,14 @@
       <c r="Z232" s="3"/>
     </row>
     <row r="233" ht="14.25" customHeight="1">
-      <c r="A233" s="17" t="s">
+      <c r="A233" s="19" t="s">
         <v>470</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>471</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -10953,15 +10986,15 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
     </row>
-    <row r="234" ht="28.5" customHeight="1">
-      <c r="A234" s="17" t="s">
+    <row r="234" ht="14.25" customHeight="1">
+      <c r="A234" s="19" t="s">
         <v>472</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>473</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -10987,15 +11020,15 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
-      <c r="A235" s="17" t="s">
+    <row r="235" ht="28.5" customHeight="1">
+      <c r="A235" s="19" t="s">
         <v>474</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>475</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -11022,14 +11055,14 @@
       <c r="Z235" s="3"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="17" t="s">
+      <c r="A236" s="19" t="s">
         <v>476</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>477</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -11056,14 +11089,14 @@
       <c r="Z236" s="3"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
-      <c r="A237" s="17" t="s">
+      <c r="A237" s="19" t="s">
         <v>478</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>479</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -11090,14 +11123,14 @@
       <c r="Z237" s="3"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="17" t="s">
+      <c r="A238" s="19" t="s">
         <v>480</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>481</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -11124,14 +11157,14 @@
       <c r="Z238" s="3"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c r="A239" s="17" t="s">
+      <c r="A239" s="19" t="s">
         <v>482</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>483</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -11158,14 +11191,14 @@
       <c r="Z239" s="3"/>
     </row>
     <row r="240" ht="14.25" customHeight="1">
-      <c r="A240" s="17" t="s">
+      <c r="A240" s="19" t="s">
         <v>484</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>485</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -11192,14 +11225,14 @@
       <c r="Z240" s="3"/>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c r="A241" s="17" t="s">
+      <c r="A241" s="19" t="s">
         <v>486</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>487</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -11226,14 +11259,14 @@
       <c r="Z241" s="3"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
-      <c r="A242" s="17" t="s">
+      <c r="A242" s="19" t="s">
         <v>488</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>489</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -11260,14 +11293,14 @@
       <c r="Z242" s="3"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="17" t="s">
+      <c r="A243" s="19" t="s">
         <v>490</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>491</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -11294,14 +11327,14 @@
       <c r="Z243" s="3"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="17" t="s">
+      <c r="A244" s="19" t="s">
         <v>492</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>493</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -11328,14 +11361,14 @@
       <c r="Z244" s="3"/>
     </row>
     <row r="245" ht="14.25" customHeight="1">
-      <c r="A245" s="17" t="s">
+      <c r="A245" s="19" t="s">
         <v>494</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>495</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -11362,14 +11395,14 @@
       <c r="Z245" s="3"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
-      <c r="A246" s="17" t="s">
+      <c r="A246" s="19" t="s">
         <v>496</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>497</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -11396,14 +11429,14 @@
       <c r="Z246" s="3"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="17" t="s">
+      <c r="A247" s="19" t="s">
         <v>498</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>499</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -11430,14 +11463,14 @@
       <c r="Z247" s="3"/>
     </row>
     <row r="248" ht="14.25" customHeight="1">
-      <c r="A248" s="17" t="s">
+      <c r="A248" s="19" t="s">
         <v>500</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>501</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -11464,14 +11497,14 @@
       <c r="Z248" s="3"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="17" t="s">
+      <c r="A249" s="19" t="s">
         <v>502</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>503</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -11498,14 +11531,14 @@
       <c r="Z249" s="3"/>
     </row>
     <row r="250" ht="14.25" customHeight="1">
-      <c r="A250" s="17" t="s">
+      <c r="A250" s="19" t="s">
         <v>504</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>505</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -11532,14 +11565,14 @@
       <c r="Z250" s="3"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="17" t="s">
+      <c r="A251" s="19" t="s">
         <v>506</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>507</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -11566,14 +11599,14 @@
       <c r="Z251" s="3"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="17" t="s">
+      <c r="A252" s="19" t="s">
         <v>508</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>509</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -11600,14 +11633,14 @@
       <c r="Z252" s="3"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="17" t="s">
+      <c r="A253" s="19" t="s">
         <v>510</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>511</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -11634,14 +11667,14 @@
       <c r="Z253" s="3"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c r="A254" s="17" t="s">
+      <c r="A254" s="19" t="s">
         <v>512</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>513</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -11668,14 +11701,14 @@
       <c r="Z254" s="3"/>
     </row>
     <row r="255" ht="14.25" customHeight="1">
-      <c r="A255" s="17" t="s">
+      <c r="A255" s="19" t="s">
         <v>514</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>515</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -11702,14 +11735,14 @@
       <c r="Z255" s="3"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="17" t="s">
+      <c r="A256" s="19" t="s">
         <v>516</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>517</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -11736,14 +11769,14 @@
       <c r="Z256" s="3"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
-      <c r="A257" s="17" t="s">
+      <c r="A257" s="19" t="s">
         <v>518</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>519</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -11770,14 +11803,14 @@
       <c r="Z257" s="3"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="17" t="s">
+      <c r="A258" s="19" t="s">
         <v>520</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>521</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -11803,15 +11836,15 @@
       <c r="Y258" s="3"/>
       <c r="Z258" s="3"/>
     </row>
-    <row r="259" ht="28.5" customHeight="1">
-      <c r="A259" s="17" t="s">
+    <row r="259" ht="14.25" customHeight="1">
+      <c r="A259" s="19" t="s">
         <v>522</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>523</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -11837,15 +11870,15 @@
       <c r="Y259" s="3"/>
       <c r="Z259" s="3"/>
     </row>
-    <row r="260" ht="14.25" customHeight="1">
-      <c r="A260" s="17" t="s">
+    <row r="260" ht="28.5" customHeight="1">
+      <c r="A260" s="19" t="s">
         <v>524</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>525</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -11872,14 +11905,14 @@
       <c r="Z260" s="3"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="17" t="s">
+      <c r="A261" s="19" t="s">
         <v>526</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>527</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -11906,14 +11939,14 @@
       <c r="Z261" s="3"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="17" t="s">
+      <c r="A262" s="19" t="s">
         <v>528</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>529</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -11940,14 +11973,14 @@
       <c r="Z262" s="3"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c r="A263" s="17" t="s">
+      <c r="A263" s="19" t="s">
         <v>530</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>531</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -11974,14 +12007,14 @@
       <c r="Z263" s="3"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="17" t="s">
+      <c r="A264" s="19" t="s">
         <v>532</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>533</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -12008,14 +12041,14 @@
       <c r="Z264" s="3"/>
     </row>
     <row r="265" ht="14.25" customHeight="1">
-      <c r="A265" s="17" t="s">
+      <c r="A265" s="19" t="s">
         <v>534</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>535</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -12042,14 +12075,14 @@
       <c r="Z265" s="3"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
-      <c r="A266" s="17" t="s">
+      <c r="A266" s="19" t="s">
         <v>536</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>537</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -12076,14 +12109,14 @@
       <c r="Z266" s="3"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="17" t="s">
+      <c r="A267" s="19" t="s">
         <v>538</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>539</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -12110,14 +12143,14 @@
       <c r="Z267" s="3"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c r="A268" s="17" t="s">
+      <c r="A268" s="19" t="s">
         <v>540</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>541</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -12144,14 +12177,14 @@
       <c r="Z268" s="3"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="17" t="s">
-        <v>63</v>
+      <c r="A269" s="19" t="s">
+        <v>542</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>88</v>
+        <v>543</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -12178,14 +12211,14 @@
       <c r="Z269" s="3"/>
     </row>
     <row r="270" ht="14.25" customHeight="1">
-      <c r="A270" s="17" t="s">
+      <c r="A270" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -12212,14 +12245,14 @@
       <c r="Z270" s="3"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="17" t="s">
-        <v>542</v>
+      <c r="A271" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>543</v>
+        <v>124</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -12246,14 +12279,14 @@
       <c r="Z271" s="3"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c r="A272" s="17" t="s">
+      <c r="A272" s="19" t="s">
         <v>544</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>545</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -12280,14 +12313,14 @@
       <c r="Z272" s="3"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="17" t="s">
+      <c r="A273" s="19" t="s">
         <v>546</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>547</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -12314,14 +12347,14 @@
       <c r="Z273" s="3"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
-      <c r="A274" s="17" t="s">
+      <c r="A274" s="19" t="s">
         <v>548</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>549</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -12348,14 +12381,14 @@
       <c r="Z274" s="3"/>
     </row>
     <row r="275" ht="14.25" customHeight="1">
-      <c r="A275" s="17" t="s">
+      <c r="A275" s="19" t="s">
         <v>550</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>551</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -12382,14 +12415,14 @@
       <c r="Z275" s="3"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
-      <c r="A276" s="17" t="s">
+      <c r="A276" s="19" t="s">
         <v>552</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>553</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -12416,14 +12449,14 @@
       <c r="Z276" s="3"/>
     </row>
     <row r="277" ht="14.25" customHeight="1">
-      <c r="A277" s="17" t="s">
+      <c r="A277" s="19" t="s">
         <v>554</v>
       </c>
-      <c r="B277" s="18" t="s">
+      <c r="B277" s="3" t="s">
         <v>555</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -12449,15 +12482,15 @@
       <c r="Y277" s="3"/>
       <c r="Z277" s="3"/>
     </row>
-    <row r="278" ht="28.5" customHeight="1">
-      <c r="A278" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="B278" s="3" t="s">
+    <row r="278" ht="14.25" customHeight="1">
+      <c r="A278" s="19" t="s">
         <v>556</v>
       </c>
+      <c r="B278" s="20" t="s">
+        <v>557</v>
+      </c>
       <c r="C278" s="3" t="s">
-        <v>557</v>
+        <v>465</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -12484,14 +12517,14 @@
       <c r="Z278" s="3"/>
     </row>
     <row r="279" ht="28.5" customHeight="1">
-      <c r="A279" s="17" t="s">
-        <v>472</v>
+      <c r="A279" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>558</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -12518,14 +12551,14 @@
       <c r="Z279" s="3"/>
     </row>
     <row r="280" ht="28.5" customHeight="1">
-      <c r="A280" s="17" t="s">
-        <v>472</v>
+      <c r="A280" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B280" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C280" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -12551,15 +12584,15 @@
       <c r="Y280" s="3"/>
       <c r="Z280" s="3"/>
     </row>
-    <row r="281" ht="14.25" customHeight="1">
-      <c r="A281" s="17" t="s">
-        <v>472</v>
+    <row r="281" ht="28.5" customHeight="1">
+      <c r="A281" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -12585,15 +12618,15 @@
       <c r="Y281" s="3"/>
       <c r="Z281" s="3"/>
     </row>
-    <row r="282" ht="28.5" customHeight="1">
-      <c r="A282" s="17" t="s">
-        <v>472</v>
+    <row r="282" ht="14.25" customHeight="1">
+      <c r="A282" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -12619,15 +12652,15 @@
       <c r="Y282" s="3"/>
       <c r="Z282" s="3"/>
     </row>
-    <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="17" t="s">
-        <v>472</v>
+    <row r="283" ht="28.5" customHeight="1">
+      <c r="A283" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -12653,15 +12686,15 @@
       <c r="Y283" s="3"/>
       <c r="Z283" s="3"/>
     </row>
-    <row r="284" ht="28.5" customHeight="1">
-      <c r="A284" s="17" t="s">
-        <v>472</v>
+    <row r="284" ht="14.25" customHeight="1">
+      <c r="A284" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -12688,14 +12721,14 @@
       <c r="Z284" s="3"/>
     </row>
     <row r="285" ht="28.5" customHeight="1">
-      <c r="A285" s="17" t="s">
-        <v>472</v>
+      <c r="A285" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -12722,14 +12755,14 @@
       <c r="Z285" s="3"/>
     </row>
     <row r="286" ht="28.5" customHeight="1">
-      <c r="A286" s="17" t="s">
-        <v>472</v>
+      <c r="A286" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -12755,15 +12788,15 @@
       <c r="Y286" s="3"/>
       <c r="Z286" s="3"/>
     </row>
-    <row r="287" ht="14.25" customHeight="1">
-      <c r="A287" s="17" t="s">
-        <v>472</v>
+    <row r="287" ht="28.5" customHeight="1">
+      <c r="A287" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -12789,15 +12822,15 @@
       <c r="Y287" s="3"/>
       <c r="Z287" s="3"/>
     </row>
-    <row r="288" ht="28.5" customHeight="1">
-      <c r="A288" s="17" t="s">
-        <v>472</v>
+    <row r="288" ht="14.25" customHeight="1">
+      <c r="A288" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -12824,14 +12857,14 @@
       <c r="Z288" s="3"/>
     </row>
     <row r="289" ht="28.5" customHeight="1">
-      <c r="A289" s="17" t="s">
-        <v>472</v>
+      <c r="A289" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -12858,14 +12891,14 @@
       <c r="Z289" s="3"/>
     </row>
     <row r="290" ht="28.5" customHeight="1">
-      <c r="A290" s="17" t="s">
-        <v>472</v>
+      <c r="A290" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -12891,15 +12924,15 @@
       <c r="Y290" s="3"/>
       <c r="Z290" s="3"/>
     </row>
-    <row r="291" ht="14.25" customHeight="1">
-      <c r="A291" s="17" t="s">
-        <v>570</v>
+    <row r="291" ht="28.5" customHeight="1">
+      <c r="A291" s="19" t="s">
+        <v>474</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>571</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -12926,14 +12959,14 @@
       <c r="Z291" s="3"/>
     </row>
     <row r="292" ht="14.25" customHeight="1">
-      <c r="A292" s="17" t="s">
+      <c r="A292" s="19" t="s">
         <v>572</v>
       </c>
-      <c r="B292" s="18" t="s">
+      <c r="B292" s="3" t="s">
         <v>573</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -12960,14 +12993,14 @@
       <c r="Z292" s="3"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="17" t="s">
+      <c r="A293" s="19" t="s">
         <v>574</v>
       </c>
-      <c r="B293" s="3" t="s">
+      <c r="B293" s="20" t="s">
         <v>575</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -12994,14 +13027,14 @@
       <c r="Z293" s="3"/>
     </row>
     <row r="294" ht="14.25" customHeight="1">
-      <c r="A294" s="17" t="s">
+      <c r="A294" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="B294" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B294" s="3" t="s">
+      <c r="C294" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="C294" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -13028,14 +13061,14 @@
       <c r="Z294" s="3"/>
     </row>
     <row r="295" ht="14.25" customHeight="1">
-      <c r="A295" s="17" t="s">
+      <c r="A295" s="19" t="s">
         <v>579</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>580</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -13062,14 +13095,14 @@
       <c r="Z295" s="3"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="17" t="s">
+      <c r="A296" s="19" t="s">
         <v>581</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>582</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -13096,14 +13129,14 @@
       <c r="Z296" s="3"/>
     </row>
     <row r="297" ht="14.25" customHeight="1">
-      <c r="A297" s="17" t="s">
+      <c r="A297" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="B297" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B297" s="3" t="s">
+      <c r="C297" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="C297" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -13130,14 +13163,14 @@
       <c r="Z297" s="3"/>
     </row>
     <row r="298" ht="14.25" customHeight="1">
-      <c r="A298" s="17" t="s">
+      <c r="A298" s="19" t="s">
         <v>586</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>587</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -13164,14 +13197,14 @@
       <c r="Z298" s="3"/>
     </row>
     <row r="299" ht="14.25" customHeight="1">
-      <c r="A299" s="17" t="s">
+      <c r="A299" s="19" t="s">
         <v>588</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>589</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -13198,14 +13231,14 @@
       <c r="Z299" s="3"/>
     </row>
     <row r="300" ht="14.25" customHeight="1">
-      <c r="A300" s="17" t="s">
+      <c r="A300" s="19" t="s">
         <v>590</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="C300" s="19" t="s">
-        <v>6</v>
+      <c r="C300" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -13232,13 +13265,13 @@
       <c r="Z300" s="3"/>
     </row>
     <row r="301" ht="14.25" customHeight="1">
-      <c r="A301" s="17" t="s">
+      <c r="A301" s="19" t="s">
         <v>592</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="C301" s="19" t="s">
+      <c r="C301" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D301" s="3"/>
@@ -13266,13 +13299,13 @@
       <c r="Z301" s="3"/>
     </row>
     <row r="302" ht="14.25" customHeight="1">
-      <c r="A302" s="17" t="s">
+      <c r="A302" s="19" t="s">
         <v>594</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C302" s="19" t="s">
+      <c r="C302" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D302" s="3"/>
@@ -13300,13 +13333,13 @@
       <c r="Z302" s="3"/>
     </row>
     <row r="303" ht="14.25" customHeight="1">
-      <c r="A303" s="17" t="s">
+      <c r="A303" s="19" t="s">
         <v>596</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="C303" s="19" t="s">
+      <c r="C303" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D303" s="3"/>
@@ -13334,13 +13367,13 @@
       <c r="Z303" s="3"/>
     </row>
     <row r="304" ht="14.25" customHeight="1">
-      <c r="A304" s="17" t="s">
+      <c r="A304" s="19" t="s">
         <v>598</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="C304" s="19" t="s">
+      <c r="C304" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D304" s="3"/>
@@ -13368,13 +13401,13 @@
       <c r="Z304" s="3"/>
     </row>
     <row r="305" ht="14.25" customHeight="1">
-      <c r="A305" s="17" t="s">
+      <c r="A305" s="19" t="s">
         <v>600</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="C305" s="19" t="s">
+      <c r="C305" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D305" s="3"/>
@@ -13402,13 +13435,13 @@
       <c r="Z305" s="3"/>
     </row>
     <row r="306" ht="14.25" customHeight="1">
-      <c r="A306" s="17" t="s">
+      <c r="A306" s="19" t="s">
         <v>602</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="C306" s="19" t="s">
+      <c r="C306" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D306" s="3"/>
@@ -13435,14 +13468,14 @@
       <c r="Y306" s="3"/>
       <c r="Z306" s="3"/>
     </row>
-    <row r="307" ht="42.75" customHeight="1">
-      <c r="A307" s="17" t="s">
+    <row r="307" ht="14.25" customHeight="1">
+      <c r="A307" s="19" t="s">
         <v>604</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="C307" s="19" t="s">
+      <c r="C307" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D307" s="3"/>
@@ -13469,14 +13502,14 @@
       <c r="Y307" s="3"/>
       <c r="Z307" s="3"/>
     </row>
-    <row r="308" ht="14.25" customHeight="1">
-      <c r="A308" s="17" t="s">
+    <row r="308" ht="42.75" customHeight="1">
+      <c r="A308" s="19" t="s">
         <v>606</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C308" s="19" t="s">
+      <c r="C308" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D308" s="3"/>
@@ -13504,13 +13537,13 @@
       <c r="Z308" s="3"/>
     </row>
     <row r="309" ht="14.25" customHeight="1">
-      <c r="A309" s="17" t="s">
+      <c r="A309" s="19" t="s">
         <v>608</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="C309" s="19" t="s">
+      <c r="C309" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D309" s="3"/>
@@ -13538,13 +13571,13 @@
       <c r="Z309" s="3"/>
     </row>
     <row r="310" ht="14.25" customHeight="1">
-      <c r="A310" s="17" t="s">
-        <v>608</v>
+      <c r="A310" s="19" t="s">
+        <v>610</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="C310" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="C310" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D310" s="3"/>
@@ -13572,13 +13605,13 @@
       <c r="Z310" s="3"/>
     </row>
     <row r="311" ht="14.25" customHeight="1">
-      <c r="A311" s="17" t="s">
+      <c r="A311" s="19" t="s">
         <v>610</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="C311" s="19" t="s">
+      <c r="C311" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D311" s="3"/>
@@ -13605,14 +13638,14 @@
       <c r="Y311" s="3"/>
       <c r="Z311" s="3"/>
     </row>
-    <row r="312" ht="28.5" customHeight="1">
-      <c r="A312" s="17" t="s">
+    <row r="312" ht="14.25" customHeight="1">
+      <c r="A312" s="19" t="s">
         <v>612</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="C312" s="19" t="s">
+      <c r="C312" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D312" s="3"/>
@@ -13639,15 +13672,15 @@
       <c r="Y312" s="3"/>
       <c r="Z312" s="3"/>
     </row>
-    <row r="313" ht="14.25" customHeight="1">
-      <c r="A313" s="17" t="s">
+    <row r="313" ht="28.5" customHeight="1">
+      <c r="A313" s="19" t="s">
         <v>614</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="C313" s="3" t="s">
-        <v>616</v>
+      <c r="C313" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -13674,14 +13707,14 @@
       <c r="Z313" s="3"/>
     </row>
     <row r="314" ht="14.25" customHeight="1">
-      <c r="A314" s="17" t="s">
+      <c r="A314" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="B314" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B314" s="3" t="s">
+      <c r="C314" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="C314" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -13708,14 +13741,14 @@
       <c r="Z314" s="3"/>
     </row>
     <row r="315" ht="14.25" customHeight="1">
-      <c r="A315" s="17" t="s">
+      <c r="A315" s="19" t="s">
         <v>619</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>620</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -13741,15 +13774,15 @@
       <c r="Y315" s="3"/>
       <c r="Z315" s="3"/>
     </row>
-    <row r="316" ht="28.5" customHeight="1">
-      <c r="A316" s="17" t="s">
+    <row r="316" ht="14.25" customHeight="1">
+      <c r="A316" s="19" t="s">
         <v>621</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>622</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -13776,14 +13809,14 @@
       <c r="Z316" s="3"/>
     </row>
     <row r="317" ht="28.5" customHeight="1">
-      <c r="A317" s="17" t="s">
-        <v>621</v>
+      <c r="A317" s="19" t="s">
+        <v>623</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -13809,15 +13842,15 @@
       <c r="Y317" s="3"/>
       <c r="Z317" s="3"/>
     </row>
-    <row r="318" ht="14.25" customHeight="1">
-      <c r="A318" s="17" t="s">
-        <v>624</v>
+    <row r="318" ht="28.5" customHeight="1">
+      <c r="A318" s="19" t="s">
+        <v>623</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>625</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -13844,14 +13877,14 @@
       <c r="Z318" s="3"/>
     </row>
     <row r="319" ht="14.25" customHeight="1">
-      <c r="A319" s="17" t="s">
+      <c r="A319" s="19" t="s">
         <v>626</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>627</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -13878,14 +13911,14 @@
       <c r="Z319" s="3"/>
     </row>
     <row r="320" ht="14.25" customHeight="1">
-      <c r="A320" s="17" t="s">
+      <c r="A320" s="19" t="s">
         <v>628</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>629</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -13912,14 +13945,14 @@
       <c r="Z320" s="3"/>
     </row>
     <row r="321" ht="14.25" customHeight="1">
-      <c r="A321" s="17" t="s">
+      <c r="A321" s="19" t="s">
         <v>630</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>631</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -13946,14 +13979,14 @@
       <c r="Z321" s="3"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c r="A322" s="17" t="s">
+      <c r="A322" s="19" t="s">
         <v>632</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>633</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -13980,14 +14013,14 @@
       <c r="Z322" s="3"/>
     </row>
     <row r="323" ht="14.25" customHeight="1">
-      <c r="A323" s="17" t="s">
-        <v>632</v>
+      <c r="A323" s="19" t="s">
+        <v>634</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -14014,14 +14047,14 @@
       <c r="Z323" s="3"/>
     </row>
     <row r="324" ht="14.25" customHeight="1">
-      <c r="A324" s="17" t="s">
+      <c r="A324" s="19" t="s">
         <v>634</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>635</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -14048,14 +14081,14 @@
       <c r="Z324" s="3"/>
     </row>
     <row r="325" ht="14.25" customHeight="1">
-      <c r="A325" s="17" t="s">
+      <c r="A325" s="19" t="s">
         <v>636</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>637</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -14082,14 +14115,14 @@
       <c r="Z325" s="3"/>
     </row>
     <row r="326" ht="14.25" customHeight="1">
-      <c r="A326" s="17" t="s">
+      <c r="A326" s="19" t="s">
         <v>638</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>639</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -14116,14 +14149,14 @@
       <c r="Z326" s="3"/>
     </row>
     <row r="327" ht="14.25" customHeight="1">
-      <c r="A327" s="17" t="s">
+      <c r="A327" s="19" t="s">
         <v>640</v>
       </c>
-      <c r="B327" s="18" t="s">
+      <c r="B327" s="3" t="s">
         <v>641</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -14150,14 +14183,14 @@
       <c r="Z327" s="3"/>
     </row>
     <row r="328" ht="14.25" customHeight="1">
-      <c r="A328" s="17" t="s">
-        <v>636</v>
-      </c>
-      <c r="B328" s="18" t="s">
-        <v>637</v>
+      <c r="A328" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="B328" s="20" t="s">
+        <v>643</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -14184,14 +14217,14 @@
       <c r="Z328" s="3"/>
     </row>
     <row r="329" ht="14.25" customHeight="1">
-      <c r="A329" s="17" t="s">
+      <c r="A329" s="19" t="s">
         <v>638</v>
       </c>
-      <c r="B329" s="3" t="s">
+      <c r="B329" s="20" t="s">
         <v>639</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -14218,14 +14251,14 @@
       <c r="Z329" s="3"/>
     </row>
     <row r="330" ht="14.25" customHeight="1">
-      <c r="A330" s="17" t="s">
+      <c r="A330" s="19" t="s">
         <v>640</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>641</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -14252,14 +14285,14 @@
       <c r="Z330" s="3"/>
     </row>
     <row r="331" ht="14.25" customHeight="1">
-      <c r="A331" s="17" t="s">
-        <v>614</v>
+      <c r="A331" s="19" t="s">
+        <v>642</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -14286,14 +14319,14 @@
       <c r="Z331" s="3"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
-      <c r="A332" s="17" t="s">
-        <v>617</v>
-      </c>
-      <c r="B332" s="18" t="s">
+      <c r="A332" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C332" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="C332" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -14320,14 +14353,14 @@
       <c r="Z332" s="3"/>
     </row>
     <row r="333" ht="14.25" customHeight="1">
-      <c r="A333" s="17" t="s">
-        <v>643</v>
-      </c>
-      <c r="B333" s="3" t="s">
-        <v>644</v>
+      <c r="A333" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="B333" s="20" t="s">
+        <v>620</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -14354,14 +14387,14 @@
       <c r="Z333" s="3"/>
     </row>
     <row r="334" ht="14.25" customHeight="1">
-      <c r="A334" s="17" t="s">
+      <c r="A334" s="19" t="s">
         <v>645</v>
       </c>
-      <c r="B334" s="18" t="s">
+      <c r="B334" s="3" t="s">
         <v>646</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -14388,14 +14421,14 @@
       <c r="Z334" s="3"/>
     </row>
     <row r="335" ht="14.25" customHeight="1">
-      <c r="A335" s="17" t="s">
+      <c r="A335" s="19" t="s">
         <v>647</v>
       </c>
-      <c r="B335" s="3" t="s">
+      <c r="B335" s="20" t="s">
         <v>648</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -14421,15 +14454,15 @@
       <c r="Y335" s="3"/>
       <c r="Z335" s="3"/>
     </row>
-    <row r="336" ht="28.5" customHeight="1">
-      <c r="A336" s="17" t="s">
+    <row r="336" ht="14.25" customHeight="1">
+      <c r="A336" s="19" t="s">
         <v>649</v>
       </c>
-      <c r="B336" s="18" t="s">
+      <c r="B336" s="3" t="s">
         <v>650</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -14455,15 +14488,15 @@
       <c r="Y336" s="3"/>
       <c r="Z336" s="3"/>
     </row>
-    <row r="337" ht="14.25" customHeight="1">
-      <c r="A337" s="17" t="s">
+    <row r="337" ht="28.5" customHeight="1">
+      <c r="A337" s="19" t="s">
         <v>651</v>
       </c>
-      <c r="B337" s="18" t="s">
+      <c r="B337" s="20" t="s">
         <v>652</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -14490,14 +14523,14 @@
       <c r="Z337" s="3"/>
     </row>
     <row r="338" ht="14.25" customHeight="1">
-      <c r="A338" s="17" t="s">
+      <c r="A338" s="19" t="s">
         <v>653</v>
       </c>
-      <c r="B338" s="18" t="s">
+      <c r="B338" s="20" t="s">
         <v>654</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -14524,14 +14557,14 @@
       <c r="Z338" s="3"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c r="A339" s="17" t="s">
+      <c r="A339" s="19" t="s">
         <v>655</v>
       </c>
-      <c r="B339" s="3" t="s">
+      <c r="B339" s="20" t="s">
         <v>656</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -14558,14 +14591,14 @@
       <c r="Z339" s="3"/>
     </row>
     <row r="340" ht="14.25" customHeight="1">
-      <c r="A340" s="17" t="s">
+      <c r="A340" s="19" t="s">
         <v>657</v>
       </c>
-      <c r="B340" s="18" t="s">
+      <c r="B340" s="3" t="s">
         <v>658</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -14592,14 +14625,14 @@
       <c r="Z340" s="3"/>
     </row>
     <row r="341" ht="14.25" customHeight="1">
-      <c r="A341" s="17" t="s">
+      <c r="A341" s="19" t="s">
         <v>659</v>
       </c>
-      <c r="B341" s="3" t="s">
+      <c r="B341" s="20" t="s">
         <v>660</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -14626,14 +14659,14 @@
       <c r="Z341" s="3"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c r="A342" s="17" t="s">
+      <c r="A342" s="19" t="s">
         <v>661</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>662</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -14660,14 +14693,14 @@
       <c r="Z342" s="3"/>
     </row>
     <row r="343" ht="14.25" customHeight="1">
-      <c r="A343" s="17" t="s">
-        <v>632</v>
+      <c r="A343" s="19" t="s">
+        <v>663</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -14694,14 +14727,14 @@
       <c r="Z343" s="3"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c r="A344" s="17" t="s">
-        <v>638</v>
+      <c r="A344" s="19" t="s">
+        <v>634</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -14728,14 +14761,14 @@
       <c r="Z344" s="3"/>
     </row>
     <row r="345" ht="14.25" customHeight="1">
-      <c r="A345" s="17" t="s">
-        <v>665</v>
-      </c>
-      <c r="B345" s="20" t="s">
+      <c r="A345" s="19" t="s">
+        <v>640</v>
+      </c>
+      <c r="B345" s="3" t="s">
         <v>666</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -14762,14 +14795,14 @@
       <c r="Z345" s="3"/>
     </row>
     <row r="346" ht="14.25" customHeight="1">
-      <c r="A346" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="B346" s="20" t="s">
+      <c r="A346" s="19" t="s">
         <v>667</v>
       </c>
+      <c r="B346" s="22" t="s">
+        <v>668</v>
+      </c>
       <c r="C346" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -14796,9 +14829,15 @@
       <c r="Z346" s="3"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
-      <c r="A347" s="3"/>
-      <c r="B347" s="3"/>
-      <c r="C347" s="3"/>
+      <c r="A347" s="19" t="s">
+        <v>628</v>
+      </c>
+      <c r="B347" s="22" t="s">
+        <v>669</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>618</v>
+      </c>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
@@ -14824,15 +14863,9 @@
       <c r="Z347" s="3"/>
     </row>
     <row r="348" ht="14.25" customHeight="1">
-      <c r="A348" s="17" t="s">
-        <v>668</v>
-      </c>
-      <c r="B348" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="C348" s="3" t="s">
-        <v>669</v>
-      </c>
+      <c r="A348" s="3"/>
+      <c r="B348" s="3"/>
+      <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
@@ -14858,14 +14891,14 @@
       <c r="Z348" s="3"/>
     </row>
     <row r="349" ht="14.25" customHeight="1">
-      <c r="A349" s="17" t="s">
+      <c r="A349" s="19" t="s">
         <v>670</v>
       </c>
-      <c r="B349" s="20" t="s">
+      <c r="B349" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="C349" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="C349" s="3" t="s">
-        <v>669</v>
       </c>
       <c r="D349" s="3"/>
       <c r="E349" s="3"/>
@@ -14892,14 +14925,14 @@
       <c r="Z349" s="3"/>
     </row>
     <row r="350" ht="14.25" customHeight="1">
-      <c r="A350" s="17" t="s">
+      <c r="A350" s="19" t="s">
         <v>672</v>
       </c>
-      <c r="B350" s="20" t="s">
+      <c r="B350" s="22" t="s">
         <v>673</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -14926,14 +14959,14 @@
       <c r="Z350" s="3"/>
     </row>
     <row r="351" ht="14.25" customHeight="1">
-      <c r="A351" s="17" t="s">
+      <c r="A351" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="B351" s="20" t="s">
-        <v>58</v>
+      <c r="B351" s="22" t="s">
+        <v>675</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
@@ -14960,14 +14993,14 @@
       <c r="Z351" s="3"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
-      <c r="A352" s="17" t="s">
-        <v>675</v>
-      </c>
-      <c r="B352" s="20" t="s">
+      <c r="A352" s="19" t="s">
         <v>676</v>
       </c>
+      <c r="B352" s="22" t="s">
+        <v>58</v>
+      </c>
       <c r="C352" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -14994,14 +15027,14 @@
       <c r="Z352" s="3"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c r="A353" s="17" t="s">
+      <c r="A353" s="19" t="s">
         <v>677</v>
       </c>
-      <c r="B353" s="20" t="s">
+      <c r="B353" s="22" t="s">
         <v>678</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D353" s="3"/>
       <c r="E353" s="3"/>
@@ -15028,14 +15061,14 @@
       <c r="Z353" s="3"/>
     </row>
     <row r="354" ht="14.25" customHeight="1">
-      <c r="A354" s="17" t="s">
+      <c r="A354" s="19" t="s">
         <v>679</v>
       </c>
-      <c r="B354" s="20" t="s">
+      <c r="B354" s="22" t="s">
         <v>680</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -15062,9 +15095,15 @@
       <c r="Z354" s="3"/>
     </row>
     <row r="355" ht="14.25" customHeight="1">
-      <c r="A355" s="3"/>
-      <c r="B355" s="3"/>
-      <c r="C355" s="3"/>
+      <c r="A355" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="B355" s="22" t="s">
+        <v>682</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>671</v>
+      </c>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
@@ -15090,15 +15129,9 @@
       <c r="Z355" s="3"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c r="A356" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="B356" s="20" t="s">
-        <v>681</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>682</v>
-      </c>
+      <c r="A356" s="3"/>
+      <c r="B356" s="3"/>
+      <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
@@ -15124,14 +15157,14 @@
       <c r="Z356" s="3"/>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c r="A357" s="17" t="s">
+      <c r="A357" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="B357" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="B357" s="20" t="s">
+      <c r="C357" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>682</v>
       </c>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
@@ -15158,14 +15191,14 @@
       <c r="Z357" s="3"/>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c r="A358" s="17" t="s">
+      <c r="A358" s="19" t="s">
         <v>685</v>
       </c>
-      <c r="B358" s="20" t="s">
+      <c r="B358" s="22" t="s">
         <v>686</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -15192,14 +15225,14 @@
       <c r="Z358" s="3"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
-      <c r="A359" s="17" t="s">
+      <c r="A359" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="B359" s="20" t="s">
+      <c r="B359" s="22" t="s">
         <v>688</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
@@ -15226,14 +15259,14 @@
       <c r="Z359" s="3"/>
     </row>
     <row r="360" ht="14.25" customHeight="1">
-      <c r="A360" s="17" t="s">
+      <c r="A360" s="19" t="s">
         <v>689</v>
       </c>
-      <c r="B360" s="20" t="s">
+      <c r="B360" s="22" t="s">
         <v>690</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -15260,14 +15293,14 @@
       <c r="Z360" s="3"/>
     </row>
     <row r="361" ht="14.25" customHeight="1">
-      <c r="A361" s="17" t="s">
+      <c r="A361" s="19" t="s">
         <v>691</v>
       </c>
-      <c r="B361" s="20" t="s">
+      <c r="B361" s="22" t="s">
         <v>692</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
@@ -15294,14 +15327,14 @@
       <c r="Z361" s="3"/>
     </row>
     <row r="362" ht="14.25" customHeight="1">
-      <c r="A362" s="17" t="s">
+      <c r="A362" s="19" t="s">
         <v>693</v>
       </c>
-      <c r="B362" s="20" t="s">
+      <c r="B362" s="22" t="s">
         <v>694</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -15328,14 +15361,14 @@
       <c r="Z362" s="3"/>
     </row>
     <row r="363" ht="14.25" customHeight="1">
-      <c r="A363" s="17" t="s">
+      <c r="A363" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="B363" s="20" t="s">
+      <c r="B363" s="22" t="s">
         <v>696</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
@@ -15362,14 +15395,14 @@
       <c r="Z363" s="3"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c r="A364" s="17" t="s">
+      <c r="A364" s="19" t="s">
         <v>697</v>
       </c>
-      <c r="B364" s="20" t="s">
+      <c r="B364" s="22" t="s">
         <v>698</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -15396,14 +15429,14 @@
       <c r="Z364" s="3"/>
     </row>
     <row r="365" ht="14.25" customHeight="1">
-      <c r="A365" s="17" t="s">
-        <v>697</v>
-      </c>
-      <c r="B365" s="20" t="s">
-        <v>698</v>
+      <c r="A365" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="B365" s="22" t="s">
+        <v>700</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
@@ -15430,14 +15463,14 @@
       <c r="Z365" s="3"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c r="A366" s="17" t="s">
+      <c r="A366" s="19" t="s">
         <v>699</v>
       </c>
-      <c r="B366" s="20" t="s">
+      <c r="B366" s="22" t="s">
         <v>700</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -15464,14 +15497,14 @@
       <c r="Z366" s="3"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
-      <c r="A367" s="17" t="s">
+      <c r="A367" s="19" t="s">
         <v>701</v>
       </c>
-      <c r="B367" s="20" t="s">
+      <c r="B367" s="22" t="s">
         <v>702</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
@@ -15498,14 +15531,14 @@
       <c r="Z367" s="3"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c r="A368" s="17" t="s">
+      <c r="A368" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="B368" s="20" t="s">
+      <c r="B368" s="22" t="s">
         <v>704</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -15532,14 +15565,14 @@
       <c r="Z368" s="3"/>
     </row>
     <row r="369" ht="14.25" customHeight="1">
-      <c r="A369" s="17" t="s">
+      <c r="A369" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="B369" s="20" t="s">
+      <c r="B369" s="22" t="s">
         <v>706</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
@@ -15566,14 +15599,14 @@
       <c r="Z369" s="3"/>
     </row>
     <row r="370" ht="14.25" customHeight="1">
-      <c r="A370" s="17" t="s">
+      <c r="A370" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="B370" s="20" t="s">
+      <c r="B370" s="22" t="s">
         <v>708</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -15600,14 +15633,14 @@
       <c r="Z370" s="3"/>
     </row>
     <row r="371" ht="14.25" customHeight="1">
-      <c r="A371" s="17" t="s">
+      <c r="A371" s="19" t="s">
         <v>709</v>
       </c>
-      <c r="B371" s="20" t="s">
+      <c r="B371" s="22" t="s">
         <v>710</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
@@ -15634,14 +15667,14 @@
       <c r="Z371" s="3"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
-      <c r="A372" s="17" t="s">
+      <c r="A372" s="19" t="s">
         <v>711</v>
       </c>
-      <c r="B372" s="20" t="s">
+      <c r="B372" s="22" t="s">
         <v>712</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -15668,14 +15701,14 @@
       <c r="Z372" s="3"/>
     </row>
     <row r="373" ht="14.25" customHeight="1">
-      <c r="A373" s="17" t="s">
+      <c r="A373" s="19" t="s">
         <v>713</v>
       </c>
-      <c r="B373" s="20" t="s">
+      <c r="B373" s="22" t="s">
         <v>714</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
@@ -15702,14 +15735,14 @@
       <c r="Z373" s="3"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c r="A374" s="17" t="s">
+      <c r="A374" s="19" t="s">
         <v>715</v>
       </c>
-      <c r="B374" s="20" t="s">
-        <v>712</v>
+      <c r="B374" s="22" t="s">
+        <v>716</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -15736,14 +15769,14 @@
       <c r="Z374" s="3"/>
     </row>
     <row r="375" ht="14.25" customHeight="1">
-      <c r="A375" s="17" t="s">
-        <v>716</v>
-      </c>
-      <c r="B375" s="20" t="s">
+      <c r="A375" s="19" t="s">
         <v>717</v>
       </c>
+      <c r="B375" s="22" t="s">
+        <v>714</v>
+      </c>
       <c r="C375" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
@@ -15770,14 +15803,14 @@
       <c r="Z375" s="3"/>
     </row>
     <row r="376" ht="14.25" customHeight="1">
-      <c r="A376" s="17" t="s">
+      <c r="A376" s="19" t="s">
         <v>718</v>
       </c>
-      <c r="B376" s="20" t="s">
+      <c r="B376" s="22" t="s">
         <v>719</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -15804,14 +15837,14 @@
       <c r="Z376" s="3"/>
     </row>
     <row r="377" ht="14.25" customHeight="1">
-      <c r="A377" s="17" t="s">
+      <c r="A377" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="B377" s="20" t="s">
-        <v>717</v>
+      <c r="B377" s="22" t="s">
+        <v>721</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
@@ -15838,14 +15871,14 @@
       <c r="Z377" s="3"/>
     </row>
     <row r="378" ht="14.25" customHeight="1">
-      <c r="A378" s="17" t="s">
-        <v>721</v>
-      </c>
-      <c r="B378" s="20" t="s">
-        <v>690</v>
+      <c r="A378" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="B378" s="22" t="s">
+        <v>719</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -15872,14 +15905,14 @@
       <c r="Z378" s="3"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
-      <c r="A379" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="B379" s="20" t="s">
+      <c r="A379" s="19" t="s">
         <v>723</v>
       </c>
+      <c r="B379" s="22" t="s">
+        <v>692</v>
+      </c>
       <c r="C379" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
@@ -15906,14 +15939,14 @@
       <c r="Z379" s="3"/>
     </row>
     <row r="380" ht="14.25" customHeight="1">
-      <c r="A380" s="17" t="s">
+      <c r="A380" s="19" t="s">
         <v>724</v>
       </c>
-      <c r="B380" s="20" t="s">
+      <c r="B380" s="22" t="s">
         <v>725</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -15940,14 +15973,14 @@
       <c r="Z380" s="3"/>
     </row>
     <row r="381" ht="14.25" customHeight="1">
-      <c r="A381" s="17" t="s">
+      <c r="A381" s="19" t="s">
         <v>726</v>
       </c>
-      <c r="B381" s="20" t="s">
+      <c r="B381" s="22" t="s">
         <v>727</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
@@ -15974,14 +16007,14 @@
       <c r="Z381" s="3"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c r="A382" s="17" t="s">
+      <c r="A382" s="19" t="s">
         <v>728</v>
       </c>
-      <c r="B382" s="20" t="s">
+      <c r="B382" s="22" t="s">
         <v>729</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -16008,14 +16041,14 @@
       <c r="Z382" s="3"/>
     </row>
     <row r="383" ht="14.25" customHeight="1">
-      <c r="A383" s="17" t="s">
+      <c r="A383" s="19" t="s">
         <v>730</v>
       </c>
-      <c r="B383" s="20" t="s">
+      <c r="B383" s="22" t="s">
         <v>731</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
@@ -16042,14 +16075,14 @@
       <c r="Z383" s="3"/>
     </row>
     <row r="384" ht="14.25" customHeight="1">
-      <c r="A384" s="17" t="s">
+      <c r="A384" s="19" t="s">
         <v>732</v>
       </c>
-      <c r="B384" s="20" t="s">
+      <c r="B384" s="22" t="s">
         <v>733</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -16076,14 +16109,14 @@
       <c r="Z384" s="3"/>
     </row>
     <row r="385" ht="14.25" customHeight="1">
-      <c r="A385" s="17" t="s">
+      <c r="A385" s="19" t="s">
         <v>734</v>
       </c>
-      <c r="B385" s="20" t="s">
+      <c r="B385" s="22" t="s">
         <v>735</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
@@ -16110,14 +16143,14 @@
       <c r="Z385" s="3"/>
     </row>
     <row r="386" ht="14.25" customHeight="1">
-      <c r="A386" s="17" t="s">
+      <c r="A386" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="B386" s="20" t="s">
+      <c r="B386" s="22" t="s">
         <v>737</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -16144,14 +16177,14 @@
       <c r="Z386" s="3"/>
     </row>
     <row r="387" ht="14.25" customHeight="1">
-      <c r="A387" s="17" t="s">
+      <c r="A387" s="19" t="s">
         <v>738</v>
       </c>
-      <c r="B387" s="20" t="s">
+      <c r="B387" s="22" t="s">
         <v>739</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
@@ -16178,14 +16211,14 @@
       <c r="Z387" s="3"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c r="A388" s="17" t="s">
+      <c r="A388" s="19" t="s">
         <v>740</v>
       </c>
-      <c r="B388" s="20" t="s">
+      <c r="B388" s="22" t="s">
         <v>741</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -16212,14 +16245,14 @@
       <c r="Z388" s="3"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c r="A389" s="17" t="s">
+      <c r="A389" s="19" t="s">
         <v>742</v>
       </c>
-      <c r="B389" s="20" t="s">
-        <v>741</v>
+      <c r="B389" s="22" t="s">
+        <v>743</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
@@ -16246,14 +16279,14 @@
       <c r="Z389" s="3"/>
     </row>
     <row r="390" ht="14.25" customHeight="1">
-      <c r="A390" s="17" t="s">
+      <c r="A390" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="B390" s="22" t="s">
         <v>743</v>
       </c>
-      <c r="B390" s="20" t="s">
-        <v>744</v>
-      </c>
       <c r="C390" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -16280,14 +16313,14 @@
       <c r="Z390" s="3"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c r="A391" s="17" t="s">
+      <c r="A391" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="B391" s="20" t="s">
+      <c r="B391" s="22" t="s">
         <v>746</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
@@ -16314,14 +16347,14 @@
       <c r="Z391" s="3"/>
     </row>
     <row r="392" ht="14.25" customHeight="1">
-      <c r="A392" s="17" t="s">
+      <c r="A392" s="19" t="s">
         <v>747</v>
       </c>
-      <c r="B392" s="20" t="s">
+      <c r="B392" s="22" t="s">
         <v>748</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -16348,14 +16381,14 @@
       <c r="Z392" s="3"/>
     </row>
     <row r="393" ht="14.25" customHeight="1">
-      <c r="A393" s="17" t="s">
+      <c r="A393" s="19" t="s">
         <v>749</v>
       </c>
-      <c r="B393" s="20" t="s">
+      <c r="B393" s="22" t="s">
         <v>750</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
@@ -16382,14 +16415,14 @@
       <c r="Z393" s="3"/>
     </row>
     <row r="394" ht="14.25" customHeight="1">
-      <c r="A394" s="17" t="s">
+      <c r="A394" s="19" t="s">
         <v>751</v>
       </c>
-      <c r="B394" s="20" t="s">
+      <c r="B394" s="22" t="s">
         <v>752</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -16416,14 +16449,14 @@
       <c r="Z394" s="3"/>
     </row>
     <row r="395" ht="14.25" customHeight="1">
-      <c r="A395" s="17" t="s">
+      <c r="A395" s="19" t="s">
         <v>753</v>
       </c>
-      <c r="B395" s="20" t="s">
+      <c r="B395" s="22" t="s">
         <v>754</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
@@ -16450,14 +16483,14 @@
       <c r="Z395" s="3"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c r="A396" s="17" t="s">
+      <c r="A396" s="19" t="s">
         <v>755</v>
       </c>
-      <c r="B396" s="20" t="s">
+      <c r="B396" s="22" t="s">
         <v>756</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -16484,14 +16517,14 @@
       <c r="Z396" s="3"/>
     </row>
     <row r="397" ht="14.25" customHeight="1">
-      <c r="A397" s="17" t="s">
+      <c r="A397" s="19" t="s">
         <v>757</v>
       </c>
-      <c r="B397" s="20" t="s">
-        <v>733</v>
+      <c r="B397" s="22" t="s">
+        <v>758</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
@@ -16518,14 +16551,14 @@
       <c r="Z397" s="3"/>
     </row>
     <row r="398" ht="14.25" customHeight="1">
-      <c r="A398" s="17" t="s">
-        <v>758</v>
-      </c>
-      <c r="B398" s="20" t="s">
+      <c r="A398" s="19" t="s">
         <v>759</v>
       </c>
+      <c r="B398" s="22" t="s">
+        <v>735</v>
+      </c>
       <c r="C398" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -16552,14 +16585,14 @@
       <c r="Z398" s="3"/>
     </row>
     <row r="399" ht="14.25" customHeight="1">
-      <c r="A399" s="17" t="s">
+      <c r="A399" s="19" t="s">
         <v>760</v>
       </c>
-      <c r="B399" s="20" t="s">
+      <c r="B399" s="22" t="s">
         <v>761</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
@@ -16586,14 +16619,14 @@
       <c r="Z399" s="3"/>
     </row>
     <row r="400" ht="14.25" customHeight="1">
-      <c r="A400" s="17" t="s">
+      <c r="A400" s="19" t="s">
         <v>762</v>
       </c>
-      <c r="B400" s="20" t="s">
-        <v>690</v>
+      <c r="B400" s="22" t="s">
+        <v>763</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -16620,14 +16653,14 @@
       <c r="Z400" s="3"/>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c r="A401" s="17" t="s">
-        <v>763</v>
-      </c>
-      <c r="B401" s="20" t="s">
+      <c r="A401" s="19" t="s">
         <v>764</v>
       </c>
+      <c r="B401" s="22" t="s">
+        <v>692</v>
+      </c>
       <c r="C401" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
@@ -16654,14 +16687,14 @@
       <c r="Z401" s="3"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c r="A402" s="17" t="s">
+      <c r="A402" s="19" t="s">
         <v>765</v>
       </c>
-      <c r="B402" s="20" t="s">
-        <v>281</v>
+      <c r="B402" s="22" t="s">
+        <v>766</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>282</v>
+        <v>684</v>
       </c>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -16688,11 +16721,11 @@
       <c r="Z402" s="3"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c r="A403" s="17" t="s">
-        <v>766</v>
-      </c>
-      <c r="B403" s="20" t="s">
-        <v>284</v>
+      <c r="A403" s="19" t="s">
+        <v>767</v>
+      </c>
+      <c r="B403" s="22" t="s">
+        <v>281</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>282</v>
@@ -16722,11 +16755,11 @@
       <c r="Z403" s="3"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
-      <c r="A404" s="17" t="s">
-        <v>767</v>
-      </c>
-      <c r="B404" s="20" t="s">
-        <v>286</v>
+      <c r="A404" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="B404" s="22" t="s">
+        <v>284</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>282</v>
@@ -16756,11 +16789,11 @@
       <c r="Z404" s="3"/>
     </row>
     <row r="405" ht="14.25" customHeight="1">
-      <c r="A405" s="17" t="s">
-        <v>768</v>
-      </c>
-      <c r="B405" s="20" t="s">
-        <v>288</v>
+      <c r="A405" s="19" t="s">
+        <v>769</v>
+      </c>
+      <c r="B405" s="22" t="s">
+        <v>286</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>282</v>
@@ -16790,11 +16823,11 @@
       <c r="Z405" s="3"/>
     </row>
     <row r="406" ht="14.25" customHeight="1">
-      <c r="A406" s="17" t="s">
-        <v>769</v>
-      </c>
-      <c r="B406" s="20" t="s">
-        <v>290</v>
+      <c r="A406" s="19" t="s">
+        <v>770</v>
+      </c>
+      <c r="B406" s="22" t="s">
+        <v>288</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>282</v>
@@ -16824,11 +16857,11 @@
       <c r="Z406" s="3"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c r="A407" s="17" t="s">
-        <v>770</v>
-      </c>
-      <c r="B407" s="20" t="s">
-        <v>292</v>
+      <c r="A407" s="19" t="s">
+        <v>771</v>
+      </c>
+      <c r="B407" s="22" t="s">
+        <v>290</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>282</v>
@@ -16858,11 +16891,11 @@
       <c r="Z407" s="3"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
-      <c r="A408" s="17" t="s">
-        <v>771</v>
-      </c>
-      <c r="B408" s="20" t="s">
-        <v>294</v>
+      <c r="A408" s="19" t="s">
+        <v>772</v>
+      </c>
+      <c r="B408" s="22" t="s">
+        <v>292</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>282</v>
@@ -16892,11 +16925,11 @@
       <c r="Z408" s="3"/>
     </row>
     <row r="409" ht="14.25" customHeight="1">
-      <c r="A409" s="17" t="s">
-        <v>772</v>
-      </c>
-      <c r="B409" s="20" t="s">
-        <v>296</v>
+      <c r="A409" s="19" t="s">
+        <v>773</v>
+      </c>
+      <c r="B409" s="22" t="s">
+        <v>294</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>282</v>
@@ -16926,11 +16959,11 @@
       <c r="Z409" s="3"/>
     </row>
     <row r="410" ht="14.25" customHeight="1">
-      <c r="A410" s="17" t="s">
-        <v>773</v>
-      </c>
-      <c r="B410" s="20" t="s">
-        <v>298</v>
+      <c r="A410" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="B410" s="22" t="s">
+        <v>296</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>282</v>
@@ -16960,14 +16993,14 @@
       <c r="Z410" s="3"/>
     </row>
     <row r="411" ht="14.25" customHeight="1">
-      <c r="A411" s="17" t="s">
-        <v>774</v>
-      </c>
-      <c r="B411" s="3" t="s">
+      <c r="A411" s="19" t="s">
         <v>775</v>
       </c>
+      <c r="B411" s="22" t="s">
+        <v>298</v>
+      </c>
       <c r="C411" s="3" t="s">
-        <v>776</v>
+        <v>282</v>
       </c>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
@@ -16994,16 +17027,16 @@
       <c r="Z411" s="3"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
-      <c r="A412" s="17" t="s">
+      <c r="A412" s="19" t="s">
+        <v>776</v>
+      </c>
+      <c r="B412" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B412" s="3" t="s">
+      <c r="C412" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="C412" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D412" s="21"/>
+      <c r="D412" s="3"/>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
       <c r="G412" s="3"/>
@@ -17028,16 +17061,16 @@
       <c r="Z412" s="3"/>
     </row>
     <row r="413" ht="14.25" customHeight="1">
-      <c r="A413" s="17" t="s">
+      <c r="A413" s="19" t="s">
         <v>779</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>780</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D413" s="3"/>
+        <v>778</v>
+      </c>
+      <c r="D413" s="23"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
       <c r="G413" s="3"/>
@@ -17062,14 +17095,14 @@
       <c r="Z413" s="3"/>
     </row>
     <row r="414" ht="14.25" customHeight="1">
-      <c r="A414" s="17" t="s">
+      <c r="A414" s="19" t="s">
         <v>781</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>782</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -17096,14 +17129,14 @@
       <c r="Z414" s="3"/>
     </row>
     <row r="415" ht="14.25" customHeight="1">
-      <c r="A415" s="3" t="s">
+      <c r="A415" s="19" t="s">
         <v>783</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="C415" s="22" t="s">
-        <v>159</v>
+      <c r="C415" s="3" t="s">
+        <v>778</v>
       </c>
       <c r="D415" s="3"/>
       <c r="E415" s="3"/>
@@ -17130,14 +17163,14 @@
       <c r="Z415" s="3"/>
     </row>
     <row r="416" ht="14.25" customHeight="1">
-      <c r="A416" s="17" t="s">
+      <c r="A416" s="3" t="s">
         <v>785</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="C416" s="21" t="s">
-        <v>327</v>
+      <c r="C416" s="24" t="s">
+        <v>159</v>
       </c>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
@@ -17164,13 +17197,13 @@
       <c r="Z416" s="3"/>
     </row>
     <row r="417" ht="14.25" customHeight="1">
-      <c r="A417" s="17" t="s">
+      <c r="A417" s="19" t="s">
         <v>787</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="C417" s="21" t="s">
+      <c r="C417" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D417" s="3"/>
@@ -17198,13 +17231,13 @@
       <c r="Z417" s="3"/>
     </row>
     <row r="418" ht="14.25" customHeight="1">
-      <c r="A418" s="17" t="s">
+      <c r="A418" s="19" t="s">
         <v>789</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="C418" s="21" t="s">
+      <c r="C418" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D418" s="3"/>
@@ -17232,13 +17265,13 @@
       <c r="Z418" s="3"/>
     </row>
     <row r="419" ht="14.25" customHeight="1">
-      <c r="A419" s="17" t="s">
+      <c r="A419" s="19" t="s">
         <v>791</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="C419" s="21" t="s">
+      <c r="C419" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D419" s="3"/>
@@ -17266,13 +17299,13 @@
       <c r="Z419" s="3"/>
     </row>
     <row r="420" ht="14.25" customHeight="1">
-      <c r="A420" s="17" t="s">
-        <v>791</v>
+      <c r="A420" s="19" t="s">
+        <v>793</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="C420" s="21" t="s">
+        <v>794</v>
+      </c>
+      <c r="C420" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D420" s="3"/>
@@ -17300,13 +17333,13 @@
       <c r="Z420" s="3"/>
     </row>
     <row r="421" ht="14.25" customHeight="1">
-      <c r="A421" s="17" t="s">
-        <v>794</v>
+      <c r="A421" s="19" t="s">
+        <v>793</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="C421" s="21" t="s">
+      <c r="C421" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D421" s="3"/>
@@ -17334,13 +17367,13 @@
       <c r="Z421" s="3"/>
     </row>
     <row r="422" ht="14.25" customHeight="1">
-      <c r="A422" s="17" t="s">
+      <c r="A422" s="19" t="s">
         <v>796</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="C422" s="21" t="s">
+      <c r="C422" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D422" s="3"/>
@@ -17368,9 +17401,15 @@
       <c r="Z422" s="3"/>
     </row>
     <row r="423" ht="14.25" customHeight="1">
-      <c r="A423" s="3"/>
-      <c r="B423" s="3"/>
-      <c r="C423" s="3"/>
+      <c r="A423" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="B423" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="C423" s="23" t="s">
+        <v>327</v>
+      </c>
       <c r="D423" s="3"/>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
@@ -17395,16 +17434,10 @@
       <c r="Y423" s="3"/>
       <c r="Z423" s="3"/>
     </row>
-    <row r="424" ht="28.5" customHeight="1">
-      <c r="A424" s="17" t="s">
-        <v>798</v>
-      </c>
-      <c r="B424" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>317</v>
-      </c>
+    <row r="424" ht="14.25" customHeight="1">
+      <c r="A424" s="3"/>
+      <c r="B424" s="3"/>
+      <c r="C424" s="3"/>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
@@ -17430,14 +17463,14 @@
       <c r="Z424" s="3"/>
     </row>
     <row r="425" ht="28.5" customHeight="1">
-      <c r="A425" s="17" t="s">
+      <c r="A425" s="19" t="s">
         <v>800</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>305</v>
+        <v>801</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>801</v>
+        <v>317</v>
       </c>
       <c r="D425" s="3"/>
       <c r="E425" s="3"/>
@@ -17463,15 +17496,15 @@
       <c r="Y425" s="3"/>
       <c r="Z425" s="3"/>
     </row>
-    <row r="426" ht="14.25" customHeight="1">
-      <c r="A426" s="17" t="s">
+    <row r="426" ht="28.5" customHeight="1">
+      <c r="A426" s="19" t="s">
         <v>802</v>
       </c>
       <c r="B426" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C426" s="3" t="s">
         <v>803</v>
-      </c>
-      <c r="C426" s="3" t="s">
-        <v>801</v>
       </c>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
@@ -17498,14 +17531,14 @@
       <c r="Z426" s="3"/>
     </row>
     <row r="427" ht="14.25" customHeight="1">
-      <c r="A427" s="17" t="s">
+      <c r="A427" s="19" t="s">
         <v>804</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>303</v>
+        <v>805</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D427" s="3"/>
       <c r="E427" s="3"/>
@@ -17532,14 +17565,14 @@
       <c r="Z427" s="3"/>
     </row>
     <row r="428" ht="14.25" customHeight="1">
-      <c r="A428" s="23" t="s">
-        <v>805</v>
-      </c>
-      <c r="B428" s="24" t="s">
+      <c r="A428" s="19" t="s">
         <v>806</v>
       </c>
-      <c r="C428" s="21" t="s">
-        <v>807</v>
+      <c r="B428" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>803</v>
       </c>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
@@ -17567,13 +17600,13 @@
     </row>
     <row r="429" ht="14.25" customHeight="1">
       <c r="A429" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="B429" s="26" t="s">
         <v>808</v>
       </c>
-      <c r="B429" s="21" t="s">
+      <c r="C429" s="23" t="s">
         <v>809</v>
-      </c>
-      <c r="C429" s="21" t="s">
-        <v>807</v>
       </c>
       <c r="D429" s="3"/>
       <c r="E429" s="3"/>
@@ -17600,14 +17633,14 @@
       <c r="Z429" s="3"/>
     </row>
     <row r="430" ht="14.25" customHeight="1">
-      <c r="A430" s="3" t="s">
+      <c r="A430" s="27" t="s">
         <v>810</v>
       </c>
-      <c r="B430" s="3" t="s">
+      <c r="B430" s="23" t="s">
         <v>811</v>
       </c>
-      <c r="C430" s="3" t="s">
-        <v>807</v>
+      <c r="C430" s="23" t="s">
+        <v>809</v>
       </c>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
@@ -17637,11 +17670,11 @@
       <c r="A431" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B431" s="3" t="s">
+      <c r="B431" s="28" t="s">
         <v>813</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D431" s="3"/>
       <c r="E431" s="3"/>
@@ -17675,7 +17708,7 @@
         <v>815</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
@@ -17709,7 +17742,7 @@
         <v>817</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="D433" s="3"/>
       <c r="E433" s="3"/>
@@ -17737,13 +17770,13 @@
     </row>
     <row r="434" ht="14.25" customHeight="1">
       <c r="A434" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B434" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="B434" s="3" t="s">
+      <c r="C434" s="3" t="s">
         <v>820</v>
-      </c>
-      <c r="C434" s="19" t="s">
-        <v>6</v>
       </c>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
@@ -17770,13 +17803,13 @@
       <c r="Z434" s="3"/>
     </row>
     <row r="435" ht="14.25" customHeight="1">
-      <c r="A435" s="26" t="s">
+      <c r="A435" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="B435" s="27" t="s">
+      <c r="B435" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="C435" s="28" t="s">
+      <c r="C435" s="21" t="s">
         <v>6</v>
       </c>
       <c r="D435" s="3"/>
@@ -17804,13 +17837,13 @@
       <c r="Z435" s="3"/>
     </row>
     <row r="436" ht="14.25" customHeight="1">
-      <c r="A436" s="28" t="s">
+      <c r="A436" s="29" t="s">
         <v>823</v>
       </c>
-      <c r="B436" s="27" t="s">
+      <c r="B436" s="30" t="s">
         <v>824</v>
       </c>
-      <c r="C436" s="28" t="s">
+      <c r="C436" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D436" s="3"/>
@@ -17838,13 +17871,13 @@
       <c r="Z436" s="3"/>
     </row>
     <row r="437" ht="14.25" customHeight="1">
-      <c r="A437" s="28" t="s">
+      <c r="A437" s="31" t="s">
         <v>825</v>
       </c>
-      <c r="B437" s="27" t="s">
+      <c r="B437" s="30" t="s">
         <v>826</v>
       </c>
-      <c r="C437" s="28" t="s">
+      <c r="C437" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D437" s="3"/>
@@ -17872,14 +17905,14 @@
       <c r="Z437" s="3"/>
     </row>
     <row r="438" ht="14.25" customHeight="1">
-      <c r="A438" s="28" t="s">
+      <c r="A438" s="31" t="s">
         <v>827</v>
       </c>
-      <c r="B438" s="27" t="s">
+      <c r="B438" s="30" t="s">
         <v>828</v>
       </c>
-      <c r="C438" s="28" t="s">
-        <v>159</v>
+      <c r="C438" s="31" t="s">
+        <v>6</v>
       </c>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
@@ -17906,14 +17939,14 @@
       <c r="Z438" s="3"/>
     </row>
     <row r="439" ht="14.25" customHeight="1">
-      <c r="A439" s="28" t="s">
+      <c r="A439" s="31" t="s">
         <v>829</v>
       </c>
-      <c r="B439" s="27" t="s">
+      <c r="B439" s="30" t="s">
         <v>830</v>
       </c>
-      <c r="C439" s="28" t="s">
-        <v>6</v>
+      <c r="C439" s="31" t="s">
+        <v>159</v>
       </c>
       <c r="D439" s="3"/>
       <c r="E439" s="3"/>
@@ -17940,13 +17973,13 @@
       <c r="Z439" s="3"/>
     </row>
     <row r="440" ht="14.25" customHeight="1">
-      <c r="A440" s="28" t="s">
+      <c r="A440" s="31" t="s">
         <v>831</v>
       </c>
-      <c r="B440" s="27" t="s">
+      <c r="B440" s="30" t="s">
         <v>832</v>
       </c>
-      <c r="C440" s="28" t="s">
+      <c r="C440" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D440" s="3"/>
@@ -17974,13 +18007,13 @@
       <c r="Z440" s="3"/>
     </row>
     <row r="441" ht="14.25" customHeight="1">
-      <c r="A441" s="28" t="s">
+      <c r="A441" s="31" t="s">
         <v>833</v>
       </c>
-      <c r="B441" s="27" t="s">
+      <c r="B441" s="30" t="s">
         <v>834</v>
       </c>
-      <c r="C441" s="28" t="s">
+      <c r="C441" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D441" s="3"/>
@@ -18008,9 +18041,15 @@
       <c r="Z441" s="3"/>
     </row>
     <row r="442" ht="14.25" customHeight="1">
-      <c r="A442" s="3"/>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
+      <c r="A442" s="31" t="s">
+        <v>835</v>
+      </c>
+      <c r="B442" s="30" t="s">
+        <v>836</v>
+      </c>
+      <c r="C442" s="31" t="s">
+        <v>6</v>
+      </c>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
@@ -33687,10 +33726,38 @@
       <c r="Y1001" s="3"/>
       <c r="Z1001" s="3"/>
     </row>
+    <row r="1002" ht="14.25" customHeight="1">
+      <c r="A1002" s="3"/>
+      <c r="B1002" s="3"/>
+      <c r="C1002" s="3"/>
+      <c r="D1002" s="3"/>
+      <c r="E1002" s="3"/>
+      <c r="F1002" s="3"/>
+      <c r="G1002" s="3"/>
+      <c r="H1002" s="3"/>
+      <c r="I1002" s="3"/>
+      <c r="J1002" s="3"/>
+      <c r="K1002" s="3"/>
+      <c r="L1002" s="3"/>
+      <c r="M1002" s="3"/>
+      <c r="N1002" s="3"/>
+      <c r="O1002" s="3"/>
+      <c r="P1002" s="3"/>
+      <c r="Q1002" s="3"/>
+      <c r="R1002" s="3"/>
+      <c r="S1002" s="3"/>
+      <c r="T1002" s="3"/>
+      <c r="U1002" s="3"/>
+      <c r="V1002" s="3"/>
+      <c r="W1002" s="3"/>
+      <c r="X1002" s="3"/>
+      <c r="Y1002" s="3"/>
+      <c r="Z1002" s="3"/>
+    </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{69C3906C-70E3-4709-B001-22E5206BF726}" filter="1" showAutoFilter="1">
-      <autoFilter ref="$A$1:$D$189"/>
+    <customSheetView guid="{840AC4D9-05FC-4DF1-A02E-909E79011D7E}" filter="1" showAutoFilter="1">
+      <autoFilter ref="$A$1:$D$190"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1862576941"/>
@@ -33699,105 +33766,109 @@
     </customSheetView>
   </customSheetViews>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C203:C441">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C204:C442">
       <formula1>"General,VPN,MAIL_PRIVACY,LIVE_TV,GITHUB_APPS,Android_APPS,Antivirus PC,File_Transfer,E-BOOKS,DNS,High-Level-Lang,CODE2IMG,CLOUD_STORAGE,E-BANKING,Stocks,JOBS,EDU,Maps,IPTV"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B56"/>
-    <hyperlink r:id="rId2" ref="B59"/>
-    <hyperlink r:id="rId3" ref="B60"/>
-    <hyperlink r:id="rId4" ref="B63"/>
-    <hyperlink r:id="rId5" ref="B88"/>
-    <hyperlink r:id="rId6" ref="B89"/>
-    <hyperlink r:id="rId7" ref="B160"/>
-    <hyperlink r:id="rId8" ref="B197"/>
-    <hyperlink r:id="rId9" ref="B277"/>
-    <hyperlink r:id="rId10" ref="B292"/>
-    <hyperlink r:id="rId11" ref="B327"/>
-    <hyperlink r:id="rId12" ref="B328"/>
-    <hyperlink r:id="rId13" ref="B332"/>
-    <hyperlink r:id="rId14" ref="B334"/>
-    <hyperlink r:id="rId15" ref="B336"/>
-    <hyperlink r:id="rId16" ref="B337"/>
-    <hyperlink r:id="rId17" ref="B338"/>
-    <hyperlink r:id="rId18" ref="B340"/>
-    <hyperlink r:id="rId19" ref="B345"/>
-    <hyperlink r:id="rId20" ref="B346"/>
-    <hyperlink r:id="rId21" ref="B348"/>
-    <hyperlink r:id="rId22" ref="B349"/>
-    <hyperlink r:id="rId23" ref="B350"/>
-    <hyperlink r:id="rId24" ref="B351"/>
-    <hyperlink r:id="rId25" ref="B352"/>
-    <hyperlink r:id="rId26" ref="B353"/>
-    <hyperlink r:id="rId27" ref="B354"/>
-    <hyperlink r:id="rId28" ref="B357"/>
-    <hyperlink r:id="rId29" ref="B358"/>
-    <hyperlink r:id="rId30" ref="B359"/>
-    <hyperlink r:id="rId31" ref="B360"/>
-    <hyperlink r:id="rId32" ref="B361"/>
-    <hyperlink r:id="rId33" ref="B362"/>
-    <hyperlink r:id="rId34" ref="B363"/>
-    <hyperlink r:id="rId35" ref="B364"/>
-    <hyperlink r:id="rId36" ref="B365"/>
-    <hyperlink r:id="rId37" ref="B366"/>
-    <hyperlink r:id="rId38" ref="B367"/>
-    <hyperlink r:id="rId39" ref="B368"/>
-    <hyperlink r:id="rId40" ref="B369"/>
-    <hyperlink r:id="rId41" ref="B370"/>
-    <hyperlink r:id="rId42" ref="B371"/>
-    <hyperlink r:id="rId43" ref="B372"/>
-    <hyperlink r:id="rId44" ref="B373"/>
-    <hyperlink r:id="rId45" ref="B374"/>
-    <hyperlink r:id="rId46" ref="B375"/>
-    <hyperlink r:id="rId47" ref="B376"/>
-    <hyperlink r:id="rId48" ref="B377"/>
-    <hyperlink r:id="rId49" ref="B378"/>
-    <hyperlink r:id="rId50" ref="B379"/>
-    <hyperlink r:id="rId51" ref="B380"/>
-    <hyperlink r:id="rId52" ref="B381"/>
-    <hyperlink r:id="rId53" location="/" ref="B382"/>
-    <hyperlink r:id="rId54" ref="B383"/>
-    <hyperlink r:id="rId55" location="/s/feed" ref="B384"/>
-    <hyperlink r:id="rId56" ref="B385"/>
-    <hyperlink r:id="rId57" ref="B386"/>
-    <hyperlink r:id="rId58" ref="B387"/>
-    <hyperlink r:id="rId59" location="content" ref="B388"/>
-    <hyperlink r:id="rId60" ref="B389"/>
-    <hyperlink r:id="rId61" ref="B390"/>
-    <hyperlink r:id="rId62" ref="B391"/>
-    <hyperlink r:id="rId63" ref="B392"/>
-    <hyperlink r:id="rId64" ref="B393"/>
-    <hyperlink r:id="rId65" ref="B394"/>
-    <hyperlink r:id="rId66" ref="B395"/>
-    <hyperlink r:id="rId67" ref="B396"/>
-    <hyperlink r:id="rId68" location="/s/feed" ref="B397"/>
-    <hyperlink r:id="rId69" ref="B398"/>
-    <hyperlink r:id="rId70" ref="B399"/>
-    <hyperlink r:id="rId71" ref="B400"/>
-    <hyperlink r:id="rId72" ref="B401"/>
-    <hyperlink r:id="rId73" ref="B402"/>
-    <hyperlink r:id="rId74" ref="B403"/>
-    <hyperlink r:id="rId75" ref="B404"/>
-    <hyperlink r:id="rId76" ref="B405"/>
-    <hyperlink r:id="rId77" ref="B407"/>
-    <hyperlink r:id="rId78" ref="B408"/>
-    <hyperlink r:id="rId79" ref="B409"/>
-    <hyperlink r:id="rId80" ref="B410"/>
-    <hyperlink r:id="rId81" ref="B435"/>
-    <hyperlink r:id="rId82" ref="B436"/>
-    <hyperlink r:id="rId83" ref="B437"/>
-    <hyperlink r:id="rId84" ref="B438"/>
-    <hyperlink r:id="rId85" ref="B439"/>
-    <hyperlink r:id="rId86" ref="B440"/>
-    <hyperlink r:id="rId87" ref="B441"/>
+    <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="B56"/>
+    <hyperlink r:id="rId3" ref="B59"/>
+    <hyperlink r:id="rId4" ref="B60"/>
+    <hyperlink r:id="rId5" ref="B63"/>
+    <hyperlink r:id="rId6" ref="B85"/>
+    <hyperlink r:id="rId7" ref="B88"/>
+    <hyperlink r:id="rId8" ref="B89"/>
+    <hyperlink r:id="rId9" ref="B160"/>
+    <hyperlink r:id="rId10" ref="B169"/>
+    <hyperlink r:id="rId11" ref="B198"/>
+    <hyperlink r:id="rId12" ref="B278"/>
+    <hyperlink r:id="rId13" ref="B293"/>
+    <hyperlink r:id="rId14" ref="B328"/>
+    <hyperlink r:id="rId15" ref="B329"/>
+    <hyperlink r:id="rId16" ref="B333"/>
+    <hyperlink r:id="rId17" ref="B335"/>
+    <hyperlink r:id="rId18" ref="B337"/>
+    <hyperlink r:id="rId19" ref="B338"/>
+    <hyperlink r:id="rId20" ref="B339"/>
+    <hyperlink r:id="rId21" ref="B341"/>
+    <hyperlink r:id="rId22" ref="B346"/>
+    <hyperlink r:id="rId23" ref="B347"/>
+    <hyperlink r:id="rId24" ref="B349"/>
+    <hyperlink r:id="rId25" ref="B350"/>
+    <hyperlink r:id="rId26" ref="B351"/>
+    <hyperlink r:id="rId27" ref="B352"/>
+    <hyperlink r:id="rId28" ref="B353"/>
+    <hyperlink r:id="rId29" ref="B354"/>
+    <hyperlink r:id="rId30" ref="B355"/>
+    <hyperlink r:id="rId31" ref="B358"/>
+    <hyperlink r:id="rId32" ref="B359"/>
+    <hyperlink r:id="rId33" ref="B360"/>
+    <hyperlink r:id="rId34" ref="B361"/>
+    <hyperlink r:id="rId35" ref="B362"/>
+    <hyperlink r:id="rId36" ref="B363"/>
+    <hyperlink r:id="rId37" ref="B364"/>
+    <hyperlink r:id="rId38" ref="B365"/>
+    <hyperlink r:id="rId39" ref="B366"/>
+    <hyperlink r:id="rId40" ref="B367"/>
+    <hyperlink r:id="rId41" ref="B368"/>
+    <hyperlink r:id="rId42" ref="B369"/>
+    <hyperlink r:id="rId43" ref="B370"/>
+    <hyperlink r:id="rId44" ref="B371"/>
+    <hyperlink r:id="rId45" ref="B372"/>
+    <hyperlink r:id="rId46" ref="B373"/>
+    <hyperlink r:id="rId47" ref="B374"/>
+    <hyperlink r:id="rId48" ref="B375"/>
+    <hyperlink r:id="rId49" ref="B376"/>
+    <hyperlink r:id="rId50" ref="B377"/>
+    <hyperlink r:id="rId51" ref="B378"/>
+    <hyperlink r:id="rId52" ref="B379"/>
+    <hyperlink r:id="rId53" ref="B380"/>
+    <hyperlink r:id="rId54" ref="B381"/>
+    <hyperlink r:id="rId55" ref="B382"/>
+    <hyperlink r:id="rId56" location="/" ref="B383"/>
+    <hyperlink r:id="rId57" ref="B384"/>
+    <hyperlink r:id="rId58" location="/s/feed" ref="B385"/>
+    <hyperlink r:id="rId59" ref="B386"/>
+    <hyperlink r:id="rId60" ref="B387"/>
+    <hyperlink r:id="rId61" ref="B388"/>
+    <hyperlink r:id="rId62" location="content" ref="B389"/>
+    <hyperlink r:id="rId63" ref="B390"/>
+    <hyperlink r:id="rId64" ref="B391"/>
+    <hyperlink r:id="rId65" ref="B392"/>
+    <hyperlink r:id="rId66" ref="B393"/>
+    <hyperlink r:id="rId67" ref="B394"/>
+    <hyperlink r:id="rId68" ref="B395"/>
+    <hyperlink r:id="rId69" ref="B396"/>
+    <hyperlink r:id="rId70" ref="B397"/>
+    <hyperlink r:id="rId71" location="/s/feed" ref="B398"/>
+    <hyperlink r:id="rId72" ref="B399"/>
+    <hyperlink r:id="rId73" ref="B400"/>
+    <hyperlink r:id="rId74" ref="B401"/>
+    <hyperlink r:id="rId75" ref="B402"/>
+    <hyperlink r:id="rId76" ref="B403"/>
+    <hyperlink r:id="rId77" ref="B404"/>
+    <hyperlink r:id="rId78" ref="B405"/>
+    <hyperlink r:id="rId79" ref="B406"/>
+    <hyperlink r:id="rId80" ref="B408"/>
+    <hyperlink r:id="rId81" ref="B409"/>
+    <hyperlink r:id="rId82" ref="B410"/>
+    <hyperlink r:id="rId83" ref="B411"/>
+    <hyperlink r:id="rId84" ref="B431"/>
+    <hyperlink r:id="rId85" ref="B436"/>
+    <hyperlink r:id="rId86" ref="B437"/>
+    <hyperlink r:id="rId87" ref="B438"/>
+    <hyperlink r:id="rId88" ref="B439"/>
+    <hyperlink r:id="rId89" ref="B440"/>
+    <hyperlink r:id="rId90" ref="B441"/>
+    <hyperlink r:id="rId91" ref="B442"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId88"/>
+  <drawing r:id="rId92"/>
   <tableParts count="1">
-    <tablePart r:id="rId90"/>
+    <tablePart r:id="rId94"/>
   </tableParts>
 </worksheet>
 </file>